--- a/Excel/3_6_Enteric_OtherLivestock_WIP_v01.xlsx
+++ b/Excel/3_6_Enteric_OtherLivestock_WIP_v01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DB85443-1AB0-4F6B-8C19-503EACF4483A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07A1365E-8315-46F7-9F41-915D2185C9A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="270" yWindow="120" windowWidth="38085" windowHeight="20475" activeTab="2" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="5070" yWindow="5070" windowWidth="28800" windowHeight="15345" firstSheet="7" activeTab="7" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -20,12 +20,13 @@
     <sheet name="Input - Other Livestock" sheetId="70" r:id="rId5"/>
     <sheet name="3.6.1.1-2 Enteric Methane" sheetId="69" r:id="rId6"/>
     <sheet name="Constants - Other Livestock" sheetId="79" r:id="rId7"/>
-    <sheet name="Constants - Common" sheetId="98" r:id="rId8"/>
+    <sheet name="Constants - Common" sheetId="102" r:id="rId8"/>
     <sheet name="Acknowledgements" sheetId="72" r:id="rId9"/>
     <sheet name="Tab template" sheetId="74" r:id="rId10"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId11"/>
+    <externalReference r:id="rId12"/>
   </externalReferences>
   <definedNames>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e">_xlfn.LAMBDA(_xlpm.E_CH4,_xlpm.GWP_CH4, _xlpm.E_CH4 * _xlpm.GWP_CH4)</definedName>
@@ -107,6 +108,13 @@
     <definedName name="Common_SourceData.Common_SourceData_EFN2O_Title">_xlfn.LAMBDA("Nitrous oxide emission factors for inorganic fertiliser application")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFN2O_Unit">_xlfn.LAMBDA("(kg N2O-N / kg N")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFN2O_Variation">_xlfn.LAMBDA(_xlfn.MAKEARRAY(5, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VARIATION OF SOURCE DATA:";"Removed duplicate 'Aquaculture' row.";"Removed asterisks to aid lookup.";"Added 'production system only', 'rainfall zone' and 'irrigation method' columns to aid lookup.";"Duplicated 'non-irrigated pasture' row with same EF for low and high rainfall zones to aid lookup."}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Climate zone","EFNi &amp; EFN2O";"Wet climate zone",0.006;"Dry climate zone",0.005}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_NIRReference">_xlfn.LAMBDA("")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Source">_xlfn.LAMBDA("VEERG 2026: Table A.2.1.4")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Title">_xlfn.LAMBDA("Emission factor for organic fertiliser and crop residues returned to the soil")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Unit">_xlfn.LAMBDA("kg N2O - N / kg N")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Variable">_xlfn.LAMBDA("EFNi &amp; EFN2Oi")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Variation">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Climate zone","EFPRP";"Wet climate zone",0.006;"Dry climate zone",0.002}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_NIRReference">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Source">_xlfn.LAMBDA("VEERG 2026: Table A.2.2.2")</definedName>
@@ -178,9 +186,12 @@
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Variation">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VARIATION OF SOURCE DATA:";"Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.";"Fixed typo - Changed 'Fry' to 'Dry'."}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="CommonLivestock_InputFunctions.AverageLiveweightEndOfMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart,_xlpm.LiveweightAtStart,_xlpm.LiveweightGain, [0]!CommonLivestock_InputFunctions.LivestockMovement_ProportionalAverageLiveweightAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStart) + [0]!CommonLivestock_InputFunctions.LivestockMovement_ProportionalAverageLiveweightRemainingAtEndOfMonth(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStart, _xlpm.LiveweightAtStart, _xlpm.LiveweightGain))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_AverageLiveweightAddedDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR([0]!CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass) / [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass), 0))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_GetMovementLiveweightGain" localSheetId="7">_xlfn.LAMBDA(_xlpm.LivestockClass,_xlpm.MovementDate, _xlfn.LET(_xlpm.ym, TEXT(_xlpm.MovementDate, "yyyymm"), IFERROR(INDEX(_xlfn._xlws.FILTER(#REF!, (TEXT(#REF!, "yyyymm") = _xlpm.ym) * (#REF! = _xlpm.LivestockClass)), 1), "")))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_GetMovementLiveweightGain">_xlfn.LAMBDA(_xlpm.LivestockClass,_xlpm.MovementDate, _xlfn.LET(_xlpm.ym, TEXT(_xlpm.MovementDate, "yyyymm"), IFERROR(INDEX(_xlfn._xlws.FILTER(#REF!, (TEXT(#REF!, "yyyymm") = _xlpm.ym) * (#REF! = _xlpm.LivestockClass)), 1), "")))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth" localSheetId="7">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadAtEndOfMonth">_xlfn.LAMBDA(_xlpm.HeadAtStart,_xlpm.Month,_xlpm.LivestockClass, _xlpm.HeadAtStart + [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass) - [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadLostDuringMonth(_xlpm.Month, _xlpm.LivestockClass))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadLostDuringMonth" localSheetId="7">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadLostDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadRemainingAtMonthEnd">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStartOfMonth, MAX(_xlpm.HeadAtStartOfMonth - [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadLostDuringMonth(_xlpm.Month, _xlpm.LivestockClass), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_LiveweightAddedDuringMonth">_xlfn.LAMBDA(_xlpm.LivestockClass,_xlpm.MovementDate,_xlpm.WeightAtMovementDate,_xlpm.Head, IFERROR(_xlpm.Head * (_xlpm.WeightAtMovementDate + [0]!CommonLivestock_InputFunctions.LivestockMovement_LiveweightGrownDuringMonthPerHead(_xlpm.LivestockClass, _xlpm.MovementDate)), 0))</definedName>
@@ -192,9 +203,12 @@
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_ProportionalAverageLiveweightRemainingAtEndOfMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart,_xlpm.LiveweightAtStart,_xlpm.LiveweightGain, [0]!CommonLivestock_InputFunctions.LivestockMovement_ProportionHeadRemainingAtEndOfMonth(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStart) * CommonLivestock_InputFunctions.LivestockMovement_AverageLiveweightRemainingHead(_xlpm.Month, _xlpm.LiveweightAtStart, _xlpm.LiveweightGain))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_ProportionHeadAddedDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart, IFERROR(MIN(1, [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass) / [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAtEndOfMonth(_xlpm.HeadAtStart, _xlpm.Month, _xlpm.LivestockClass)), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_ProportionHeadRemainingAtEndOfMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart, IFERROR(MIN(1, [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadRemainingAtMonthEnd(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStart) / [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAtEndOfMonth(_xlpm.HeadAtStart, _xlpm.Month, _xlpm.LivestockClass)), 0))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightAddedDuringMonth" localSheetId="7">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightAddedDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightGrownDuringMonth" localSheetId="7">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightGrownDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightGrownDuringMonthAddedAndRemaining">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart, [0]!CommonLivestock_InputFunctions.LivestockMovement_LiveweightGrownFromMonthStartTotal(_xlpm.LivestockClass, _xlpm.Month, _xlpm.HeadAtStart) + [0]!CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightGrownDuringMonth(_xlpm.Month, _xlpm.LivestockClass))</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(19, 3, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Symbol","Manure management system","";"1","Anaerobic lagoon","Anaerobic lagoon (m=1)";"2","Liquid systems","Liquid systems (m=2)";"3","Daily spread","Daily spread (m=3)";"3a","Sump and dispersal system","Sump and dispersal system (m=3a)";"3b","Drains to paddock","Drains to paddock (m=3b)";"4","Solid storage","Solid storage (m=4)";"5","Drylot (feed pad)","Drylot (feed pad) (m=5)";"6","Composting (passive windrow)","Composting (passive windrow) (m=6)";"7","Digester / covered lagoons","Digester / covered lagoons (m=7)";"8","Deep litter","Deep litter (m=8)";"9","Pit storage","Pit storage (m=9)";"10","Poultry manure with bedding","Poultry manure with bedding (m=10)";"11","Poultry manure without bedding","Poultry manure without bedding (m=11)";"11a","Belt manure removal","Belt manure removal (m=11a)";"11b","Manure stored in house","Manure stored in house (m=11b)";"12","Direct processing","Direct processing (m=12)";"13","Direct application","Direct application (m=13)";"14","Pasture range and paddock","Pasture range and paddock (m=14)"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="EntericMethane_OtherLivestock_Equations.VEERG_3_6_1_1__1_TotalAnnualMethaneFromEntericFermentationOtherLivestock">_xlfn.LAMBDA(_xlpm.N_j,_xlpm.M_j, SUM(_xlpm.N_j * _xlpm.M_j) * 10 ^ -3)</definedName>
     <definedName name="EntericMethane_OtherLivestock_Equations.VEERG_3_6_1_1__1_TotalAnnualMethaneFromEntericFermentationOtherLivestock_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"N_j","number of livestock of each livestock type j","head","Input";"M_j","enteric fermentation emission factor","kg CH4/head/year","Constant";"j","livestock type","","Input"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="EntericMethane_OtherLivestock_Equations.VEERG_3_6_1_1__1_TotalAnnualMethaneFromEntericFermentationOtherLivestock_LatexEquation">_xlfn.LAMBDA("E_{enteric}=\sum_j(N_j\times M_j)\times 10^{-3}")</definedName>
@@ -317,7 +331,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="146">
   <si>
     <t>Home</t>
   </si>
@@ -806,6 +820,12 @@
   </si>
   <si>
     <t>t CH4</t>
+  </si>
+  <si>
+    <t>Climate Zone</t>
+  </si>
+  <si>
+    <t>EFNi &amp; EFN2Oi</t>
   </si>
 </sst>
 </file>
@@ -2111,7 +2131,31 @@
     <cellStyle name="Variable type input" xfId="64" xr:uid="{515940C5-98BF-44F7-AAB8-0D7808DD5C6C}"/>
     <cellStyle name="Variable type other" xfId="65" xr:uid="{5D88A237-9D54-45E0-A48E-F67D0639FDE2}"/>
   </cellStyles>
-  <dxfs count="66">
+  <dxfs count="67">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -3610,20 +3654,20 @@
   </dxfs>
   <tableStyles count="3" defaultTableStyle="Equation table" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Editable table" pivot="0" count="6" xr9:uid="{8C498A1C-5864-4BF8-8739-A3055FE117E0}">
-      <tableStyleElement type="wholeTable" dxfId="65"/>
-      <tableStyleElement type="headerRow" dxfId="64"/>
-      <tableStyleElement type="totalRow" dxfId="63"/>
-      <tableStyleElement type="firstColumn" dxfId="62"/>
-      <tableStyleElement type="firstRowStripe" dxfId="61"/>
-      <tableStyleElement type="secondRowStripe" dxfId="60"/>
+      <tableStyleElement type="wholeTable" dxfId="66"/>
+      <tableStyleElement type="headerRow" dxfId="65"/>
+      <tableStyleElement type="totalRow" dxfId="64"/>
+      <tableStyleElement type="firstColumn" dxfId="63"/>
+      <tableStyleElement type="firstRowStripe" dxfId="62"/>
+      <tableStyleElement type="secondRowStripe" dxfId="61"/>
     </tableStyle>
     <tableStyle name="Equation table" pivot="0" count="6" xr9:uid="{B247698E-E41D-4CCD-AA0A-C14817E9DE65}">
-      <tableStyleElement type="wholeTable" dxfId="59"/>
-      <tableStyleElement type="headerRow" dxfId="58"/>
-      <tableStyleElement type="totalRow" dxfId="57"/>
-      <tableStyleElement type="firstColumn" dxfId="56"/>
-      <tableStyleElement type="firstRowStripe" dxfId="55"/>
-      <tableStyleElement type="secondRowStripe" dxfId="54"/>
+      <tableStyleElement type="wholeTable" dxfId="60"/>
+      <tableStyleElement type="headerRow" dxfId="59"/>
+      <tableStyleElement type="totalRow" dxfId="58"/>
+      <tableStyleElement type="firstColumn" dxfId="57"/>
+      <tableStyleElement type="firstRowStripe" dxfId="56"/>
+      <tableStyleElement type="secondRowStripe" dxfId="55"/>
     </tableStyle>
     <tableStyle name="Table Style 1" pivot="0" count="0" xr9:uid="{97B370DB-5463-4A31-9160-5A96BD6A559D}"/>
   </tableStyles>
@@ -4836,6 +4880,7 @@
       <sheetName val="Constants - Common"/>
       <sheetName val="Constants - Livestock"/>
       <sheetName val="Acknowledgements"/>
+      <sheetName val="4_7_ManureManagement_OtherLives"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -4848,6 +4893,27 @@
       <sheetData sheetId="7"/>
       <sheetData sheetId="8"/>
       <sheetData sheetId="9"/>
+      <sheetData sheetId="10" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Home"/>
+      <sheetName val="Constants - Common"/>
+      <sheetName val="Acknowledgements"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4927,7 +4993,7 @@
     <tableColumn id="1" xr3:uid="{D57CB9BE-4423-4B3C-8812-0053460E9FD4}" name="Other livestock type">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_EntericFermentationEmissionFactor_Data(),Table_SourceData_OtherLivestock_EntericEF[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{076CA99E-B6FF-4452-AA90-21B8618FF161}" name="Mj" dataDxfId="53" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{076CA99E-B6FF-4452-AA90-21B8618FF161}" name="Mj" dataDxfId="54" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_EntericFermentationEmissionFactor_Data(),Table_SourceData_OtherLivestock_EntericEF[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4936,7 +5002,7 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{FC1E3F9B-244C-4BDB-9EAA-280B1B88DFD0}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{971AF780-EF58-40FF-A830-4A54D473212F}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
   <autoFilter ref="D47:H54" xr:uid="{C1F562BB-DAA6-45BB-951A-7BAFA5B64B45}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4945,19 +5011,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{9107412D-787D-4251-B022-2C951856B5CC}" name="Gas">
+    <tableColumn id="1" xr3:uid="{FA2AB5E5-72DD-48EA-A441-7826E274BEFA}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{EDAE218C-BED9-4F30-BC1A-BDA604C52911}" name="Conversion factor">
+    <tableColumn id="5" xr3:uid="{C069A4B0-ECBC-487A-9D3E-D40BCB3AFE2D}" name="Conversion factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{7B252330-4D09-4BE1-91E1-8F007E37DA8F}" name="Conversion factor 1">
+    <tableColumn id="2" xr3:uid="{6F9E09B3-0380-428A-9CB8-C5355F18AB24}" name="Conversion factor 1">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{EB2A94A6-B09F-44FC-92A1-CCB07CD838C7}" name="Conversion factor 2">
+    <tableColumn id="3" xr3:uid="{D99DCAD2-B15F-455D-A39D-C0CB7872FAC8}" name="Conversion factor 2">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{F2DB3A9E-EA47-4626-8AA6-4142F2BE5B34}" name="Conversion factor combined">
+    <tableColumn id="4" xr3:uid="{479D1385-10B4-4C3D-812C-B3ADC8B6446F}" name="Conversion factor combined">
       <calculatedColumnFormula>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4966,7 +5032,7 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{EC639B46-F2B6-417E-849A-4051D3B16B01}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{C571E06B-2FB6-4DCB-9306-6E8B7E50DF11}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
   <autoFilter ref="D89:S97" xr:uid="{5A437AE9-7724-4CF2-ACCF-291078682FB9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4986,52 +5052,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{25162FA7-7F7F-4C9C-8231-8FC51C581FD1}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{C1368F08-D067-4EEC-B0CC-D2E1F6D93274}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{6E2C0A27-43A1-4D92-B3A8-944DC7691E0A}" name="MAT" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{773305BF-D908-4C35-A934-C13BC9D3D8FF}" name="MAT" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{BCEE406F-741C-4AB5-8347-FD3CEB5D1690}" name="MAP" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
+    <tableColumn id="3" xr3:uid="{DF05DA85-723A-420A-AA03-0A716BECCE22}" name="MAP" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{BF112A88-84E8-4D38-B54C-79713ED69470}" name="Frost days per year" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
+    <tableColumn id="4" xr3:uid="{8B8F9D2B-3A8F-44F1-9417-280165AE86AB}" name="Frost days per year" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{DEDF2179-1AFD-46AA-97FF-2C7CC2C8F0A0}" name="Elevation" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
+    <tableColumn id="5" xr3:uid="{31B1CBF8-C757-4A17-AD4E-3FED04A08D97}" name="Elevation" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{517703E3-C0ED-43E3-909F-4C1979577D3C}" name="MAP:PET" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
+    <tableColumn id="6" xr3:uid="{9F5D51C1-ECC4-49B6-A4BE-AE3B3C663E64}" name="MAP:PET" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{666A24A7-650A-4B3E-982A-50311730DB7C}" name="Min temp" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
+    <tableColumn id="7" xr3:uid="{874F3D25-0748-4359-BEF3-58E34D4DFAA6}" name="Min temp" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{5604EDD5-66DF-4ECC-BCE6-DD11FD6DB4D6}" name="Max temp" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
+    <tableColumn id="8" xr3:uid="{79652299-3198-47E6-B342-A54F0A0B3674}" name="Max temp" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{6DA99F2D-CE18-432C-AB0D-72F425C17C5E}" name="Min rainfall" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
+    <tableColumn id="9" xr3:uid="{A0139A89-1186-4484-B833-03C424C4D2C4}" name="Min rainfall" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{BC2916D3-A7D1-4722-A9DC-991CB2F62BD8}" name="Max rainfall" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
+    <tableColumn id="10" xr3:uid="{BD7A797C-3EEA-481F-9533-984ECCA62AC3}" name="Max rainfall" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{1E64F234-4E02-4B45-A3A1-B18E3FFCFC37}" name="Min frost days" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
+    <tableColumn id="11" xr3:uid="{29123C0E-9E60-43AB-8679-2AC0908200D0}" name="Min frost days" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{70F03B18-1155-4824-8E62-AE5F3FA2A39C}" name="Max frost days" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
+    <tableColumn id="15" xr3:uid="{04AF6D35-FBEF-4E38-B28D-0C23F8EDC5F6}" name="Max frost days" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{C3AD9C66-0836-47F7-A64C-E903E6DAF5EE}" name="Min elevation" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
+    <tableColumn id="12" xr3:uid="{475991F7-F3B5-4EEA-966A-7AA8BC301814}" name="Min elevation" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{ED33ED06-8D20-47FE-B0B6-650FCDD420E2}" name="Max elevation" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
+    <tableColumn id="16" xr3:uid="{767BBD4C-C554-4460-AAD8-ECADA490C9C0}" name="Max elevation" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{3C28BB66-16DC-4BC9-BE53-61187001ECC2}" name="Min MAP:PET" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
+    <tableColumn id="13" xr3:uid="{65D9D85B-649F-4683-B866-BF022CDF3E13}" name="Min MAP:PET" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{FFF015AD-8516-434B-A94C-11CB9D62F62D}" name="Max MAP:PET" totalsRowDxfId="20" totalsRowCellStyle="Content bold">
+    <tableColumn id="17" xr3:uid="{969B2D30-E5CD-48F6-AF2A-DAC6295F1FF1}" name="Max MAP:PET" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5040,16 +5106,16 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{B975CFAC-C9D3-4E10-914B-A74776502697}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{DDDF37ED-9327-4273-B740-938A1214436F}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
   <autoFilter ref="D63:E77" xr:uid="{3597E019-B21E-4B76-BCC8-D02D497BCFA9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{2BBE1D44-5D3C-421E-B886-5F058BD82B23}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{26F7317C-9F68-4F62-B737-D7ABF2DFF387}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C3E0B2F3-1F7B-4FCF-B0F4-658087312975}" name="Wet or Dry Zone" totalsRowDxfId="19" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{229B1B14-5629-4B1C-9602-463A80BF745E}" name="Wet or Dry Zone" totalsRowDxfId="20" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5058,7 +5124,7 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{4F86B9BF-70ED-46B9-A712-EA42AC73454A}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{190E8CDE-696F-471D-B4F7-D0F3BE6AD6E3}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
   <autoFilter ref="D109:G112" xr:uid="{AB16FEAB-AB03-45E1-BBD4-66D29CD412DF}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5066,16 +5132,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{D5BB3355-DBBC-43C3-9C8D-BC097471993C}" name="Temperature Zone">
+    <tableColumn id="1" xr3:uid="{A767FA53-E454-4115-A4B3-DED062EED278}" name="Temperature Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{15DB6AA7-91D7-4725-9AA9-D1055AF7678C}" name="MAT">
+    <tableColumn id="2" xr3:uid="{28532D1E-227F-4FEB-818C-7F2BC92126D0}" name="MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{0AD7766B-F917-4247-BA12-141E5E455D92}" name="Min MAT">
+    <tableColumn id="3" xr3:uid="{45E163CE-3902-4B82-B9CC-59620B4E4ED4}" name="Min MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{BEC491C5-29B7-47D8-92E3-A6B4AA3DF904}" name="Max MAT">
+    <tableColumn id="4" xr3:uid="{96F2EA78-ED18-493D-8A43-55427191118E}" name="Max MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5084,7 +5150,7 @@
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{FF94A906-91DA-4FAF-A89B-CEF60B0D1275}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{78354839-706C-4F2B-BF62-2EF4D3DA4D6A}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
   <autoFilter ref="D119:G121" xr:uid="{E08772F3-2E8C-40A8-B755-08A5BBDF4130}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5092,16 +5158,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{3D6E0C09-0BD8-471F-8A53-A12A9E178BF7}" name="Rainfall Zone">
+    <tableColumn id="1" xr3:uid="{587CE355-CB72-4F48-96ED-6DC9E1A54DA9}" name="Rainfall Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{13B32985-837D-4685-9D0B-839BCC352710}" name="Annual rainfall">
+    <tableColumn id="2" xr3:uid="{CF57602B-CA70-4AA7-94E6-9CE1D9C8C294}" name="Annual rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{81010191-F2A6-4E17-8104-721B45E9D660}" name="Min rainfall">
+    <tableColumn id="3" xr3:uid="{6165D635-272A-4C24-B337-38B8A33057DA}" name="Min rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{AD6D3163-2840-4E3F-896D-5DF709C34D97}" name="Max rainfall">
+    <tableColumn id="4" xr3:uid="{02DC014A-F442-41A1-82FF-EFC4545791D6}" name="Max rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5110,16 +5176,16 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{1A2C3C00-7D5E-482F-8CA2-A213D7DF8D38}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{38538017-FC63-4011-82EC-704266C8D2C4}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
   <autoFilter ref="D127:E129" xr:uid="{A159E140-02ED-4547-B6E1-6695D8B16A11}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{A4167ABF-B475-4336-9AEE-96008ED98E6B}" name="Leaching Zone">
+    <tableColumn id="1" xr3:uid="{DFAA5237-AAFB-4DF9-9DA3-DCD93FAB1DC5}" name="Leaching Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{75B56258-627E-484F-9B94-6FD90490B5C5}" name="Leaching criteria">
+    <tableColumn id="2" xr3:uid="{A09764E1-6E11-4B1C-B1F1-FEBC49B8E8D3}" name="Leaching criteria">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5128,16 +5194,16 @@
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{4B10AEB1-ABAB-4497-8F48-0C15CDA46026}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{1853BA63-FF03-4462-8DF7-1B181A1E988D}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
   <autoFilter ref="D153:E158" xr:uid="{133D42B0-F6D2-470A-858A-37E6A7F5EC2B}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{48FCAEBE-8FA0-4664-B3AE-973A3E77EF02}" name="Data source">
+    <tableColumn id="1" xr3:uid="{42863E7D-F37C-4BA5-9E68-29F1E38F6FDA}" name="Data source">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{F269D724-DA61-40DD-B1DD-62089B53A254}" name="Data score">
+    <tableColumn id="2" xr3:uid="{4991511C-C30A-414A-A986-F9F2B5CC50FF}" name="Data score">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5146,16 +5212,16 @@
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="33" xr:uid="{45FE08A5-0001-4080-8F90-757F959BAB2B}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="33" xr:uid="{73AEE5E4-934C-4F38-B902-F08C65D152AC}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
   <autoFilter ref="D134:E136" xr:uid="{308E99BE-FE1F-47A4-B2CA-97217277C4E9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{ACC4E2B3-A6FC-4D50-BE90-6D711BFC3B97}" name="Is in leaching zone">
+    <tableColumn id="1" xr3:uid="{C06588B3-DEB9-485D-8845-44DC96AA1C03}" name="Is in leaching zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{35F8284C-32FA-4320-AF32-3F44CCB77CF7}" name="FracWET" dataDxfId="18">
+    <tableColumn id="2" xr3:uid="{0CB971CE-8314-492D-B32B-05442AFAE65D}" name="FracWET" dataDxfId="19">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5164,7 +5230,7 @@
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="34" xr:uid="{B985452B-55AC-4EB5-AA25-EAD220463DA8}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="34" xr:uid="{BC204499-D622-48C9-BC09-4C59BFEF7A12}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
   <autoFilter ref="D186:H199" xr:uid="{D41FBEA4-8379-4DF7-A068-BF94D364F1A2}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5173,19 +5239,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{D74A144B-9F75-433D-BE41-D183AF51F2BB}" name="Production system j">
+    <tableColumn id="1" xr3:uid="{FE9A6402-9F17-45D6-81C9-B41AC3C7954F}" name="Production system j">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{87B0476D-5F45-43A5-9823-48327AFBBFC0}" name="EFN2O">
+    <tableColumn id="2" xr3:uid="{7CE8B532-E797-4359-A943-59732EBA406D}" name="EFN2O">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{A580C8EE-E9FD-4201-94D1-F99A9BC27373}" name="Production system only">
+    <tableColumn id="3" xr3:uid="{A318BF51-4D2E-48DE-BE88-1E4A8ED19B82}" name="Production system only">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{50C2C17E-A21C-4FDA-82A8-EF761C0E6BF7}" name="Irrigation method">
+    <tableColumn id="4" xr3:uid="{2C6FADCF-C3FB-4DD1-9001-F40AFA0E89CC}" name="Irrigation method">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{7F2E249C-6080-446E-8674-6F29CE0873E0}" name="Rainfall zone">
+    <tableColumn id="5" xr3:uid="{8487FBC9-6B3C-4956-B063-649C33304B05}" name="Rainfall zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5194,16 +5260,16 @@
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="35" xr:uid="{F1D7CB04-0839-425A-B673-CEA7A9C3FB85}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="35" xr:uid="{51ECE1AA-22EA-44EA-9C2E-4882AFCB4FA8}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
   <autoFilter ref="D142:E147" xr:uid="{1F48CA34-50DE-46D5-B32A-BB3A1E818E37}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{6328C683-420D-4EA6-AF9D-245995DC8FD1}" name="Irrigation type i">
+    <tableColumn id="1" xr3:uid="{E69E76C7-3ABC-4D33-A248-F4FD8C78DC75}" name="Irrigation type i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{9E5FEA9D-8FB5-494C-9D24-0E6BFC0C6057}" name="FracWET" dataDxfId="17" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{30062886-D624-44B9-A4D6-8172FDB32ACC}" name="FracWET" dataDxfId="18" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5212,16 +5278,16 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{75649617-63F2-4A80-A5EB-06A3280A3C57}" name="Table_SourceData_OtherLivestock_VolatileSolids" displayName="Table_SourceData_OtherLivestock_VolatileSolids" ref="D24:E32" totalsRowShown="0" dataDxfId="52" dataCellStyle="Content normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{75649617-63F2-4A80-A5EB-06A3280A3C57}" name="Table_SourceData_OtherLivestock_VolatileSolids" displayName="Table_SourceData_OtherLivestock_VolatileSolids" ref="D24:E32" totalsRowShown="0" dataDxfId="53" dataCellStyle="Content normal">
   <autoFilter ref="D24:E32" xr:uid="{75649617-63F2-4A80-A5EB-06A3280A3C57}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{3E3B834E-0F7A-47D3-954A-A57B2234370A}" name="Other livestock type" dataDxfId="51" dataCellStyle="Content normal">
+    <tableColumn id="1" xr3:uid="{3E3B834E-0F7A-47D3-954A-A57B2234370A}" name="Other livestock type" dataDxfId="52" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_VolatileSolidsProduced_Data(),Table_SourceData_OtherLivestock_VolatileSolids[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{0BCFF128-A246-43C6-BB57-DC9448A80579}" name="VSj" dataDxfId="50" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{0BCFF128-A246-43C6-BB57-DC9448A80579}" name="VSj" dataDxfId="51" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_VolatileSolidsProduced_Data(),Table_SourceData_OtherLivestock_VolatileSolids[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5230,16 +5296,16 @@
 </file>
 
 <file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="36" xr:uid="{E9AFCB04-6C42-4BD7-84F4-CB502355AF0E}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="36" xr:uid="{6C67BE23-86D2-4A05-B2BC-EE396C2C0C0E}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
   <autoFilter ref="D206:E208" xr:uid="{D5BE3F89-D70E-4C53-A71C-E756622DEF38}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{FB787692-FEAA-422C-9A68-A116E1C1D839}" name="Climate zone">
+    <tableColumn id="1" xr3:uid="{1236BDD8-AEEC-4D8A-AEFB-ED9356DF3DD1}" name="Climate zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{AFBB6C89-F456-4C86-80FD-B734DEFDFF30}" name="EFPRP" dataDxfId="16" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{F6888293-D606-47A6-8932-E2CD434BD8A5}" name="EFPRP" dataDxfId="17" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5248,16 +5314,16 @@
 </file>
 
 <file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="37" xr:uid="{A23F6973-616E-44B9-9455-AEC834A8AADB}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="37" xr:uid="{AFCD272F-7568-43A4-AF7A-23066986692E}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
   <autoFilter ref="D212:E224" xr:uid="{97796C3A-D95E-4077-AA20-A8FE4145DAAD}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{E0DBFFCC-335E-4C29-BC47-5C2A3243CFF0}" name="Month">
+    <tableColumn id="1" xr3:uid="{082A87F0-D13A-4480-8492-F3D2503C41E2}" name="Month">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{AC3827EF-FE9E-4E81-A7C7-95A7165D62C5}" name="Season" dataDxfId="15" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{3A38DFCE-8BC1-411E-9649-BA3B242C5C67}" name="Season" dataDxfId="16" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5266,7 +5332,7 @@
 </file>
 
 <file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="39" xr:uid="{88FD98D7-E5DB-4B28-9E47-A6481BEC1373}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="39" xr:uid="{A9D87315-F27A-46A3-A327-DB14F89DB92B}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
   <autoFilter ref="D231:S250" xr:uid="{1D72DD9B-C8FA-48F4-9A11-20231FF87B5A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5286,52 +5352,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{8C0CBC0D-B831-4C7E-9F24-0EE0037F3E6B}" name="Temperature zone">
+    <tableColumn id="1" xr3:uid="{74BFEBA4-3487-4BE5-88B9-85DB7D433F74}" name="Temperature zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{B6E0D171-2FBE-46A9-9B1F-1269E55C1B38}" name="MAT (ºC)" dataDxfId="14" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{EE7A79F3-7EC2-470C-8060-08333EAEE5D6}" name="MAT (ºC)" dataDxfId="15" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{7FF50BBA-30EE-4E1A-9449-9265A1067683}" name="Anaerobic lagoon" dataDxfId="13" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{FB41F6A9-5353-48F8-BBE2-FDDAFFCEC3DF}" name="Anaerobic lagoon" dataDxfId="14" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{53654E61-5BB1-44D1-A97F-E38B4117F28F}" name="Digester / covered lagoons" dataDxfId="12" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{46BC84F5-D586-4491-8920-08D8E8254F8B}" name="Digester / covered lagoons" dataDxfId="13" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{5736C277-B619-4577-BE61-C6F2CFEBBDF4}" name="Liquid systems" dataDxfId="11" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{48357028-DF7D-43C1-8693-BE3CCAEDC19B}" name="Liquid systems" dataDxfId="12" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{A4F5FCA7-77C5-40B2-BAC9-EBF849F5559B}" name="Daily spread" dataDxfId="10" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{46A64015-6571-40C8-8B97-9ACD24D0FDFF}" name="Daily spread" dataDxfId="11" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{D7CABD47-531A-49AF-865F-934434068DEC}" name="Composting (passive windrow)" dataDxfId="9" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{BE8A0DB7-DA22-4D11-8D6E-5B03E95383E1}" name="Composting (passive windrow)" dataDxfId="10" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{5B3C335A-BC58-40E9-8E75-96ED6CCF795D}" name="Solid storage" dataDxfId="8" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{8E9FF3D7-C170-4D01-8CAA-D667E3762352}" name="Solid storage" dataDxfId="9" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{2D3901FD-AFED-45CA-9E32-1204AF6D4874}" name="Pit storage" dataDxfId="7" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{EE8195E9-7EB7-4255-B88A-1A7D661007AC}" name="Pit storage" dataDxfId="8" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{343A0FE7-0AA0-43C9-9A4F-02E9C242020A}" name="Deep litter" dataDxfId="6" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{E8290DA2-F81B-417D-8DFF-811E04AE5CD6}" name="Deep litter" dataDxfId="7" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{FAF69A1E-4587-4DCD-9535-2ECADB3A8A73}" name="Poultry manure with bedding" dataDxfId="5" dataCellStyle="Content normal">
+    <tableColumn id="11" xr3:uid="{8556C44B-D53C-43B5-AFA8-775CF9A97C5A}" name="Poultry manure with bedding" dataDxfId="6" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{9D86AF5D-FDC1-4EE1-9D47-BA4BE96F619F}" name="Poultry manure without bedding" dataDxfId="4" dataCellStyle="Content normal">
+    <tableColumn id="12" xr3:uid="{6D7005A7-1332-4775-A075-04932CE4CB0C}" name="Poultry manure without bedding" dataDxfId="5" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{C15483D8-6A7E-4D26-B81F-096629F52A98}" name="Direct processing" dataDxfId="3" dataCellStyle="Content normal">
+    <tableColumn id="13" xr3:uid="{CD24F3C7-0171-4241-9095-F217ACFB21FD}" name="Direct processing" dataDxfId="4" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{F82A14FE-E6A5-4C72-AE16-87CCAF66B3DB}" name="Direct application" dataDxfId="2" dataCellStyle="Content normal">
+    <tableColumn id="14" xr3:uid="{B9A1E1BC-6DAC-4A86-933B-0394729DEF0D}" name="Direct application" dataDxfId="3" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{DBBFE03E-A035-4E39-B68B-F044C4B1E37F}" name="Pasture range and paddock" dataDxfId="1" dataCellStyle="Content normal">
+    <tableColumn id="15" xr3:uid="{D37545E7-3A7F-4E1D-9175-AF768DF5CDBB}" name="Pasture range and paddock" dataDxfId="2" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{EE478F66-8602-4161-AB22-52FED9A026F5}" name="MAT raw" dataDxfId="0" dataCellStyle="Content normal">
+    <tableColumn id="16" xr3:uid="{01BDA555-814C-4F57-A554-B9E8D1197D3B}" name="MAT raw" dataDxfId="1" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5339,17 +5405,35 @@
 </table>
 </file>
 
+<file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="40" xr:uid="{918D91AC-F0D7-45AF-888F-8CCD5245EE64}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
+  <autoFilter ref="D257:E259" xr:uid="{56E01C14-1BB8-4015-9158-4CEB4D3B605C}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{FD1030A0-8423-4F54-A208-B8E2F9F2CCAF}" name="Climate Zone">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{5D7849B7-3122-4868-94E6-53DB0ADF4E31}" name="EFNi &amp; EFN2Oi" dataDxfId="0" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{522C94C8-449D-4574-AF4D-39C274C53A6F}" name="Table_SourceData_OtherLivestock_NitrogenExcreted" displayName="Table_SourceData_OtherLivestock_NitrogenExcreted" ref="D39:E47" totalsRowShown="0" dataDxfId="49" dataCellStyle="Content normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{522C94C8-449D-4574-AF4D-39C274C53A6F}" name="Table_SourceData_OtherLivestock_NitrogenExcreted" displayName="Table_SourceData_OtherLivestock_NitrogenExcreted" ref="D39:E47" totalsRowShown="0" dataDxfId="50" dataCellStyle="Content normal">
   <autoFilter ref="D39:E47" xr:uid="{522C94C8-449D-4574-AF4D-39C274C53A6F}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{92CD5559-01AC-4144-B6DC-7F856864840C}" name="Other livestock type" dataDxfId="48" dataCellStyle="Content normal">
+    <tableColumn id="1" xr3:uid="{92CD5559-01AC-4144-B6DC-7F856864840C}" name="Other livestock type" dataDxfId="49" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_NitrogenExcreted_Data(),Table_SourceData_OtherLivestock_NitrogenExcreted[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{A4955FC2-927B-4DF6-B94C-068E74A6FF39}" name="NEj" dataDxfId="47" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{A4955FC2-927B-4DF6-B94C-068E74A6FF39}" name="NEj" dataDxfId="48" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_NitrogenExcreted_Data(),Table_SourceData_OtherLivestock_NitrogenExcreted[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5358,20 +5442,20 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{08C66B47-C28A-4E61-BD61-AB59792A938B}" name="Table_SourceData_OtherLivestock_AverageLiveweight" displayName="Table_SourceData_OtherLivestock_AverageLiveweight" ref="D54:F64" totalsRowShown="0" dataDxfId="46" dataCellStyle="Content normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{08C66B47-C28A-4E61-BD61-AB59792A938B}" name="Table_SourceData_OtherLivestock_AverageLiveweight" displayName="Table_SourceData_OtherLivestock_AverageLiveweight" ref="D54:F64" totalsRowShown="0" dataDxfId="47" dataCellStyle="Content normal">
   <autoFilter ref="D54:F64" xr:uid="{08C66B47-C28A-4E61-BD61-AB59792A938B}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{92B26601-57E2-4637-B097-133483C8744F}" name="Other livestock type" dataDxfId="45" dataCellStyle="Content normal">
+    <tableColumn id="1" xr3:uid="{92B26601-57E2-4637-B097-133483C8744F}" name="Other livestock type" dataDxfId="46" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_AverageLiveweight_Data(),Table_SourceData_OtherLivestock_AverageLiveweight[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{6D10B565-469B-4476-91DD-3E192D501AEC}" name="Wco" dataDxfId="44" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{6D10B565-469B-4476-91DD-3E192D501AEC}" name="Wco" dataDxfId="45" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_AverageLiveweight_Data(),Table_SourceData_OtherLivestock_AverageLiveweight[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{4285ACF1-A507-45A9-B06F-3C8A119CF7C4}" name="Wco2" dataDxfId="43" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{4285ACF1-A507-45A9-B06F-3C8A119CF7C4}" name="Wco2" dataDxfId="44" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_AverageLiveweight_Data(),Table_SourceData_OtherLivestock_AverageLiveweight[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5380,20 +5464,20 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{717E53D2-4463-4A85-80B5-5691AD7D98C8}" name="Table_SourceData_OtherLivestock_FractionWasteInMMS" displayName="Table_SourceData_OtherLivestock_FractionWasteInMMS" ref="D71:F79" totalsRowShown="0" dataDxfId="42" dataCellStyle="Content normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{717E53D2-4463-4A85-80B5-5691AD7D98C8}" name="Table_SourceData_OtherLivestock_FractionWasteInMMS" displayName="Table_SourceData_OtherLivestock_FractionWasteInMMS" ref="D71:F79" totalsRowShown="0" dataDxfId="43" dataCellStyle="Content normal">
   <autoFilter ref="D71:F79" xr:uid="{717E53D2-4463-4A85-80B5-5691AD7D98C8}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{3C1197CD-1D52-441D-BBC2-CD949C23252D}" name="Other livestock type" dataDxfId="41" dataCellStyle="Content normal">
+    <tableColumn id="1" xr3:uid="{3C1197CD-1D52-441D-BBC2-CD949C23252D}" name="Other livestock type" dataDxfId="42" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_FractionWasteInMMS_Data(),Table_SourceData_OtherLivestock_FractionWasteInMMS[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{8073D8FF-B3DA-4F6A-932F-294E074768D7}" name="Pasture range and paddock" dataDxfId="40" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{8073D8FF-B3DA-4F6A-932F-294E074768D7}" name="Pasture range and paddock" dataDxfId="41" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_FractionWasteInMMS_Data(),Table_SourceData_OtherLivestock_FractionWasteInMMS[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{BE446918-69F7-4B13-8457-24AF8D4D48BC}" name="Uncovered anaerobic lagoon" dataDxfId="39" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{BE446918-69F7-4B13-8457-24AF8D4D48BC}" name="Uncovered anaerobic lagoon" dataDxfId="40" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_FractionWasteInMMS_Data(),Table_SourceData_OtherLivestock_FractionWasteInMMS[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5402,20 +5486,20 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{AFA04BB4-DA20-428E-BF28-5455856D0A35}" name="Table_SourceData_OtherLivestock_MCF" displayName="Table_SourceData_OtherLivestock_MCF" ref="D86:F94" totalsRowShown="0" dataDxfId="38" dataCellStyle="Content normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{AFA04BB4-DA20-428E-BF28-5455856D0A35}" name="Table_SourceData_OtherLivestock_MCF" displayName="Table_SourceData_OtherLivestock_MCF" ref="D86:F94" totalsRowShown="0" dataDxfId="39" dataCellStyle="Content normal">
   <autoFilter ref="D86:F94" xr:uid="{AFA04BB4-DA20-428E-BF28-5455856D0A35}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{378D0529-B2BA-4B26-B22D-9D5AE994C705}" name="Other livestock type" dataDxfId="37" dataCellStyle="Content normal">
+    <tableColumn id="1" xr3:uid="{378D0529-B2BA-4B26-B22D-9D5AE994C705}" name="Other livestock type" dataDxfId="38" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_MethaneConversionFactor_Data(),Table_SourceData_OtherLivestock_MCF[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{614FC5E3-9067-4D7A-9048-5C785284F6FC}" name="Pasture range and paddock" dataDxfId="36" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{614FC5E3-9067-4D7A-9048-5C785284F6FC}" name="Pasture range and paddock" dataDxfId="37" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_MethaneConversionFactor_Data(),Table_SourceData_OtherLivestock_MCF[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{9125F130-A695-42FD-984B-66D9A47F338B}" name="Uncovered anaerobic lagoon" dataDxfId="35" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{9125F130-A695-42FD-984B-66D9A47F338B}" name="Uncovered anaerobic lagoon" dataDxfId="36" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_MethaneConversionFactor_Data(),Table_SourceData_OtherLivestock_MCF[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5424,20 +5508,20 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{819F82E1-8BFB-49BB-A84C-1541D2694B39}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{3CE089AD-2CC8-4A13-B28C-D1C37F1413FD}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
   <autoFilter ref="D6:F14" xr:uid="{E0906749-7FC7-47DE-82F6-F796C4463018}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{70652AFC-F3E8-4421-AFD1-2D686D40D22D}" name="State/Territory">
+    <tableColumn id="1" xr3:uid="{5C8F314E-448B-4DFB-9FB6-24EB1C068822}" name="State/Territory">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{1FA7E548-C0EA-432C-8E8B-704642D10B8B}" name="Common Name">
+    <tableColumn id="2" xr3:uid="{0CDE5FB6-156E-4C8F-BE5E-AE847E4623E5}" name="Common Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{EBC3E112-1444-44E8-96B3-3CA9BA6303FD}" name="Abbreviation">
+    <tableColumn id="3" xr3:uid="{48462493-A4EA-444E-992B-54CD236800AC}" name="Abbreviation">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5446,12 +5530,12 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{4E187021-E65C-4405-B076-51664A260F70}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{277630A7-A8D1-4F5F-B575-BC9FABFD34E8}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
   <autoFilter ref="D20:D30" xr:uid="{5FA81339-C6C8-4D36-BEEA-6C4AEDD9E676}">
     <filterColumn colId="0" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{BE8A74F0-502F-4C09-B30D-79967B1CA4B3}" name="SA 4 Name">
+    <tableColumn id="1" xr3:uid="{D18F34C1-11FB-4248-811F-713D855F6948}" name="SA 4 Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5460,16 +5544,16 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{E185DEA7-0F0B-4043-8184-02AAE04CE1D3}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{A11C6061-9DBF-4C48-A0C9-EF5912EE11FB}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
   <autoFilter ref="D36:E43" xr:uid="{B8E87A66-3E41-4AD3-925D-01EE21B43D7A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{969FB6F5-5748-416A-B0E7-0FA856E9228D}" name="Gas">
+    <tableColumn id="1" xr3:uid="{D1260DFE-7F08-4477-ADE7-CA810E99F721}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{D288383E-5A93-48FA-8608-CEA132940F23}" name="CO2-e factor">
+    <tableColumn id="2" xr3:uid="{E52C9195-EBCB-4DA9-9E83-AFF26E2BF1B7}" name="CO2-e factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -11512,11 +11596,11 @@
       </c>
       <c r="H7" s="85">
         <f>'3.6.1.1-2 Enteric Methane'!E33</f>
-        <v>17659.599999999999</v>
+        <v>0</v>
       </c>
       <c r="I7" s="85">
         <f>H7</f>
-        <v>17659.599999999999</v>
+        <v>0</v>
       </c>
       <c r="J7" s="50" t="s">
         <v>84</v>
@@ -11538,11 +11622,11 @@
       <c r="G8" s="29"/>
       <c r="H8" s="86">
         <f>SUM(H7:H7)</f>
-        <v>17659.599999999999</v>
+        <v>0</v>
       </c>
       <c r="I8" s="86">
         <f>SUM(I7:I7)</f>
-        <v>17659.599999999999</v>
+        <v>0</v>
       </c>
       <c r="J8" s="81" t="s">
         <v>84</v>
@@ -14329,8 +14413,8 @@
       </c>
       <c r="F31" s="106"/>
       <c r="G31" s="48">
-        <f>Common_InputFunctions.Utility_LookupValueInTableNumber("CH4",[1]!Table_GWPData[Gas],[1]!Table_GWPData[CO2-e factor])</f>
-        <v>28</v>
+        <f>Common_InputFunctions.Utility_LookupValueInTableNumber("CH4",[1]!Table_GWPData1412[Gas],[1]!Table_GWPData1412[CO2-e factor])</f>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -14340,7 +14424,7 @@
       </c>
       <c r="E33" s="43" cm="1">
         <f t="array" ref="E33">Common_Equations.Common_ConvertCH4ToCO2e(G30,G31)</f>
-        <v>17659.599999999999</v>
+        <v>0</v>
       </c>
       <c r="F33" s="81" t="str" cm="1">
         <f t="array" ref="F33">Common_Equations.Common_ConvertN2OToCO2e_Unit()</f>
@@ -16117,8 +16201,8 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7548F5C8-4326-4B87-AF98-B62783E0FF5C}">
-  <dimension ref="A1:BY250"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61A98245-077D-4620-A68F-E98BAE61B1C4}">
+  <dimension ref="A1:BY259"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.7109375" style="7" customWidth="1"/>
@@ -16154,10 +16238,7 @@
     </row>
     <row r="2" spans="1:65" s="9" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="str">
-        <f>HYPERLINK("#'Home'!A1", "Home")</f>
-        <v>Home</v>
-      </c>
+      <c r="A3"/>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
@@ -16181,17 +16262,11 @@
       <c r="W3" s="11"/>
     </row>
     <row r="4" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="str">
-        <f>HYPERLINK("#'Overview'!A1", "Overview")</f>
-        <v>Overview</v>
-      </c>
+      <c r="A4"/>
       <c r="BM4" s="3"/>
     </row>
     <row r="5" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="17" t="str">
-        <f>HYPERLINK("#'Results'!A1", "Results")</f>
-        <v>Results</v>
-      </c>
+      <c r="A5"/>
       <c r="D5" s="6" t="str" cm="1">
         <f t="array" ref="D5">Common_SourceData.Common_SourceData_AustralianStatesTerritories_Title()</f>
         <v>Australian states and territories</v>
@@ -16199,7 +16274,7 @@
       <c r="BM5" s="3"/>
     </row>
     <row r="6" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="16"/>
+      <c r="A6"/>
       <c r="D6" s="35" t="s">
         <v>12</v>
       </c>
@@ -16211,9 +16286,7 @@
       </c>
     </row>
     <row r="7" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="20" t="s">
-        <v>3</v>
-      </c>
+      <c r="A7"/>
       <c r="D7" s="35" t="str" cm="1">
         <f t="array" ref="D7">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>New South Wales</v>
@@ -16228,10 +16301,7 @@
       </c>
     </row>
     <row r="8" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="17" t="str">
-        <f>HYPERLINK("#'Input - Site'!A1", "Site")</f>
-        <v>Site</v>
-      </c>
+      <c r="A8"/>
       <c r="D8" s="35" t="str" cm="1">
         <f t="array" ref="D8">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>Australian Capital Territory</v>
@@ -16246,10 +16316,7 @@
       </c>
     </row>
     <row r="9" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="17" t="str">
-        <f>HYPERLINK("#'Input - Other Livestock'!A1", "Other Livestock")</f>
-        <v>Other Livestock</v>
-      </c>
+      <c r="A9"/>
       <c r="D9" s="35" t="str" cm="1">
         <f t="array" ref="D9">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>Victoria</v>
@@ -16264,7 +16331,7 @@
       </c>
     </row>
     <row r="10" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="17"/>
+      <c r="A10"/>
       <c r="D10" s="35" t="str" cm="1">
         <f t="array" ref="D10">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>Queensland</v>
@@ -16279,9 +16346,7 @@
       </c>
     </row>
     <row r="11" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
-        <v>56</v>
-      </c>
+      <c r="A11"/>
       <c r="D11" s="35" t="str" cm="1">
         <f t="array" ref="D11">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>South Australia</v>
@@ -16297,10 +16362,7 @@
       <c r="BM11" s="3"/>
     </row>
     <row r="12" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="17" t="str">
-        <f>HYPERLINK("#'3.6.1.1-2 Enteric Methane'!A1", "3.6.1.1-2 Enteric Methane")</f>
-        <v>3.6.1.1-2 Enteric Methane</v>
-      </c>
+      <c r="A12"/>
       <c r="D12" s="35" t="str" cm="1">
         <f t="array" ref="D12">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>Western Australia</v>
@@ -16331,9 +16393,7 @@
       </c>
     </row>
     <row r="14" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="18" t="s">
-        <v>4</v>
-      </c>
+      <c r="A14"/>
       <c r="D14" s="35" t="str" cm="1">
         <f t="array" ref="D14">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>Northern Territory</v>
@@ -16348,22 +16408,13 @@
       </c>
     </row>
     <row r="15" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="17" t="str">
-        <f>HYPERLINK("#'Constants - Other Livestock'!A1", "Constants - Other Livestock")</f>
-        <v>Constants - Other Livestock</v>
-      </c>
+      <c r="A15"/>
     </row>
     <row r="16" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="17" t="str">
-        <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
-        <v>Constants - Common</v>
-      </c>
+      <c r="A16"/>
     </row>
     <row r="17" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="17" t="str">
-        <f>HYPERLINK("#'Acknowledgements'!A1", "Acknowledgements")</f>
-        <v>Acknowledgements</v>
-      </c>
+      <c r="A17"/>
     </row>
     <row r="18" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18"/>
@@ -16386,7 +16437,7 @@
       </c>
     </row>
     <row r="21" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="17"/>
+      <c r="A21"/>
       <c r="D21" s="35" t="str" cm="1">
         <f t="array" ref="D21">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Bunbury</v>
@@ -17554,31 +17605,31 @@
       </c>
       <c r="T97" s="35"/>
     </row>
-    <row r="98" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D98" s="50" t="str" cm="1">
-        <f t="array" ref="D98:D101">Common_SourceData.Common_SourceData_ClimateZones_Appendices()</f>
+    <row r="98" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D99" s="50" t="str" cm="1">
+        <f t="array" ref="D99:D102">Common_SourceData.Common_SourceData_ClimateZones_Appendices()</f>
         <v>Note:</v>
-      </c>
-    </row>
-    <row r="99" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D99" s="50" t="str">
-        <v>MAT = mean annual temperature</v>
       </c>
     </row>
     <row r="100" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D100" s="50" t="str">
-        <v>MAP = mean annual precipitation</v>
+        <v>MAT = mean annual temperature</v>
       </c>
     </row>
     <row r="101" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D101" s="50" t="str">
+        <v>MAP = mean annual precipitation</v>
+      </c>
+    </row>
+    <row r="102" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D102" s="50" t="str">
         <v>PET = potential evapotranspiration</v>
       </c>
     </row>
-    <row r="102" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D102" s="50"/>
-    </row>
-    <row r="103" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D103" s="50"/>
+    </row>
     <row r="104" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="105" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D105" s="6" t="str" cm="1">
@@ -20064,10 +20115,62 @@
         <v>28</v>
       </c>
     </row>
+    <row r="253" spans="4:19" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="D253" s="6" t="str" cm="1">
+        <f t="array" ref="D253">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Title()</f>
+        <v>Emission factor for organic fertiliser and crop residues returned to the soil</v>
+      </c>
+    </row>
+    <row r="254" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D254" s="5" t="str" cm="1">
+        <f t="array" ref="D254">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Source()</f>
+        <v>VEERG 2026: Table A.2.1.4</v>
+      </c>
+    </row>
+    <row r="255" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D255" s="1" t="str" cm="1">
+        <f t="array" ref="D255">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Variable()</f>
+        <v>EFNi &amp; EFN2Oi</v>
+      </c>
+    </row>
+    <row r="256" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D256" s="50" t="str" cm="1">
+        <f t="array" ref="D256">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Unit()</f>
+        <v>kg N2O - N / kg N</v>
+      </c>
+    </row>
+    <row r="257" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D257" s="35" t="s">
+        <v>144</v>
+      </c>
+      <c r="E257" s="35" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="258" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D258" s="35" t="str" cm="1">
+        <f t="array" ref="D258">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
+        <v>Wet climate zone</v>
+      </c>
+      <c r="E258" s="35" cm="1">
+        <f t="array" ref="E258">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
+        <v>6.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="259" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D259" s="1" t="str" cm="1">
+        <f t="array" ref="D259">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
+        <v>Dry climate zone</v>
+      </c>
+      <c r="E259" s="35" cm="1">
+        <f t="array" ref="E259">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <tableParts count="16">
+  <tableParts count="17">
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
     <tablePart r:id="rId4"/>
@@ -20084,6 +20187,7 @@
     <tablePart r:id="rId15"/>
     <tablePart r:id="rId16"/>
     <tablePart r:id="rId17"/>
+    <tablePart r:id="rId18"/>
   </tableParts>
 </worksheet>
 </file>
@@ -20104,10 +20208,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgACcARgByAHkAJwAgAHQAbwAgACcARAByAHkAJwAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBXAGUAdAAgAG8AcgAgAEQAcgB5ACAAWgBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAG4AdABhAG4AZQBcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIAB3AGUAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGgAaQBnAGgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGgAaQBnAGgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAAaQBuACAATQBBAFQAIAB2AGEAbAB1AGUAIABmAG8AcgAgAHcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGMAaABhAG4AZwBlAGQAIAAxADAAIAB0AG8AIAAxADEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAbQBpAG4AIABhAG4AZAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAGYAbwByACAATQBBAFQALAAgAE0AQQBQACwAIABmAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByACwAIABlAGwAZQB2AGEAdABpAG8AbgAsACAATQBBAFAAOgBQAEUAVAAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQBzACAAZgByAG8AbQAgAHIAZQBhAGwAIABjAGwAaQBtAGEAdABlACAAZABhAHQAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAEEARgAgAGEAYwBjAGUAcAB0AHMAIAByAGEAaQBuAGYAYQBsAGwAIABhAHMAIABhACAAcAByAG8AeAB5ACAAZgBvAHIAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADEANgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAXAAiACwAIABcACIATQBBAFAAXAAiACwAIABcACIARgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgBcACIALAAgAFwAIgBFAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAEEAUAA6AFAARQBUAFwAIgAsACAAXAAiAE0AaQBuACAAdABlAG0AcABcACIALAAgAFwAIgBNAGEAeAAgAHQAZQBtAHAAXAAiACwAIABcACIATQBpAG4AIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIATQBhAHgAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIATQBpAG4AIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AYQB4ACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGkAbgAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AYQB4ACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAG4AdABhAG4AZQBcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgA+ACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAPgAgADEAOAAgAEMAXAAiACwAIABcACIAPgAgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAyADAAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgA+ACAAMQAwADAAMAAgAG0AbQAgAC0AIABkIiAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADEAMAAwADAALgAwADAAMQAsACAAMgAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAD4AIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgA+ACAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdABlADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBUACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABFAFQAIAA9ACAAcABvAHQAZQBuAHQAaQBhAGwAIABlAHYAYQBwAG8AdAByAGEAbgBzAHAAaQByAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABNAEEAVAAgAG0AaQBuACAAYQBuAGQAIABNAEEAVAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAGUAZABpAGEAbgAgAEEAbgBuAHUAYQBsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAKABNAEEAVAApAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFQAXAAiACwAIABcACIATQBhAHgAIABNAEEAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIiAAMgA2ACAAQwBcACIALAAgADIANgAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIABcACIAMQA1ACAALQAgADIANQAgAEMAXAAiACwAIAAxADUALAAgADIANQAuADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIgADEANAAgAEMAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADQALgA5ADkAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGEAbABsACAAWgBvAG4AZQBcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgBcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGEAeABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAD4AIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAPgCjAygANdg43DXYR9wwACkAKwA12GDcNdhc3DXYVtw12FncIAA12GTcNdhO3DXYYdw12FLcNdhf3CAADiE12FzcNdhZ3DXYUdw12FbcNdhb3DXYVNwgADXYUNw12E7cNdhd3DXYTtw12FDcNdhW3DXYYdw12GbcXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGQAbwBlAHMAIABuAG8AdAAgAG8AYwBjAHUAcgBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAZCKjAygANdg43DXYR9wwACkAKwA12GDcNdhc3DXYVtw12FncIAA12GTcNdhO3DXYYdw12FLcNdhf3CAADiE12FzcNdhZ3DXYUdw12FbcNdhb3DXYVNwgADXYUNw12E7cNdhd3DXYTtw12FDcNdhW3DXYYdw12GbcXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHMAIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBZAGUAcwAgAC0AIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AIAAtACAAbgBvAHQAIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABkAGEAdABhACAAcwBjAG8AcgBlAHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAWABYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAYQB0AGEAIABzAG8AdQByAGMAZQBcACIALAAgAFwAIgBEAGEAdABhACAAcwBjAG8AcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAG4AdABlAHIAbgBhAHQAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAgAG8AcgAgAHIAZQBnAGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAAaQBuAHQAZQBuAHMAaQB0AHkAIABjAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgAGEAcABwAHIAbwB2AGUAZAAgAG0AZQB0AGgAbwBkAFwAIgAsACAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGUAcgBpAGYAaQBlAGQAIABjAHIAZQBkAGUAbgB0AGkAYQBsACAAbQBhAHQAYwBoAGkAbgBnACAASQBTAE8AMQA0ADAANgA3AFwAIgAsACAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAATABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgACgAMwAuAEQALgBiAC4AMgApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAEwARQBBAEMASABcACIALAAwAC4AMgA0AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAGcAZQBuACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAGcAZQBuACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgAgADMALgBEAC4AQgBfADEAMABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAbABlAGEAYwBoAFwAIgAsADAALgAwADEAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBOADIATwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAANQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAagBcACIALABcACIARQBGAE4AMgBPAFwAIgAsACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAXAAiACwAIABcACIASQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADUAOQAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAwAC4AMAAwADcALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGwAbwB3ACAAcgBhAGkAbgBmAGEAbABsACkAXAAiACwAMAAuADAAMAAyADkALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACkAXAAiACwAMAAuADAAMAA4ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdQBnAGEAcgBcACIALAAwAC4AMAAxADkAOQAsACAAXAAiAFMAdQBnAGEAcgBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAMAAuADAAMAA1ADMALAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAwAC4AMAAwADYANAAsACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAIAAoAGMAbwBuAHQAaQBuAHUAbwB1AHMAIABmAGwAbwBvAGQAaQBuAGcAKQBcACIALAAwAC4AMAAwADMALAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAEMAbwBuAHQAaQBuAHUAbwB1AHMAIABmAGwAbwBvAGQAaQBuAGcAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAIAAoAHMAaQBuAGcAbABlACAAYQBuAGQAIABtAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUALAAgAG8AcgAgAGEAbAB0AGUAcgBuAGEAdABlACAAdwBlAHQAdABpAG4AZwAgAGEAbgBkACAAZAByAHkAaQBuAGcAKQBcACIALAAwAC4AMAAwADUALAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAFMAaQBuAGcAbABlACAAYQBuAGQAIABtAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUALAAgAG8AcgAgAGEAbAB0AGUAcgBuAGEAdABlACAAdwBlAHQAdABpAG4AZwAgAGEAbgBkACAAZAByAHkAaQBuAGcAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcACIALAAwAC4AMAAwADIANgAsACAAXAAiAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBvAHIAZQBzAHQAcgB5AFwAIgAsADAALgAwADAAMQA4ACwAIABcACIARgBvAHIAZQBzAHQAcgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBlAG0AbwB2AGUAZAAgAGQAdQBwAGwAaQBjAGEAdABlACAAJwBBAHEAdQBhAGMAdQBsAHQAdQByAGUAJwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAJwBwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5ACcALAAgACcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAnACAAYQBuAGQAIAAnAGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZAAnACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgACcAbgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAJwAgAHIAbwB3ACAAdwBpAHQAaAAgAHMAYQBtAGUAIABFAEYAIABmAG8AcgAgAGwAbwB3ACAAYQBuAGQAIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAFwAbgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABDAGgAYQBwAHQAZQByACAAMQAsACAAcwBlAGMAdABpAG8AbgAgADEALgA4AC4AMgAgAEwAZQBhAGMAaABpAG4AZwAsACAAYwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAbgBJAFAAQwBDADoAIABOADIATwAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAE0AQQBOAEEARwBFAEQAIABTAE8ASQBMAFMALAAgAEEATgBEACAAQwBPADIAIABFAE0ASQBTAFMASQBPAE4AUwAgAEYAUgBPAE0AIABMAEkATQBFACAAQQBOAEQAIABVAFIARQBBACAAQQBQAFAATABJAEMAQQBUAEkATwBOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBXAEUAVAAgAGYAbwByACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFIAZQBmAGkAbgBlAG0AZQBuAHQAIABWAG8AbAB1AG0AZQAgADQAOgAgAEMAaABhAHAAdABlAHIAIAAxADEAOgAgAE4AMgBPACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATQBhAG4AYQBnAGUAZAAgAFMAbwBpAGwAcwAsACAAYQBuAGQAIABDAE8AMgAgAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAEwAaQBtAGUAIABhAG4AZAAgAFUAcgBlAGEAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQAgAGkAcgBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAcAByAGkAbgBrAGwAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AHIAZgBhAGMAZQAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAVABhAGIAbABlACAAYwByAGUAYQB0AGUAZAAgAGIAYQBzAGUAZAAgAG8AbgAgAFYARQBFAFIARwAgAHQAZQB4AHQAIAAnAEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuACcAXAAiACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMgA6ACAARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAbwByACAAcABhAGQAZABvAGMAawAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYAUABSAFAAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAbwByACAAcABhAGQAZABvAGMAawBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYAUABSAFAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAAMgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQwBoAGEAbgBnAGUAZAAgACcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzACcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIAAnAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAJwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAG8AbgB0AGgAcwAgAHQAbwAgAFMAZQBhAHMAbwBuAHMAIABNAGEAcABwAGkAbgBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAG4AdABoAFwAIgAsACAAXAAiAFMAZQBhAHMAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGEAbgB1AGEAcgB5AFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAYgByAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQByAGMAaABcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBwAHIAaQBsAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAeQBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AG4AZQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AGwAeQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AGcAdQBzAHQAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBwAHQAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAGMAdABvAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdgBlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBjAGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAG4AdQByAGUAIABNAGEAbgBhAGcAZQBtAGUAbgB0ACAAEyAgAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AOAAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIAMgAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUACAAKAC6AEMAKQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAFMAbAB1AHIAcgB5ACAAKAB3AGkAdABoAG8AdQB0ACAAbgBhAHQAdQByAGEAbAAgAGMAcgB1AHMAdAApAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkACAAKABiACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAUwB0AG8AcgBhAGcAZQAgADwAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgACcAUABvAHUAbAB0AHIAeQAgAHcAaQB0AGgAIABhAG4AZAAgAHcAaQB0AGgAbwB1AHQAIABsAGkAdAB0AGUAcgAnACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAAcwBlAHAAYQByAGEAdABlACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABBAGQAZABlAGQAIAAnAE0AQQBUACAAcgBhAHcAJwAgAGMAbwBsAHUAbQBuACAAdABvACAAYQBsAGwAbwB3ACAAbABvAG8AawB1AHAAIABvAGYAIABuAHUAbQBiAGUAcgBzAC4AXAAiACkAOwBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgA8AHQAPgA8AHMAPgBcACIAIAAmAFwAbgAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAUwBVAEIAUwBUAEkAVABVAFQARQAoAEMAZQBsAGwALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQAsAFwAIgBcACIAKQAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQBsAGkAbQBpAHQAZQByACwAXAAiADwALwBzAD4APABzAD4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgACYAXABuACAAIAAgACAAIAAgACAAIABcACIAPAAvAHMAPgA8AC8AdAA+AFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC8ALwBzAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQB2AGcAVABlAG0AcAAsAGEAdgBnAFIAYQBpAG4ALABmAHIAbwBzAHQARABhAHkAcwAsAGUAbABlAHYALABtAGEAcABfAHAAZQB0ACwAXABuACAAIAAgACAAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkALABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQAsAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBQAEUAVABBAHIAcgBhAHkALABtAGEAeABQAEUAVABBAHIAcgBhAHkALABcAG4AIAAgACAAIABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkAKQA8AD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPAA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAPAA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAD4APQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApADwAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAPgA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQA8AD0AbQBhAHAAXwBwAGUAdAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFAARQBUAEEAcgByAGEAeQApAD4APQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQA8AD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAPgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAEkAdABlAG0AQQByAHIAYQB5ACwAIABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAHIAaQB0AGUAcgBpAGEAMQAsACAAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFEAdQBhAG4AdABpAHQAeQAsACAAWwBNAHUAbAB0AGkAcABsAGkAZQByAF0ALAAgAFsAQwByAGkAdABlAHIAaQBhADIAXQAsAFsAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AF0ALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAbQB1AGwAdABpAHAAbABpAGUAcgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABNAHUAbAB0AGkAcABsAGkAZQByACkALAAxACwATQB1AGwAdABpAHAAbABpAGUAcgApACwAXABuACAAIAAgACAAcQB1AGEAbgB0AGkAdAB5ACwAIABRAHUAYQBuAHQAaQB0AHkAKgBNAHUAbAB0AGkAcABsAGkAZQByACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAxACkALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMgAsAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwByAGkAdABlAHIAaQBhADIAKQAsADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMgApACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAYwByAGkAdABlAHIAaQBhADEAKgBjAHIAaQB0AGUAcgBpAGEAMgAqAHEAdQBhAG4AdABpAHQAeQApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAPAAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQA+ACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgAnAHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAbgBlAHgAdAAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQA8AFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuACcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAPgBFACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4ALABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQByAHMALABTAEUAUQBVAEUATgBDAEUAKABuACwAMQAsAGYAaQByAHMAdABZAGUAYQByACwAMQApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwAsAEQAQQBUAEUAKAB5AHIAcwAsAG0ALABkACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMALABNAEEAUAAoAHMAdABhAHIAdABzACwAUABlAHIAaQBvAGQARQBuAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABhAGcALABJAEYAKABzAHQAYQByAHQAcwA9AFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcACIAIAAoAFQAaABpAHMAIAByAGUAcABvAHIAdABpAG4AZwAgAGMAeQBjAGwAZQApAFwAIgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMAVABlAHgAdAAsAFQARQBYAFQAKABzAHQAYQByAHQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMAVABlAHgAdAAsAFQARQBYAFQAKABlAG4AZABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAbgA9ADAALABcACIAXAAiACwASABTAFQAQQBDAEsAKABzAHQAYQByAHQAcwBUAGUAeAB0ACAAJgAgAFwAIgAgAHQAbwAgAFwAIgAgACYAIABlAG4AZABzAFQAZQB4AHQAIAAmACAAdABhAGcAKQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlAFwAbgA9AEwAQQBNAEIARABBACgARgB1AG4AYwB0AGkAbwBuACwAIABUAEUAWABUAEIARQBGAE8AUgBFACgARgBPAFIATQBVAEwAQQBUAEUAWABUACgARgB1AG4AYwB0AGkAbwBuACkALAAgAFwAIgAoAFwAIgApACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQAsAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAD0AXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAIAA9ACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkAPQBQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQA9AEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQA9AFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAgACsAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQAPgAwACwAIAAxACwAIAAwACkAXABuACAAIAAgACAAKQApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsAXABuAD0ATABBAE0AQgBEAEEAKABUAGEAcgBnAGUAdABDAGUAbABsACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAHMAaAAsACAAVABFAFgAVABBAEYAVABFAFIAKABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsACAAXAAiAF0AXAAiACkALABcAG4AIAAgACAAIABhAGQAZAByACwAIABDAEUATABMACgAXAAiAGEAZABkAHIAZQBzAHMAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALABcAG4AIAAgACAAIABcACIAIwAnAFwAIgAgACYAIABzAGgAIAAmACAAXAAiACcAIQBcACIAIAAmACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMQBfADIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAxACwAIAAyACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMwBfADQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAzACwAIAA0ACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAE0ATQBTACwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABcAG4AIAAgACAAIAAgACAAIAAgAE0ARQBEAEkAQQBOACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0ASQBOACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBBAFgAKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATQBNAFMALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBcAG4AVABhAGIAbABlACAAQQAuADEALgA1AC4AMQA6ACAATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAARQBuAHQAZQByAGkAYwAgAGYAZQByAG0AZQBuAHQAYQB0AGkAbwBuACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGUAYQBjAGgAIABvAHQAaABlAHIAIABsAGkAdgBlAHMAdABvAGMAawAgAHQAeQBwAGUAIAAoAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAHkAZQBhAHIAKQAgACgATQBqACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawAgAC0AIABFAG4AdABlAHIAaQBjACAAZgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZQBhAGMAaAAgAG8AdABoAGUAcgAgAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGoAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAEMASAA0ACAALwAgAGgAZQBhAGQAIAAvACAAeQBlAGEAcgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuADEAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADIALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIABUAHkAcABlAFwAIgAsACAAXAAiAE0AagBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgB1AGYAZgBhAGwAbwBcACIALAAgADYAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAG8AYQB0AHMAXAAiACwAIAA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBlAHIAXAAiACwAIAAyADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBhAG0AZQBsAHMAXAAiACwAIAA0ADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBsAHAAYQBjAGEAcwBcACIALAAgADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABvAHIAcwBlAHMAXAAiACwAIAAxADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQB1AGwAZQBzAC8AYQBzAHMAZQBzAFwAIgAsACAAMQAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAbQB1AHMALwBvAHMAdAByAGkAYwBoAGUAcwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBvAGQAdQBjAGUAZABcAG4AVABhAGIAbABlACAAQQAuADEALgA1AC4AMgA6ACAATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAAVgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIABwAHIAbwBkAHUAYwBlAGQAIABiAHkAIABlAGEAYwBoACAAbwB0AGgAZQByACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlACAAKABrAGcAIABWAFMALwBoAGUAYQBkAC8AZABhAHkAKQAgACgAVgBTAGoAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBvAGQAdQBjAGUAZABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAAVgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIABwAHIAbwBkAHUAYwBlAGQAIABiAHkAIABlAGEAYwBoACAAbwB0AGgAZQByACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBvAGQAdQBjAGUAZABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBTAGoAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAG8AZAB1AGMAZQBkAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAAVgBTACAALwAgAGgAZQBhAGQAIAAvACAAZABhAHkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAG8AZAB1AGMAZQBkAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuADIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAG8AZAB1AGMAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBvAGQAdQBjAGUAZABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAyACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAAVAB5AHAAZQBcACIALAAgAFwAIgBWAFMAagBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgB1AGYAZgBhAGwAbwBcACIALAAgADIALgA3ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBvAGEAdABzAFwAIgAsACAAMAAuADMANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGUAZQByAFwAIgAsACAAMAAuADkAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAbQBlAGwAcwBcACIALAAgADIALgA3ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBsAHAAYQBjAGEAcwBcACIALAAgADAALgAzADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABvAHIAcwBlAHMAXAAiACwAIAAyAC4ANwAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AdQBsAGUAcwAvAGEAcwBzAGUAcwBcACIALAAgADAALgA5ADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAHUAcwAvAG8AcwB0AHIAaQBjAGgAZQBzAFwAIgAsACAAMAAuADMANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADUALgAzADoAIABPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawAgAC0AIABOAGkAdAByAG8AZwBlAG4AIABlAHgAYwByAGUAdABlAGQAIABwAGUAcgAgAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQAgACgAawBnACAATgAyAE8ALwBoAGUAYQBkAC8AeQBlAGEAcgApACAAKABOAEUAagApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawAgAC0AIABOAGkAdAByAG8AZwBlAG4AIABlAHgAYwByAGUAdABlAGQAIABwAGUAcgAgAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4ARQBqAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALwAgAGgAZQBhAGQAIAAvACAAeQBlAGEAcgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA1AC4AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADIALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIABUAHkAcABlAFwAIgAsACAAXAAiAE4ARQBqAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAHUAZgBmAGEAbABvAFwAIgAsACAAMwA5AC4ANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAG8AYQB0AHMAXAAiACwAIAA3AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGUAZQByAFwAIgAsACAAMQAzAC4AMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAbQBlAGwAcwBcACIALAAgADMAOQAuADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBsAHAAYQBjAGEAcwBcACIALAAgADcALgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHMAZQBzAFwAIgAsACAAMwA5AC4ANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAHUAbABlAHMALwBhAHMAcwBlAHMAXAAiACwAIAAxADMALgAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAbQB1AHMALwBvAHMAdAByAGkAYwBoAGUAcwBcACIALAAgADcALgAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABcAG4AVABhAGIAbABlACAAQQAuADEALgA1AC4ANAA6ACAATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAAQQB2AGUAcgBhAGcAZQAgAEwAaQB2AGUAdwBlAGkAZwBoAHQAcwAgACgAVwBjAG8AKQAgACgAawBnACkAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawAgAC0AIABBAHYAZQByAGEAZwBlACAATABpAHYAZQB3AGUAaQBnAGgAdABzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBXAGMAbwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADUALgA0AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMwAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawAgAFQAeQBwAGUAIABqAFwAIgAsACAAXAAiAEEAdgBlAHIAYQBnAGUAIABMAGkAdgBlAHcAZQBpAGcAaAB0AFwAIgAsACAAXAAiAEEAdgBlAHIAYQBnAGUAIABMAGkAdgBlAHcAZQBpAGcAaAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAHUAZgBmAGEAbABvAFwAIgAsACAAMwAzADYALAAgAFwAIgAtAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAG8AYQB0AHMAXAAiACwAIAAzADMALAAgAFwAIgAyADgAawBnACAALQAgAGwAbwB3ACAAcAByAG8AZAB1AGMAdABpAHYAaQB0AHkAIABzAHkAcwB0AGUAbQBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAG8AYQB0AHMAXAAiACwAIAAzADMALAAgAFwAIgA1ADAAawBnACAALQAgAGgAaQBnAGgAIABwAHIAbwBkAHUAYwB0AGkAdgBpAHQAeQAgAHMAeQBzAHQAZQBtAHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBlAHIAXAAiACwAIAAxADIAMAAsACAAMQAyADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBhAG0AZQBsAHMAXAAiACwAIAAyADEANwAsACAANQA3ADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBsAHAAYQBjAGEAcwBcACIALAAgAFwAIgAtAFwAIgAsACAANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHMAZQBzAFwAIgAsACAAMwA3ADcALAAgADUANQAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AdQBsAGUAcwAvAGEAcwBzAGUAcwBcACIALAAgADEAMwAwACwAIAAyADQANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AdQBzAC8AbwBzAHQAcgBpAGMAaABlAHMAXAAiACwAIAAxADIAMAAsACAAMQAyADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBlAGYAZQByAGUAbgBjAGUAXAAiACwAIABcACIASQBQAEMAQwAgADIAMAAxADkAIABUAGEAYgBsAGUAIAAxADAAQQAuADUAIABbADIAXQBcACIALAAgAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFQAYQBiAGwAZQAgADEAMAAuADEAMAAgAFsAMgBdAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAHQAaQBvAG4AVwBhAHMAdABlAEkAbgBNAE0AUwBcAG4AVABhAGIAbABlACAAQQAuADEALgA1AC4ANQA6ACAATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAARgByAGEAYwB0AGkAbwBuACAAbwBmACAAdwBhAHMAdABlACAAaQBuACAAZQBhAGMAaAAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdAAgAHMAeQBzAHQAZQBtACAAKABmAHIAYQBjAHQAaQBvAG4AKQAgACgATQBNAFMAbQApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAHQAaQBvAG4AVwBhAHMAdABlAEkAbgBNAE0AUwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAARgByAGEAYwB0AGkAbwBuACAAbwBmACAAdwBhAHMAdABlACAAaQBuACAAZQBhAGMAaAAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdAAgAHMAeQBzAHQAZQBtAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwB0AGkAbwBuAFcAYQBzAHQAZQBJAG4ATQBNAFMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATQBTAG0AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAHQAaQBvAG4AVwBhAHMAdABlAEkAbgBNAE0AUwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMAdABpAG8AbgBXAGEAcwB0AGUASQBuAE0ATQBTAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuADUAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAHQAaQBvAG4AVwBhAHMAdABlAEkAbgBNAE0AUwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMAdABpAG8AbgBXAGEAcwB0AGUASQBuAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXAAiACwAIABcACIAVQBuAGMAbwB2AGUAcgBlAGQAIABBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAEMAVABcACIALAAgACAAOQA5AC4ANgA2ACwAIAAgADAALgAzADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBTAFcAXAAiACwAIAAgADkAOQAuADYANgAsACAAIAAwAC4AMwA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AVABcACIALAAgACAAOQA5AC4ANgA2ACwAIAAgADAALgAzADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBMAEQAXAAiACwAIAAgADkAOQAuADYANgAsACAAIAAwAC4AMwA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAQQBcACIALAAgACAAOQA5AC4ANgA2ACwAIAAgADAALgAzADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABBAFMAXAAiACwAIAAgADkAOQAuADYANgAsACAAIAAwAC4AMwA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYASQBDAFwAIgAsACAAIAA5ADkALgA2ADYALAAgACAAMAAuADMANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAEEAXAAiACwAIAAgADkAOQAuADYANgAsACAAIAAwAC4AMwA0AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBcAG4AVABhAGIAbABlACAAQQAuADEALgA1AC4ANgA6ACAATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAcgBlAGcAaQBvAG4AIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawAgAC0AIABNAGUAdABoAGEAbgBlACAAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAcABlAHIAIAByAGUAZwBpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBDAEYAaQBtAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuADYAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMwAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAQwBUAFwAIgAsACAAIAAwAC4AMAAwADQANwAsACAAIAAwAC4ANwAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AUwBXAFwAIgAsACAAIAAwAC4AMAAwADQANwAsACAAIAAwAC4ANwA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AVABcACIALAAgACAAMAAuADAAMAA0ADcALAAgACAAMAAuADgAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAEwARABcACIALAAgACAAMAAuADAAMAA0ADcALAAgACAAMAAuADcAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEEAXAAiACwAIAAgADAALgAwADAANAA3ACwAIAAgADAALgA3ADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABBAFMAXAAiACwAIAAgADAALgAwADAANAA3ACwAIAAgADAALgA3ADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBJAEMAXAAiACwAIAAgADAALgAwADAANAA3ACwAIAAgADAALgA3ADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBBAFwAIgAsACAAIAAwAC4AMAAwADQANwAsACAAIAAwAC4ANwA2AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAzAC4ANgA6ACAARQBuAHQAZQByAGkAYwAgAE0AZQB0AGgAYQBuAGUAIAAtACAATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADMALgA2AC4AMQAuADEAIABNAGUAdABoAG8AZAAgADEAIAAtACAARQBuAHQAZQByAGkAYwAgAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMwBfADYAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXABuAFQAbwB0AGEAbAAgAGEAbgBuAHUAYQBsACAAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAZQBuAHQAZQByAGkAYwAgAGYAZQByAG0AZQBuAHQAYQB0AGkAbwBuACAAaQBuACAAbwB0AGgAZQByACAAbABpAHYAZQBzAHQAbwBjAGsAXABuAEUAXwBlAG4AdABlAHIAaQBjAFwAbgB0ACAAQwBIADQAXABuAEUAXwB7AGUAbgB0AGUAcgBpAGMAfQA9AFwAXABzAHUAbQBfAGoAKABOAF8AagBcAFwAdABpAG0AZQBzACAATQBfAGoAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcAG4ATgBfAGoAIAA9ACAAbgB1AG0AYgBlAHIAIABvAGYAIABsAGkAdgBlAHMAdABvAGMAawAgAG8AZgAgAGUAYQBjAGgAIABsAGkAdgBlAHMAdABvAGMAawAgAHQAeQBwAGUAIABqACAAKABoAGUAYQBkACkAXABuAE0AXwBqACAAPQAgAGUAbgB0AGUAcgBpAGMAIABmAGUAcgBtAGUAbgB0AGEAdABpAG8AbgAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAKABrAGcAIABDAEgANAAvAGgAZQBhAGQALwB5AGUAYQByACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADYAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATgBfAGoALAAgAE0AXwBqACwAXABuACAAIAAgACAAUwBVAE0AKABOAF8AagAgACoAIABNAF8AagApACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8ANgBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABvAHQAYQBsACAAYQBuAG4AdQBhAGwAIABtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABlAG4AdABlAHIAaQBjACAAZgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AIABpAG4AIABvAHQAaABlAHIAIABsAGkAdgBlAHMAdABvAGMAawBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADYAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBlAG4AdABlAHIAaQBjAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8ANgBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAEgANABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADYAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMwAuADYALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwA2AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8ANgBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AGUAbgB0AGUAcgBpAGMAfQA9AFwAXABzAHUAbQBfAGoAKABOAF8AagBcAFwAdABpAG0AZQBzACAATQBfAGoAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADYAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBfAGoAXAAiACwAIABcACIAbgB1AG0AYgBlAHIAIABvAGYAIABsAGkAdgBlAHMAdABvAGMAawAgAG8AZgAgAGUAYQBjAGgAIABsAGkAdgBlAHMAdABvAGMAawAgAHQAeQBwAGUAIABqAFwAIgAsACAAXAAiAGgAZQBhAGQAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAF8AagBcACIALAAgAFwAIgBlAG4AdABlAHIAaQBjACAAZgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBcACIALAAgAFwAIgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwB5AGUAYQByAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAagBcACIALAAgAFwAIgBsAGkAdgBlAHMAdABvAGMAawAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgAiAH0AXQAsACIAcAByAG8AagBlAGMAdABOAGEAbQBlAHMAIgA6AFsAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADEAXwAyACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAG8AZAB1AGMAZQBkAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBvAGQAdQBjAGUAZABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAbwBkAHUAYwBlAGQAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBvAGQAdQBjAGUAZABfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBvAGQAdQBjAGUAZABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBvAGQAdQBjAGUAZABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAHQAaQBvAG4AVwBhAHMAdABlAEkAbgBNAE0AUwBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMAdABpAG8AbgBXAGEAcwB0AGUASQBuAE0ATQBTAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwB0AGkAbwBuAFcAYQBzAHQAZQBJAG4ATQBNAFMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwB0AGkAbwBuAFcAYQBzAHQAZQBJAG4ATQBNAFMAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMAdABpAG8AbgBXAGEAcwB0AGUASQBuAE0ATQBTAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAHQAaQBvAG4AVwBhAHMAdABlAEkAbgBNAE0AUwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAEQAYQB0AGEAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8ANgBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwA2AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVABpAHQAbABlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADYAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8ANgBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFUAbgBpAHQAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8ANgBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADYAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwA2AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwA2AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AQQByAGcAdQBtAGUAbgB0AHMAIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -20302,7 +20402,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -20311,7 +20411,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
@@ -20322,15 +20422,11 @@
 </p:properties>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACkAKgAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADIAKQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAHQAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAC8AdABcAHUAMAAwADMAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAdQAwADAAMgA3AFwAIgAgAFwAdQAwADAAMgA2ACAAcwBoACAAXAB1ADAAMAAyADYAIABcACIAXAB1ADAAMAAyADcAIQBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgAFwAdQAwADAAMgA2ACAAXAAiACAAXAAiACAAXAB1ADAAMAAyADYAIABUAGkAdABsAGUAQwBlAGwAbABcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAiACwAIgB0AGUAeAB0ACIAOgAiAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuADEAOgAgAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAALQAgAEUAbgB0AGUAcgBpAGMAIABmAGUAcgBtAGUAbgB0AGEAdABpAG8AbgAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABlAGEAYwBoACAAbwB0AGgAZQByACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlACAAKABrAGcAIABDAEgANAAvAGgAZQBhAGQALwB5AGUAYQByACkAIAAoAE0AagApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAARQBuAHQAZQByAGkAYwAgAGYAZQByAG0AZQBuAHQAYQB0AGkAbwBuACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGUAYQBjAGgAIABvAHQAaABlAHIAIABsAGkAdgBlAHMAdABvAGMAawAgAHQAeQBwAGUAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBqAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABDAEgANAAgAC8AIABoAGUAYQBkACAALwAgAHkAZQBhAHIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADUALgAxAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAyACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAAVAB5AHAAZQBcACIALAAgAFwAIgBNAGoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBmAGYAYQBsAG8AXAAiACwAIAA2ADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBvAGEAdABzAFwAIgAsACAANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGUAZQByAFwAIgAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAYQBtAGUAbABzAFwAIgAsACAANAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbABwAGEAYwBhAHMAXAAiACwAIAA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHMAZQBzAFwAIgAsACAAMQA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AdQBsAGUAcwAvAGEAcwBzAGUAcwBcACIALAAgADEAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AdQBzAC8AbwBzAHQAcgBpAGMAaABlAHMAXAAiACwAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAbwBkAHUAYwBlAGQAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuADIAOgAgAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAALQAgAFYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAcAByAG8AZAB1AGMAZQBkACAAYgB5ACAAZQBhAGMAaAAgAG8AdABoAGUAcgAgAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQAgACgAawBnACAAVgBTAC8AaABlAGEAZAAvAGQAYQB5ACkAIAAoAFYAUwBqACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAbwBkAHUAYwBlAGQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAALQAgAFYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAcAByAG8AZAB1AGMAZQBkACAAYgB5ACAAZQBhAGMAaAAgAG8AdABoAGUAcgAgAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAbwBkAHUAYwBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAUwBqAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBvAGQAdQBjAGUAZABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAFYAUwAgAC8AIABoAGUAYQBkACAALwAgAGQAYQB5AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBvAGQAdQBjAGUAZABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADUALgAyAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBvAGQAdQBjAGUAZABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAbwBkAHUAYwBlAGQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMgAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawAgAFQAeQBwAGUAXAAiACwAIABcACIAVgBTAGoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBmAGYAYQBsAG8AXAAiACwAIAAyAC4ANwAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAbwBhAHQAcwBcACIALAAgADAALgAzADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGUAcgBcACIALAAgADAALgA5ADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBhAG0AZQBsAHMAXAAiACwAIAAyAC4ANwAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbABwAGEAYwBhAHMAXAAiACwAIAAwAC4AMwA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHMAZQBzAFwAIgAsACAAMgAuADcAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAHUAbABlAHMALwBhAHMAcwBlAHMAXAAiACwAIAAwAC4AOQAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAbQB1AHMALwBvAHMAdAByAGkAYwBoAGUAcwBcACIALAAgADAALgAzADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABcAG4AVABhAGIAbABlACAAQQAuADEALgA1AC4AMwA6ACAATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAATgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAZQBkACAAcABlAHIAIABsAGkAdgBlAHMAdABvAGMAawAgAHQAeQBwAGUAIAAoAGsAZwAgAE4AMgBPAC8AaABlAGEAZAAvAHkAZQBhAHIAKQAgACgATgBFAGoAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAATgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAZQBkACAAcABlAHIAIABsAGkAdgBlAHMAdABvAGMAawAgAHQAeQBwAGUAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAEUAagBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC8AIABoAGUAYQBkACAALwAgAHkAZQBhAHIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuADMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAyACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAAVAB5AHAAZQBcACIALAAgAFwAIgBOAEUAagBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgB1AGYAZgBhAGwAbwBcACIALAAgADMAOQAuADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBvAGEAdABzAFwAIgAsACAANwAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGUAcgBcACIALAAgADEAMwAuADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBhAG0AZQBsAHMAXAAiACwAIAAzADkALgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbABwAGEAYwBhAHMAXAAiACwAIAA3AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgBzAGUAcwBcACIALAAgADMAOQAuADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQB1AGwAZQBzAC8AYQBzAHMAZQBzAFwAIgAsACAAMQAzAC4AMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AdQBzAC8AbwBzAHQAcgBpAGMAaABlAHMAXAAiACwAIAA3AC4AMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuADQAOgAgAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAALQAgAEEAdgBlAHIAYQBnAGUAIABMAGkAdgBlAHcAZQBpAGcAaAB0AHMAIAAoAFcAYwBvACkAIAAoAGsAZwApACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAAQQB2AGUAcgBhAGcAZQAgAEwAaQB2AGUAdwBlAGkAZwBoAHQAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVwBjAG8AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA1AC4ANABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADEALAAgADMALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIABUAHkAcABlACAAagBcACIALAAgAFwAIgBBAHYAZQByAGEAZwBlACAATABpAHYAZQB3AGUAaQBnAGgAdABcACIALAAgAFwAIgBBAHYAZQByAGEAZwBlACAATABpAHYAZQB3AGUAaQBnAGgAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgB1AGYAZgBhAGwAbwBcACIALAAgADMAMwA2ACwAIABcACIALQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBvAGEAdABzAFwAIgAsACAAMwAzACwAIABcACIAMgA4AGsAZwAgAC0AIABsAG8AdwAgAHAAcgBvAGQAdQBjAHQAaQB2AGkAdAB5ACAAcwB5AHMAdABlAG0AcwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBvAGEAdABzAFwAIgAsACAAMwAzACwAIABcACIANQAwAGsAZwAgAC0AIABoAGkAZwBoACAAcAByAG8AZAB1AGMAdABpAHYAaQB0AHkAIABzAHkAcwB0AGUAbQBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGUAZQByAFwAIgAsACAAMQAyADAALAAgADEAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAYQBtAGUAbABzAFwAIgAsACAAMgAxADcALAAgADUANwAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbABwAGEAYwBhAHMAXAAiACwAIABcACIALQBcACIALAAgADYANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgBzAGUAcwBcACIALAAgADMANwA3ACwAIAA1ADUAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAHUAbABlAHMALwBhAHMAcwBlAHMAXAAiACwAIAAxADMAMAAsACAAMgA0ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAHUAcwAvAG8AcwB0AHIAaQBjAGgAZQBzAFwAIgAsACAAMQAyADAALAAgADEAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBmAGUAcgBlAG4AYwBlAFwAIgAsACAAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAVABhAGIAbABlACAAMQAwAEEALgA1ACAAWwAyAF0AXAAiACwAIABcACIASQBQAEMAQwAgADIAMAAxADkAIABUAGEAYgBsAGUAIAAxADAALgAxADAAIABbADIAXQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwB0AGkAbwBuAFcAYQBzAHQAZQBJAG4ATQBNAFMAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuADUAOgAgAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAALQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHcAYQBzAHQAZQAgAGkAbgAgAGUAYQBjAGgAIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAIABzAHkAcwB0AGUAbQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0ATQBTAG0AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwB0AGkAbwBuAFcAYQBzAHQAZQBJAG4ATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAALQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHcAYQBzAHQAZQAgAGkAbgAgAGUAYQBjAGgAIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAIABzAHkAcwB0AGUAbQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMAdABpAG8AbgBXAGEAcwB0AGUASQBuAE0ATQBTAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE0AUwBtAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwB0AGkAbwBuAFcAYQBzAHQAZQBJAG4ATQBNAFMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAHQAaQBvAG4AVwBhAHMAdABlAEkAbgBNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADUALgA1AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwB0AGkAbwBuAFcAYQBzAHQAZQBJAG4ATQBNAFMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAHQAaQBvAG4AVwBhAHMAdABlAEkAbgBNAE0AUwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAzACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQBcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBDAFQAXAAiACwAIAAgADkAOQAuADYANgAsACAAIAAwAC4AMwA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AUwBXAFwAIgAsACAAIAA5ADkALgA2ADYALAAgACAAMAAuADMANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFQAXAAiACwAIAAgADkAOQAuADYANgAsACAAIAAwAC4AMwA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEATABEAFwAIgAsACAAIAA5ADkALgA2ADYALAAgACAAMAAuADMANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEEAXAAiACwAIAAgADkAOQAuADYANgAsACAAIAAwAC4AMwA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAQQBTAFwAIgAsACAAIAA5ADkALgA2ADYALAAgACAAMAAuADMANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEkAQwBcACIALAAgACAAOQA5AC4ANgA2ACwAIAAgADAALgAzADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBBAFwAIgAsACAAIAA5ADkALgA2ADYALAAgACAAMAAuADMANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuADYAOgAgAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAALQAgAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAHIAZQBnAGkAbwBuACAAKABmAHIAYQBjAHQAaQBvAG4AKQAgACgATQBDAEYAaQBtACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAcgBlAGcAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AQwBGAGkAbQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADUALgA2AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXAAiACwAIABcACIAVQBuAGMAbwB2AGUAcgBlAGQAIABBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAEMAVABcACIALAAgACAAMAAuADAAMAA0ADcALAAgACAAMAAuADcAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFMAVwBcACIALAAgACAAMAAuADAAMAA0ADcALAAgACAAMAAuADcANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFQAXAAiACwAIAAgADAALgAwADAANAA3ACwAIAAgADAALgA4ADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBMAEQAXAAiACwAIAAgADAALgAwADAANAA3ACwAIAAgADAALgA3ADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBAFwAIgAsACAAIAAwAC4AMAAwADQANwAsACAAIAAwAC4ANwA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAQQBTAFwAIgAsACAAIAAwAC4AMAAwADQANwAsACAAIAAwAC4ANwAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYASQBDAFwAIgAsACAAIAAwAC4AMAAwADQANwAsACAAIAAwAC4ANwA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAQQBcACIALAAgACAAMAAuADAAMAA0ADcALAAgACAAMAAuADcANgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADUALgBYADoAIABPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawAgAC0AIABNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbAAgACgAbQAzACAAQwBIADQAIAAvACAAawBnACAAVgBTACkAIAAoAEIATwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawAgAC0AIABNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEIATwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBtADMAIABDAEgANAAgAC8AIABrAGcAIABWAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuAFgAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgAgAFQAaABlAHIAZQAgAHcAZQByAGUAIABuAG8AIAB2AGEAbAB1AGUAcwAgAGkAbgAgAFYARQBFAFIARwAgAHMAbwAgAHQAaABpAHMAIABkAGEAdABhACAAaABhAHMAIABiAGUAZQBuACAAZwBlAG4AZQByAGEAdABlAGQAIABiAHkAIAB1AHMAaQBuAGcAIABkAG8AYwB1AG0AZQBuAHQAZQBkACAAQgBPACAAdgBhAGwAdQBlAHMAIABmAHIAbwBtACAAbwB0AGgAZQByACAAbABpAHYAZQBzAHQAbwBjAGsAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIABUAHkAcABlAFwAIgAsACAAXAAiAEIATwBcACIALAAgAFwAIgBUAGEAawBlAG4AIABmAHIAbwBtAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAHUAZgBmAGEAbABvAFwAIgAsACAAMAAuADEAOQAsACAAXAAiAEYAZQBlAGQAbABvAHQALAAgAFAAYQBzAHQAdQByAGUAIABiAGUAZQBmAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAG8AYQB0AHMAXAAiACwAIAAwAC4AMgA0ACwAIABcACIAUwBoAGUAZQBwAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGUAZQByAFwAIgAsACAAMAAuADIANAAsACAAXAAiAFMAaABlAGUAcABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBhAG0AZQBsAHMAXAAiACwAIAAwAC4AMgA0ACwAIABcACIAUwBoAGUAZQBwAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGwAcABhAGMAYQBzAFwAIgAsACAAMAAuADIANAAsACAAXAAiAFMAaABlAGUAcABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABvAHIAcwBlAHMAXAAiACwAIAAwAC4AMQA5ACwAIABcACIARgBlAGUAZABsAG8AdAAsACAAUABhAHMAdAB1AHIAZQAgAGIAZQBlAGYAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AdQBsAGUAcwAvAGEAcwBzAGUAcwBcACIALAAgADAALgAyADQALAAgAFwAIgBTAGgAZQBlAHAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAbQB1AHMALwBvAHMAdAByAGkAYwBoAGUAcwBcACIALAAgADAALgAzADYALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAALQAgAG0AZQBhAHQAIABjAGgAaQBjAGsAZQBuAHMAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMARwBBAFMATQBTAG8AaQBsAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABmAHIAbwBtACAAdQByAGkAbgBlACAAYQBuAGQAIABmAGEAZQBjAGUAcwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGYAcgBvAG0AIAB1AHIAaQBuAGUAIABhAG4AZAAgAGYAYQBlAGMAZQBzACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMARwBBAFMATQBzAG8AaQBsAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4ASAAzAC0ATgAgACsAIABOAE8AeAAtAE4AKQAvAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4ANwAuADIALgAzACAAQwBPAE4AUwBUAEEATgBUAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMARwBBAFMATQBTAG8AaQBsAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4AMgAxACkAOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADMALgA2ADoAIABFAG4AdABlAHIAaQBjACAATQBlAHQAaABhAG4AZQAgAC0AIABPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMwAuADYALgAxAC4AMQAgAE0AZQB0AGgAbwBkACAAMQAgAC0AIABFAG4AdABlAHIAaQBjACAATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAzAF8ANgBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBcAG4AVABvAHQAYQBsACAAYQBuAG4AdQBhAGwAIABtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABlAG4AdABlAHIAaQBjACAAZgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AIABpAG4AIABvAHQAaABlAHIAIABsAGkAdgBlAHMAdABvAGMAawBcAG4ARQBfAGUAbgB0AGUAcgBpAGMAXABuAHQAIABDAEgANABcAG4ARQBfAHsAZQBuAHQAZQByAGkAYwB9AD0AXABcAHMAdQBtAF8AagAoAE4AXwBqAFwAXAB0AGkAbQBlAHMAIABNAF8AagApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBOAF8AagAgAD0AIABuAHUAbQBiAGUAcgAgAG8AZgAgAGwAaQB2AGUAcwB0AG8AYwBrACAAbwBmACAAZQBhAGMAaAAgAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQAgAGoAIAAoAGgAZQBhAGQAKQBcAG4ATQBfAGoAIAA9ACAAZQBuAHQAZQByAGkAYwAgAGYAZQByAG0AZQBuAHQAYQB0AGkAbwBuACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIAAoAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAHkAZQBhAHIAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAzAF8ANgBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABOAF8AagAsACAATQBfAGoALABcAG4AIAAgACAAIABTAFUATQAoAE4AXwBqACAAKgAgAE0AXwBqACkAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwA2AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBUAG8AdABhAGwAIABhAG4AbgB1AGEAbAAgAG0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAGUAbgB0AGUAcgBpAGMAIABmAGUAcgBtAGUAbgB0AGEAdABpAG8AbgAgAGkAbgAgAG8AdABoAGUAcgAgAGwAaQB2AGUAcwB0AG8AYwBrAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8ANgBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAGUAbgB0AGUAcgBpAGMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwA2AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMASAA0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8ANgBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAzAC4ANgAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADYAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwA2AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsAZQBuAHQAZQByAGkAYwB9AD0AXABcAHMAdQBtAF8AagAoAE4AXwBqAFwAXAB0AGkAbQBlAHMAIABNAF8AagApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8ANgBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAF8AagBcACIALAAgAFwAIgBuAHUAbQBiAGUAcgAgAG8AZgAgAGwAaQB2AGUAcwB0AG8AYwBrACAAbwBmACAAZQBhAGMAaAAgAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQAgAGoAXAAiACwAIABcACIAaABlAGEAZABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AXwBqAFwAIgAsACAAXAAiAGUAbgB0AGUAcgBpAGMAIABmAGUAcgBtAGUAbgB0AGEAdABpAG8AbgAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAHkAZQBhAHIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBqAFwAIgAsACAAXAAiAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMQBfADIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADMAXwA0ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAbwBkAHUAYwBlAGQAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAG8AZAB1AGMAZQBkAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBvAGQAdQBjAGUAZABfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAG8AZAB1AGMAZQBkAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAG8AZAB1AGMAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAG8AZAB1AGMAZQBkAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMAdABpAG8AbgBXAGEAcwB0AGUASQBuAE0ATQBTAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwB0AGkAbwBuAFcAYQBzAHQAZQBJAG4ATQBNAFMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAHQAaQBvAG4AVwBhAHMAdABlAEkAbgBNAE0AUwBfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAHQAaQBvAG4AVwBhAHMAdABlAEkAbgBNAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwB0AGkAbwBuAFcAYQBzAHQAZQBJAG4ATQBNAFMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMAdABpAG8AbgBXAGEAcwB0AGUASQBuAE0ATQBTAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8ARABhAHQAYQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwA2AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADYAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8ANgBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwA2AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVQBuAGkAdAAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwA2AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8ANgBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADYAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADYAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBBAHIAZwB1AG0AZQBuAHQAcwAiAF0ALAAiAGwAbwBjAGEAbABlACIAOgB7ACIAbABpAHMAdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHIAbwB3AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAYwBvAGwAdQBtAG4AUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFAAbwBzAGkAdABpAG8AbgBzACIAOgBbADMAXQAsACIAZABlAGMAaQBtAGEAbABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAuACIALAAiAGQAYQB0AGUATwByAGQAZQByACIAOgAiAEQATQBZACIALAAiAGMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbAAiADoAIgAkACIALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwATABlAGEAZAAiADoAdAByAHUAZQAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAGUAcABCAHkAUwBwAGEAYwBlACIAOgBmAGEAbABzAGUALAAiAHIAbwB3AEwAZQB0AHQAZQByACIAOgAiAFIAIgAsACIAYwBvAGwAdQBtAG4ATABlAHQAdABlAHIAIgA6ACIAQwAiACwAIgByAGMATABlAGYAdABCAHIAYQBjAGsAZQB0ACIAOgAiAFsAIgAsACIAcgBjAFIAaQBnAGgAdABCAHIAYQBjAGsAZQB0ACIAOgAiAF0AIgAsACIAcwB0AGEAdABlAG0AZQBuAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBsAG8AYwBhAGwAZQBOAGEAbQBlACIAOgAiAGUAbgAtAHUAcwAiAH0AfQA=</AFEJSONBlob>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809E3D44-A88D-4EBF-A307-6B8CE77A3361}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -20349,7 +20445,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -20357,7 +20453,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -20366,4 +20462,12 @@
     <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Excel/3_6_Enteric_OtherLivestock_WIP_v01.xlsx
+++ b/Excel/3_6_Enteric_OtherLivestock_WIP_v01.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07A1365E-8315-46F7-9F41-915D2185C9A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{975F5477-615C-4E31-A68B-C5D43F400110}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5070" yWindow="5070" windowWidth="28800" windowHeight="15345" firstSheet="7" activeTab="7" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="1650" yWindow="1410" windowWidth="36255" windowHeight="19140" firstSheet="1" activeTab="5" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -24,10 +24,6 @@
     <sheet name="Acknowledgements" sheetId="72" r:id="rId9"/>
     <sheet name="Tab template" sheetId="74" r:id="rId10"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId11"/>
-    <externalReference r:id="rId12"/>
-  </externalReferences>
   <definedNames>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e">_xlfn.LAMBDA(_xlpm.E_CH4,_xlpm.GWP_CH4, _xlpm.E_CH4 * _xlpm.GWP_CH4)</definedName>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"ECH4","Methane emissions (t CH4)";"GWPCH4","Global warming potential for methane (t CO2-e / t CH4)"}, _xlpm.r, _xlpm.c))))</definedName>
@@ -272,6 +268,18 @@
     <definedName name="Step1">#REF!</definedName>
     <definedName name="Step2">#REF!</definedName>
     <definedName name="Step3">#REF!</definedName>
+    <definedName name="X_Cell_OtherLivestock_Others_Alpacas_Head">'Input - Other Livestock'!$F$26</definedName>
+    <definedName name="X_Cell_OtherLivestock_Others_Camels_Head">'Input - Other Livestock'!$E$26</definedName>
+    <definedName name="X_Cell_OtherLivestock_Others_Emus_Head">'Input - Other Livestock'!$I$26</definedName>
+    <definedName name="X_Cell_OtherLivestock_Others_Horses_Head">'Input - Other Livestock'!$G$26</definedName>
+    <definedName name="X_Cell_OtherLivestock_Others_Mules_Head">'Input - Other Livestock'!$H$26</definedName>
+    <definedName name="X_Cell_Site_EndDate">'Input - Site'!$E$13</definedName>
+    <definedName name="X_Cell_Site_FarmName">'Input - Site'!$E$7</definedName>
+    <definedName name="X_Cell_Site_ReportingEntityName">'Input - Site'!$E$8</definedName>
+    <definedName name="X_Cell_Site_StartDate">'Input - Site'!$E$12</definedName>
+    <definedName name="X_Table_OtherLivestock_Buffalo_Head">'Input - Other Livestock'!$D$7:$H$8</definedName>
+    <definedName name="X_Table_OtherLivestock_Deer_Head">'Input - Other Livestock'!$D$19:$H$20</definedName>
+    <definedName name="X_Table_OtherLivestock_Goats_Head">'Input - Other Livestock'!$D$13:$J$14</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -4863,62 +4871,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Home"/>
-      <sheetName val="Overview"/>
-      <sheetName val="Results"/>
-      <sheetName val="Input - Site"/>
-      <sheetName val="Input - Feedlot"/>
-      <sheetName val="4.6.1.1-2 Manure Methane"/>
-      <sheetName val="Constants - Other Livestock"/>
-      <sheetName val="Constants - Common"/>
-      <sheetName val="Constants - Livestock"/>
-      <sheetName val="Acknowledgements"/>
-      <sheetName val="4_7_ManureManagement_OtherLives"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Home"/>
-      <sheetName val="Constants - Common"/>
-      <sheetName val="Acknowledgements"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
 <rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
   <global>
@@ -4993,7 +4945,7 @@
     <tableColumn id="1" xr3:uid="{D57CB9BE-4423-4B3C-8812-0053460E9FD4}" name="Other livestock type">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_EntericFermentationEmissionFactor_Data(),Table_SourceData_OtherLivestock_EntericEF[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{076CA99E-B6FF-4452-AA90-21B8618FF161}" name="Mj" dataDxfId="54" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{076CA99E-B6FF-4452-AA90-21B8618FF161}" name="Mj" dataDxfId="18" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_EntericFermentationEmissionFactor_Data(),Table_SourceData_OtherLivestock_EntericEF[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5055,49 +5007,49 @@
     <tableColumn id="1" xr3:uid="{C1368F08-D067-4EEC-B0CC-D2E1F6D93274}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{773305BF-D908-4C35-A934-C13BC9D3D8FF}" name="MAT" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{773305BF-D908-4C35-A934-C13BC9D3D8FF}" name="MAT" totalsRowDxfId="54" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{DF05DA85-723A-420A-AA03-0A716BECCE22}" name="MAP" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
+    <tableColumn id="3" xr3:uid="{DF05DA85-723A-420A-AA03-0A716BECCE22}" name="MAP" totalsRowDxfId="53" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{8B8F9D2B-3A8F-44F1-9417-280165AE86AB}" name="Frost days per year" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
+    <tableColumn id="4" xr3:uid="{8B8F9D2B-3A8F-44F1-9417-280165AE86AB}" name="Frost days per year" totalsRowDxfId="52" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{31B1CBF8-C757-4A17-AD4E-3FED04A08D97}" name="Elevation" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
+    <tableColumn id="5" xr3:uid="{31B1CBF8-C757-4A17-AD4E-3FED04A08D97}" name="Elevation" totalsRowDxfId="51" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{9F5D51C1-ECC4-49B6-A4BE-AE3B3C663E64}" name="MAP:PET" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
+    <tableColumn id="6" xr3:uid="{9F5D51C1-ECC4-49B6-A4BE-AE3B3C663E64}" name="MAP:PET" totalsRowDxfId="50" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{874F3D25-0748-4359-BEF3-58E34D4DFAA6}" name="Min temp" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
+    <tableColumn id="7" xr3:uid="{874F3D25-0748-4359-BEF3-58E34D4DFAA6}" name="Min temp" totalsRowDxfId="49" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{79652299-3198-47E6-B342-A54F0A0B3674}" name="Max temp" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
+    <tableColumn id="8" xr3:uid="{79652299-3198-47E6-B342-A54F0A0B3674}" name="Max temp" totalsRowDxfId="48" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{A0139A89-1186-4484-B833-03C424C4D2C4}" name="Min rainfall" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
+    <tableColumn id="9" xr3:uid="{A0139A89-1186-4484-B833-03C424C4D2C4}" name="Min rainfall" totalsRowDxfId="47" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{BD7A797C-3EEA-481F-9533-984ECCA62AC3}" name="Max rainfall" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
+    <tableColumn id="10" xr3:uid="{BD7A797C-3EEA-481F-9533-984ECCA62AC3}" name="Max rainfall" totalsRowDxfId="46" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{29123C0E-9E60-43AB-8679-2AC0908200D0}" name="Min frost days" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
+    <tableColumn id="11" xr3:uid="{29123C0E-9E60-43AB-8679-2AC0908200D0}" name="Min frost days" totalsRowDxfId="45" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{04AF6D35-FBEF-4E38-B28D-0C23F8EDC5F6}" name="Max frost days" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
+    <tableColumn id="15" xr3:uid="{04AF6D35-FBEF-4E38-B28D-0C23F8EDC5F6}" name="Max frost days" totalsRowDxfId="44" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{475991F7-F3B5-4EEA-966A-7AA8BC301814}" name="Min elevation" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
+    <tableColumn id="12" xr3:uid="{475991F7-F3B5-4EEA-966A-7AA8BC301814}" name="Min elevation" totalsRowDxfId="43" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{767BBD4C-C554-4460-AAD8-ECADA490C9C0}" name="Max elevation" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
+    <tableColumn id="16" xr3:uid="{767BBD4C-C554-4460-AAD8-ECADA490C9C0}" name="Max elevation" totalsRowDxfId="42" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{65D9D85B-649F-4683-B866-BF022CDF3E13}" name="Min MAP:PET" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
+    <tableColumn id="13" xr3:uid="{65D9D85B-649F-4683-B866-BF022CDF3E13}" name="Min MAP:PET" totalsRowDxfId="41" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{969B2D30-E5CD-48F6-AF2A-DAC6295F1FF1}" name="Max MAP:PET" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
+    <tableColumn id="17" xr3:uid="{969B2D30-E5CD-48F6-AF2A-DAC6295F1FF1}" name="Max MAP:PET" totalsRowDxfId="40" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5115,7 +5067,7 @@
     <tableColumn id="1" xr3:uid="{26F7317C-9F68-4F62-B737-D7ABF2DFF387}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{229B1B14-5629-4B1C-9602-463A80BF745E}" name="Wet or Dry Zone" totalsRowDxfId="20" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{229B1B14-5629-4B1C-9602-463A80BF745E}" name="Wet or Dry Zone" totalsRowDxfId="39" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5221,7 +5173,7 @@
     <tableColumn id="1" xr3:uid="{C06588B3-DEB9-485D-8845-44DC96AA1C03}" name="Is in leaching zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{0CB971CE-8314-492D-B32B-05442AFAE65D}" name="FracWET" dataDxfId="19">
+    <tableColumn id="2" xr3:uid="{0CB971CE-8314-492D-B32B-05442AFAE65D}" name="FracWET" dataDxfId="38">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5269,7 +5221,7 @@
     <tableColumn id="1" xr3:uid="{E69E76C7-3ABC-4D33-A248-F4FD8C78DC75}" name="Irrigation type i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{30062886-D624-44B9-A4D6-8172FDB32ACC}" name="FracWET" dataDxfId="18" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{30062886-D624-44B9-A4D6-8172FDB32ACC}" name="FracWET" dataDxfId="37" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5278,16 +5230,16 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{75649617-63F2-4A80-A5EB-06A3280A3C57}" name="Table_SourceData_OtherLivestock_VolatileSolids" displayName="Table_SourceData_OtherLivestock_VolatileSolids" ref="D24:E32" totalsRowShown="0" dataDxfId="53" dataCellStyle="Content normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{75649617-63F2-4A80-A5EB-06A3280A3C57}" name="Table_SourceData_OtherLivestock_VolatileSolids" displayName="Table_SourceData_OtherLivestock_VolatileSolids" ref="D24:E32" totalsRowShown="0" dataDxfId="17" dataCellStyle="Content normal">
   <autoFilter ref="D24:E32" xr:uid="{75649617-63F2-4A80-A5EB-06A3280A3C57}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{3E3B834E-0F7A-47D3-954A-A57B2234370A}" name="Other livestock type" dataDxfId="52" dataCellStyle="Content normal">
+    <tableColumn id="1" xr3:uid="{3E3B834E-0F7A-47D3-954A-A57B2234370A}" name="Other livestock type" dataDxfId="16" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_VolatileSolidsProduced_Data(),Table_SourceData_OtherLivestock_VolatileSolids[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{0BCFF128-A246-43C6-BB57-DC9448A80579}" name="VSj" dataDxfId="51" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{0BCFF128-A246-43C6-BB57-DC9448A80579}" name="VSj" dataDxfId="15" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_VolatileSolidsProduced_Data(),Table_SourceData_OtherLivestock_VolatileSolids[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5305,7 +5257,7 @@
     <tableColumn id="1" xr3:uid="{1236BDD8-AEEC-4D8A-AEFB-ED9356DF3DD1}" name="Climate zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{F6888293-D606-47A6-8932-E2CD434BD8A5}" name="EFPRP" dataDxfId="17" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{F6888293-D606-47A6-8932-E2CD434BD8A5}" name="EFPRP" dataDxfId="36" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5323,7 +5275,7 @@
     <tableColumn id="1" xr3:uid="{082A87F0-D13A-4480-8492-F3D2503C41E2}" name="Month">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{3A38DFCE-8BC1-411E-9649-BA3B242C5C67}" name="Season" dataDxfId="16" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{3A38DFCE-8BC1-411E-9649-BA3B242C5C67}" name="Season" dataDxfId="35" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5355,49 +5307,49 @@
     <tableColumn id="1" xr3:uid="{74BFEBA4-3487-4BE5-88B9-85DB7D433F74}" name="Temperature zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{EE7A79F3-7EC2-470C-8060-08333EAEE5D6}" name="MAT (ºC)" dataDxfId="15" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{EE7A79F3-7EC2-470C-8060-08333EAEE5D6}" name="MAT (ºC)" dataDxfId="34" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{FB41F6A9-5353-48F8-BBE2-FDDAFFCEC3DF}" name="Anaerobic lagoon" dataDxfId="14" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{FB41F6A9-5353-48F8-BBE2-FDDAFFCEC3DF}" name="Anaerobic lagoon" dataDxfId="33" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{46BC84F5-D586-4491-8920-08D8E8254F8B}" name="Digester / covered lagoons" dataDxfId="13" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{46BC84F5-D586-4491-8920-08D8E8254F8B}" name="Digester / covered lagoons" dataDxfId="32" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{48357028-DF7D-43C1-8693-BE3CCAEDC19B}" name="Liquid systems" dataDxfId="12" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{48357028-DF7D-43C1-8693-BE3CCAEDC19B}" name="Liquid systems" dataDxfId="31" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{46A64015-6571-40C8-8B97-9ACD24D0FDFF}" name="Daily spread" dataDxfId="11" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{46A64015-6571-40C8-8B97-9ACD24D0FDFF}" name="Daily spread" dataDxfId="30" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{BE8A0DB7-DA22-4D11-8D6E-5B03E95383E1}" name="Composting (passive windrow)" dataDxfId="10" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{BE8A0DB7-DA22-4D11-8D6E-5B03E95383E1}" name="Composting (passive windrow)" dataDxfId="29" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{8E9FF3D7-C170-4D01-8CAA-D667E3762352}" name="Solid storage" dataDxfId="9" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{8E9FF3D7-C170-4D01-8CAA-D667E3762352}" name="Solid storage" dataDxfId="28" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{EE8195E9-7EB7-4255-B88A-1A7D661007AC}" name="Pit storage" dataDxfId="8" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{EE8195E9-7EB7-4255-B88A-1A7D661007AC}" name="Pit storage" dataDxfId="27" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{E8290DA2-F81B-417D-8DFF-811E04AE5CD6}" name="Deep litter" dataDxfId="7" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{E8290DA2-F81B-417D-8DFF-811E04AE5CD6}" name="Deep litter" dataDxfId="26" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{8556C44B-D53C-43B5-AFA8-775CF9A97C5A}" name="Poultry manure with bedding" dataDxfId="6" dataCellStyle="Content normal">
+    <tableColumn id="11" xr3:uid="{8556C44B-D53C-43B5-AFA8-775CF9A97C5A}" name="Poultry manure with bedding" dataDxfId="25" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{6D7005A7-1332-4775-A075-04932CE4CB0C}" name="Poultry manure without bedding" dataDxfId="5" dataCellStyle="Content normal">
+    <tableColumn id="12" xr3:uid="{6D7005A7-1332-4775-A075-04932CE4CB0C}" name="Poultry manure without bedding" dataDxfId="24" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{CD24F3C7-0171-4241-9095-F217ACFB21FD}" name="Direct processing" dataDxfId="4" dataCellStyle="Content normal">
+    <tableColumn id="13" xr3:uid="{CD24F3C7-0171-4241-9095-F217ACFB21FD}" name="Direct processing" dataDxfId="23" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{B9A1E1BC-6DAC-4A86-933B-0394729DEF0D}" name="Direct application" dataDxfId="3" dataCellStyle="Content normal">
+    <tableColumn id="14" xr3:uid="{B9A1E1BC-6DAC-4A86-933B-0394729DEF0D}" name="Direct application" dataDxfId="22" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{D37545E7-3A7F-4E1D-9175-AF768DF5CDBB}" name="Pasture range and paddock" dataDxfId="2" dataCellStyle="Content normal">
+    <tableColumn id="15" xr3:uid="{D37545E7-3A7F-4E1D-9175-AF768DF5CDBB}" name="Pasture range and paddock" dataDxfId="21" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{01BDA555-814C-4F57-A554-B9E8D1197D3B}" name="MAT raw" dataDxfId="1" dataCellStyle="Content normal">
+    <tableColumn id="16" xr3:uid="{01BDA555-814C-4F57-A554-B9E8D1197D3B}" name="MAT raw" dataDxfId="20" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5415,7 +5367,7 @@
     <tableColumn id="1" xr3:uid="{FD1030A0-8423-4F54-A208-B8E2F9F2CCAF}" name="Climate Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{5D7849B7-3122-4868-94E6-53DB0ADF4E31}" name="EFNi &amp; EFN2Oi" dataDxfId="0" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{5D7849B7-3122-4868-94E6-53DB0ADF4E31}" name="EFNi &amp; EFN2Oi" dataDxfId="19" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5424,16 +5376,16 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{522C94C8-449D-4574-AF4D-39C274C53A6F}" name="Table_SourceData_OtherLivestock_NitrogenExcreted" displayName="Table_SourceData_OtherLivestock_NitrogenExcreted" ref="D39:E47" totalsRowShown="0" dataDxfId="50" dataCellStyle="Content normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{522C94C8-449D-4574-AF4D-39C274C53A6F}" name="Table_SourceData_OtherLivestock_NitrogenExcreted" displayName="Table_SourceData_OtherLivestock_NitrogenExcreted" ref="D39:E47" totalsRowShown="0" dataDxfId="14" dataCellStyle="Content normal">
   <autoFilter ref="D39:E47" xr:uid="{522C94C8-449D-4574-AF4D-39C274C53A6F}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{92CD5559-01AC-4144-B6DC-7F856864840C}" name="Other livestock type" dataDxfId="49" dataCellStyle="Content normal">
+    <tableColumn id="1" xr3:uid="{92CD5559-01AC-4144-B6DC-7F856864840C}" name="Other livestock type" dataDxfId="13" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_NitrogenExcreted_Data(),Table_SourceData_OtherLivestock_NitrogenExcreted[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{A4955FC2-927B-4DF6-B94C-068E74A6FF39}" name="NEj" dataDxfId="48" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{A4955FC2-927B-4DF6-B94C-068E74A6FF39}" name="NEj" dataDxfId="12" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_NitrogenExcreted_Data(),Table_SourceData_OtherLivestock_NitrogenExcreted[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5442,20 +5394,20 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{08C66B47-C28A-4E61-BD61-AB59792A938B}" name="Table_SourceData_OtherLivestock_AverageLiveweight" displayName="Table_SourceData_OtherLivestock_AverageLiveweight" ref="D54:F64" totalsRowShown="0" dataDxfId="47" dataCellStyle="Content normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{08C66B47-C28A-4E61-BD61-AB59792A938B}" name="Table_SourceData_OtherLivestock_AverageLiveweight" displayName="Table_SourceData_OtherLivestock_AverageLiveweight" ref="D54:F64" totalsRowShown="0" dataDxfId="11" dataCellStyle="Content normal">
   <autoFilter ref="D54:F64" xr:uid="{08C66B47-C28A-4E61-BD61-AB59792A938B}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{92B26601-57E2-4637-B097-133483C8744F}" name="Other livestock type" dataDxfId="46" dataCellStyle="Content normal">
+    <tableColumn id="1" xr3:uid="{92B26601-57E2-4637-B097-133483C8744F}" name="Other livestock type" dataDxfId="10" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_AverageLiveweight_Data(),Table_SourceData_OtherLivestock_AverageLiveweight[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{6D10B565-469B-4476-91DD-3E192D501AEC}" name="Wco" dataDxfId="45" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{6D10B565-469B-4476-91DD-3E192D501AEC}" name="Wco" dataDxfId="9" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_AverageLiveweight_Data(),Table_SourceData_OtherLivestock_AverageLiveweight[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{4285ACF1-A507-45A9-B06F-3C8A119CF7C4}" name="Wco2" dataDxfId="44" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{4285ACF1-A507-45A9-B06F-3C8A119CF7C4}" name="Wco2" dataDxfId="8" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_AverageLiveweight_Data(),Table_SourceData_OtherLivestock_AverageLiveweight[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5464,20 +5416,20 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{717E53D2-4463-4A85-80B5-5691AD7D98C8}" name="Table_SourceData_OtherLivestock_FractionWasteInMMS" displayName="Table_SourceData_OtherLivestock_FractionWasteInMMS" ref="D71:F79" totalsRowShown="0" dataDxfId="43" dataCellStyle="Content normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{717E53D2-4463-4A85-80B5-5691AD7D98C8}" name="Table_SourceData_OtherLivestock_FractionWasteInMMS" displayName="Table_SourceData_OtherLivestock_FractionWasteInMMS" ref="D71:F79" totalsRowShown="0" dataDxfId="7" dataCellStyle="Content normal">
   <autoFilter ref="D71:F79" xr:uid="{717E53D2-4463-4A85-80B5-5691AD7D98C8}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{3C1197CD-1D52-441D-BBC2-CD949C23252D}" name="Other livestock type" dataDxfId="42" dataCellStyle="Content normal">
+    <tableColumn id="1" xr3:uid="{3C1197CD-1D52-441D-BBC2-CD949C23252D}" name="Other livestock type" dataDxfId="6" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_FractionWasteInMMS_Data(),Table_SourceData_OtherLivestock_FractionWasteInMMS[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{8073D8FF-B3DA-4F6A-932F-294E074768D7}" name="Pasture range and paddock" dataDxfId="41" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{8073D8FF-B3DA-4F6A-932F-294E074768D7}" name="Pasture range and paddock" dataDxfId="5" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_FractionWasteInMMS_Data(),Table_SourceData_OtherLivestock_FractionWasteInMMS[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{BE446918-69F7-4B13-8457-24AF8D4D48BC}" name="Uncovered anaerobic lagoon" dataDxfId="40" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{BE446918-69F7-4B13-8457-24AF8D4D48BC}" name="Uncovered anaerobic lagoon" dataDxfId="4" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_FractionWasteInMMS_Data(),Table_SourceData_OtherLivestock_FractionWasteInMMS[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5486,20 +5438,20 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{AFA04BB4-DA20-428E-BF28-5455856D0A35}" name="Table_SourceData_OtherLivestock_MCF" displayName="Table_SourceData_OtherLivestock_MCF" ref="D86:F94" totalsRowShown="0" dataDxfId="39" dataCellStyle="Content normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{AFA04BB4-DA20-428E-BF28-5455856D0A35}" name="Table_SourceData_OtherLivestock_MCF" displayName="Table_SourceData_OtherLivestock_MCF" ref="D86:F94" totalsRowShown="0" dataDxfId="3" dataCellStyle="Content normal">
   <autoFilter ref="D86:F94" xr:uid="{AFA04BB4-DA20-428E-BF28-5455856D0A35}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{378D0529-B2BA-4B26-B22D-9D5AE994C705}" name="Other livestock type" dataDxfId="38" dataCellStyle="Content normal">
+    <tableColumn id="1" xr3:uid="{378D0529-B2BA-4B26-B22D-9D5AE994C705}" name="Other livestock type" dataDxfId="2" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_MethaneConversionFactor_Data(),Table_SourceData_OtherLivestock_MCF[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{614FC5E3-9067-4D7A-9048-5C785284F6FC}" name="Pasture range and paddock" dataDxfId="37" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{614FC5E3-9067-4D7A-9048-5C785284F6FC}" name="Pasture range and paddock" dataDxfId="1" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_MethaneConversionFactor_Data(),Table_SourceData_OtherLivestock_MCF[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{9125F130-A695-42FD-984B-66D9A47F338B}" name="Uncovered anaerobic lagoon" dataDxfId="36" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{9125F130-A695-42FD-984B-66D9A47F338B}" name="Uncovered anaerobic lagoon" dataDxfId="0" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_MethaneConversionFactor_Data(),Table_SourceData_OtherLivestock_MCF[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -11596,11 +11548,11 @@
       </c>
       <c r="H7" s="85">
         <f>'3.6.1.1-2 Enteric Methane'!E33</f>
-        <v>0</v>
+        <v>17659.599999999999</v>
       </c>
       <c r="I7" s="85">
         <f>H7</f>
-        <v>0</v>
+        <v>17659.599999999999</v>
       </c>
       <c r="J7" s="50" t="s">
         <v>84</v>
@@ -11622,11 +11574,11 @@
       <c r="G8" s="29"/>
       <c r="H8" s="86">
         <f>SUM(H7:H7)</f>
-        <v>0</v>
+        <v>17659.599999999999</v>
       </c>
       <c r="I8" s="86">
         <f>SUM(I7:I7)</f>
-        <v>0</v>
+        <v>17659.599999999999</v>
       </c>
       <c r="J8" s="81" t="s">
         <v>84</v>
@@ -14226,7 +14178,7 @@
         <v>Buffalo</v>
       </c>
       <c r="E19" s="48">
-        <f>SUM('Input - Other Livestock'!E8:H8)</f>
+        <f>SUM(X_Table_OtherLivestock_Buffalo_Head)</f>
         <v>4600</v>
       </c>
       <c r="F19" s="48" cm="1">
@@ -14248,7 +14200,7 @@
         <v>Goats</v>
       </c>
       <c r="E20" s="48">
-        <f>SUM('Input - Other Livestock'!E14:J14)</f>
+        <f>SUM(X_Table_OtherLivestock_Goats_Head)</f>
         <v>4800</v>
       </c>
       <c r="F20" s="48" cm="1">
@@ -14267,7 +14219,7 @@
         <v>Deer</v>
       </c>
       <c r="E21" s="48">
-        <f>SUM('Input - Other Livestock'!E20:H20)</f>
+        <f>SUM(X_Table_OtherLivestock_Deer_Head)</f>
         <v>4600</v>
       </c>
       <c r="F21" s="48" cm="1">
@@ -14285,7 +14237,7 @@
         <v>Camels</v>
       </c>
       <c r="E22" s="48">
-        <f>'Input - Other Livestock'!E26</f>
+        <f>X_Cell_OtherLivestock_Others_Camels_Head</f>
         <v>4300</v>
       </c>
       <c r="F22" s="48" cm="1">
@@ -14303,7 +14255,7 @@
         <v>Alpacas</v>
       </c>
       <c r="E23" s="48">
-        <f>'Input - Other Livestock'!F26</f>
+        <f>X_Cell_OtherLivestock_Others_Alpacas_Head</f>
         <v>100</v>
       </c>
       <c r="F23" s="48" cm="1">
@@ -14321,7 +14273,7 @@
         <v>Horses</v>
       </c>
       <c r="E24" s="48">
-        <f>'Input - Other Livestock'!G26</f>
+        <f>X_Cell_OtherLivestock_Others_Horses_Head</f>
         <v>100</v>
       </c>
       <c r="F24" s="48" cm="1">
@@ -14340,7 +14292,7 @@
         <v>Mules/asses</v>
       </c>
       <c r="E25" s="48">
-        <f>'Input - Other Livestock'!H26</f>
+        <f>X_Cell_OtherLivestock_Others_Mules_Head</f>
         <v>100</v>
       </c>
       <c r="F25" s="48" cm="1">
@@ -14358,7 +14310,7 @@
         <v>Emus/ostriches</v>
       </c>
       <c r="E26" s="48">
-        <f>'Input - Other Livestock'!I26</f>
+        <f>X_Cell_OtherLivestock_Others_Emus_Head</f>
         <v>100</v>
       </c>
       <c r="F26" s="48" cm="1">
@@ -14413,8 +14365,8 @@
       </c>
       <c r="F31" s="106"/>
       <c r="G31" s="48">
-        <f>Common_InputFunctions.Utility_LookupValueInTableNumber("CH4",[1]!Table_GWPData1412[Gas],[1]!Table_GWPData1412[CO2-e factor])</f>
-        <v>0</v>
+        <f>Common_InputFunctions.Utility_LookupValueInTableNumber("CH4",Table_GWPData[Gas],Table_GWPData[CO2-e factor])</f>
+        <v>28</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -14424,7 +14376,7 @@
       </c>
       <c r="E33" s="43" cm="1">
         <f t="array" ref="E33">Common_Equations.Common_ConvertCH4ToCO2e(G30,G31)</f>
-        <v>0</v>
+        <v>17659.599999999999</v>
       </c>
       <c r="F33" s="81" t="str" cm="1">
         <f t="array" ref="F33">Common_Equations.Common_ConvertN2OToCO2e_Unit()</f>
@@ -20208,6 +20160,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -20402,31 +20374,30 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACkAKgAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADIAKQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAHQAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAC8AdABcAHUAMAAwADMAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAdQAwADAAMgA3AFwAIgAgAFwAdQAwADAAMgA2ACAAcwBoACAAXAB1ADAAMAAyADYAIABcACIAXAB1ADAAMAAyADcAIQBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgAFwAdQAwADAAMgA2ACAAXAAiACAAXAAiACAAXAB1ADAAMAAyADYAIABUAGkAdABsAGUAQwBlAGwAbABcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAiACwAIgB0AGUAeAB0ACIAOgAiAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuADEAOgAgAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAALQAgAEUAbgB0AGUAcgBpAGMAIABmAGUAcgBtAGUAbgB0AGEAdABpAG8AbgAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABlAGEAYwBoACAAbwB0AGgAZQByACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlACAAKABrAGcAIABDAEgANAAvAGgAZQBhAGQALwB5AGUAYQByACkAIAAoAE0AagApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAARQBuAHQAZQByAGkAYwAgAGYAZQByAG0AZQBuAHQAYQB0AGkAbwBuACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGUAYQBjAGgAIABvAHQAaABlAHIAIABsAGkAdgBlAHMAdABvAGMAawAgAHQAeQBwAGUAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBqAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABDAEgANAAgAC8AIABoAGUAYQBkACAALwAgAHkAZQBhAHIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADUALgAxAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAyACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAAVAB5AHAAZQBcACIALAAgAFwAIgBNAGoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBmAGYAYQBsAG8AXAAiACwAIAA2ADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBvAGEAdABzAFwAIgAsACAANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGUAZQByAFwAIgAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAYQBtAGUAbABzAFwAIgAsACAANAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbABwAGEAYwBhAHMAXAAiACwAIAA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHMAZQBzAFwAIgAsACAAMQA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AdQBsAGUAcwAvAGEAcwBzAGUAcwBcACIALAAgADEAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AdQBzAC8AbwBzAHQAcgBpAGMAaABlAHMAXAAiACwAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAbwBkAHUAYwBlAGQAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuADIAOgAgAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAALQAgAFYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAcAByAG8AZAB1AGMAZQBkACAAYgB5ACAAZQBhAGMAaAAgAG8AdABoAGUAcgAgAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQAgACgAawBnACAAVgBTAC8AaABlAGEAZAAvAGQAYQB5ACkAIAAoAFYAUwBqACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAbwBkAHUAYwBlAGQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAALQAgAFYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAcAByAG8AZAB1AGMAZQBkACAAYgB5ACAAZQBhAGMAaAAgAG8AdABoAGUAcgAgAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAbwBkAHUAYwBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAUwBqAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBvAGQAdQBjAGUAZABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAFYAUwAgAC8AIABoAGUAYQBkACAALwAgAGQAYQB5AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBvAGQAdQBjAGUAZABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADUALgAyAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBvAGQAdQBjAGUAZABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAbwBkAHUAYwBlAGQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMgAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawAgAFQAeQBwAGUAXAAiACwAIABcACIAVgBTAGoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBmAGYAYQBsAG8AXAAiACwAIAAyAC4ANwAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAbwBhAHQAcwBcACIALAAgADAALgAzADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGUAcgBcACIALAAgADAALgA5ADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBhAG0AZQBsAHMAXAAiACwAIAAyAC4ANwAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbABwAGEAYwBhAHMAXAAiACwAIAAwAC4AMwA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHMAZQBzAFwAIgAsACAAMgAuADcAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAHUAbABlAHMALwBhAHMAcwBlAHMAXAAiACwAIAAwAC4AOQAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAbQB1AHMALwBvAHMAdAByAGkAYwBoAGUAcwBcACIALAAgADAALgAzADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABcAG4AVABhAGIAbABlACAAQQAuADEALgA1AC4AMwA6ACAATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAATgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAZQBkACAAcABlAHIAIABsAGkAdgBlAHMAdABvAGMAawAgAHQAeQBwAGUAIAAoAGsAZwAgAE4AMgBPAC8AaABlAGEAZAAvAHkAZQBhAHIAKQAgACgATgBFAGoAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAATgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAZQBkACAAcABlAHIAIABsAGkAdgBlAHMAdABvAGMAawAgAHQAeQBwAGUAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAEUAagBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC8AIABoAGUAYQBkACAALwAgAHkAZQBhAHIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuADMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAyACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAAVAB5AHAAZQBcACIALAAgAFwAIgBOAEUAagBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgB1AGYAZgBhAGwAbwBcACIALAAgADMAOQAuADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBvAGEAdABzAFwAIgAsACAANwAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGUAcgBcACIALAAgADEAMwAuADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBhAG0AZQBsAHMAXAAiACwAIAAzADkALgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbABwAGEAYwBhAHMAXAAiACwAIAA3AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgBzAGUAcwBcACIALAAgADMAOQAuADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQB1AGwAZQBzAC8AYQBzAHMAZQBzAFwAIgAsACAAMQAzAC4AMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AdQBzAC8AbwBzAHQAcgBpAGMAaABlAHMAXAAiACwAIAA3AC4AMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuADQAOgAgAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAALQAgAEEAdgBlAHIAYQBnAGUAIABMAGkAdgBlAHcAZQBpAGcAaAB0AHMAIAAoAFcAYwBvACkAIAAoAGsAZwApACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAAQQB2AGUAcgBhAGcAZQAgAEwAaQB2AGUAdwBlAGkAZwBoAHQAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVwBjAG8AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA1AC4ANABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADEALAAgADMALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIABUAHkAcABlACAAagBcACIALAAgAFwAIgBBAHYAZQByAGEAZwBlACAATABpAHYAZQB3AGUAaQBnAGgAdABcACIALAAgAFwAIgBBAHYAZQByAGEAZwBlACAATABpAHYAZQB3AGUAaQBnAGgAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgB1AGYAZgBhAGwAbwBcACIALAAgADMAMwA2ACwAIABcACIALQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBvAGEAdABzAFwAIgAsACAAMwAzACwAIABcACIAMgA4AGsAZwAgAC0AIABsAG8AdwAgAHAAcgBvAGQAdQBjAHQAaQB2AGkAdAB5ACAAcwB5AHMAdABlAG0AcwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBvAGEAdABzAFwAIgAsACAAMwAzACwAIABcACIANQAwAGsAZwAgAC0AIABoAGkAZwBoACAAcAByAG8AZAB1AGMAdABpAHYAaQB0AHkAIABzAHkAcwB0AGUAbQBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGUAZQByAFwAIgAsACAAMQAyADAALAAgADEAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAYQBtAGUAbABzAFwAIgAsACAAMgAxADcALAAgADUANwAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbABwAGEAYwBhAHMAXAAiACwAIABcACIALQBcACIALAAgADYANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgBzAGUAcwBcACIALAAgADMANwA3ACwAIAA1ADUAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAHUAbABlAHMALwBhAHMAcwBlAHMAXAAiACwAIAAxADMAMAAsACAAMgA0ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAHUAcwAvAG8AcwB0AHIAaQBjAGgAZQBzAFwAIgAsACAAMQAyADAALAAgADEAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBmAGUAcgBlAG4AYwBlAFwAIgAsACAAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAVABhAGIAbABlACAAMQAwAEEALgA1ACAAWwAyAF0AXAAiACwAIABcACIASQBQAEMAQwAgADIAMAAxADkAIABUAGEAYgBsAGUAIAAxADAALgAxADAAIABbADIAXQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwB0AGkAbwBuAFcAYQBzAHQAZQBJAG4ATQBNAFMAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuADUAOgAgAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAALQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHcAYQBzAHQAZQAgAGkAbgAgAGUAYQBjAGgAIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAIABzAHkAcwB0AGUAbQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0ATQBTAG0AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwB0AGkAbwBuAFcAYQBzAHQAZQBJAG4ATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAALQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHcAYQBzAHQAZQAgAGkAbgAgAGUAYQBjAGgAIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAIABzAHkAcwB0AGUAbQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMAdABpAG8AbgBXAGEAcwB0AGUASQBuAE0ATQBTAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE0AUwBtAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwB0AGkAbwBuAFcAYQBzAHQAZQBJAG4ATQBNAFMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAHQAaQBvAG4AVwBhAHMAdABlAEkAbgBNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADUALgA1AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwB0AGkAbwBuAFcAYQBzAHQAZQBJAG4ATQBNAFMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAHQAaQBvAG4AVwBhAHMAdABlAEkAbgBNAE0AUwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAzACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQBcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBDAFQAXAAiACwAIAAgADkAOQAuADYANgAsACAAIAAwAC4AMwA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AUwBXAFwAIgAsACAAIAA5ADkALgA2ADYALAAgACAAMAAuADMANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFQAXAAiACwAIAAgADkAOQAuADYANgAsACAAIAAwAC4AMwA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEATABEAFwAIgAsACAAIAA5ADkALgA2ADYALAAgACAAMAAuADMANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEEAXAAiACwAIAAgADkAOQAuADYANgAsACAAIAAwAC4AMwA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAQQBTAFwAIgAsACAAIAA5ADkALgA2ADYALAAgACAAMAAuADMANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEkAQwBcACIALAAgACAAOQA5AC4ANgA2ACwAIAAgADAALgAzADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBBAFwAIgAsACAAIAA5ADkALgA2ADYALAAgACAAMAAuADMANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuADYAOgAgAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAALQAgAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAHIAZQBnAGkAbwBuACAAKABmAHIAYQBjAHQAaQBvAG4AKQAgACgATQBDAEYAaQBtACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAcgBlAGcAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AQwBGAGkAbQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADUALgA2AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXAAiACwAIABcACIAVQBuAGMAbwB2AGUAcgBlAGQAIABBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAEMAVABcACIALAAgACAAMAAuADAAMAA0ADcALAAgACAAMAAuADcAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFMAVwBcACIALAAgACAAMAAuADAAMAA0ADcALAAgACAAMAAuADcANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFQAXAAiACwAIAAgADAALgAwADAANAA3ACwAIAAgADAALgA4ADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBMAEQAXAAiACwAIAAgADAALgAwADAANAA3ACwAIAAgADAALgA3ADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBAFwAIgAsACAAIAAwAC4AMAAwADQANwAsACAAIAAwAC4ANwA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAQQBTAFwAIgAsACAAIAAwAC4AMAAwADQANwAsACAAIAAwAC4ANwAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYASQBDAFwAIgAsACAAIAAwAC4AMAAwADQANwAsACAAIAAwAC4ANwA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAQQBcACIALAAgACAAMAAuADAAMAA0ADcALAAgACAAMAAuADcANgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADUALgBYADoAIABPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawAgAC0AIABNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbAAgACgAbQAzACAAQwBIADQAIAAvACAAawBnACAAVgBTACkAIAAoAEIATwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawAgAC0AIABNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEIATwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBtADMAIABDAEgANAAgAC8AIABrAGcAIABWAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuAFgAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgAgAFQAaABlAHIAZQAgAHcAZQByAGUAIABuAG8AIAB2AGEAbAB1AGUAcwAgAGkAbgAgAFYARQBFAFIARwAgAHMAbwAgAHQAaABpAHMAIABkAGEAdABhACAAaABhAHMAIABiAGUAZQBuACAAZwBlAG4AZQByAGEAdABlAGQAIABiAHkAIAB1AHMAaQBuAGcAIABkAG8AYwB1AG0AZQBuAHQAZQBkACAAQgBPACAAdgBhAGwAdQBlAHMAIABmAHIAbwBtACAAbwB0AGgAZQByACAAbABpAHYAZQBzAHQAbwBjAGsAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIABUAHkAcABlAFwAIgAsACAAXAAiAEIATwBcACIALAAgAFwAIgBUAGEAawBlAG4AIABmAHIAbwBtAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAHUAZgBmAGEAbABvAFwAIgAsACAAMAAuADEAOQAsACAAXAAiAEYAZQBlAGQAbABvAHQALAAgAFAAYQBzAHQAdQByAGUAIABiAGUAZQBmAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAG8AYQB0AHMAXAAiACwAIAAwAC4AMgA0ACwAIABcACIAUwBoAGUAZQBwAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGUAZQByAFwAIgAsACAAMAAuADIANAAsACAAXAAiAFMAaABlAGUAcABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBhAG0AZQBsAHMAXAAiACwAIAAwAC4AMgA0ACwAIABcACIAUwBoAGUAZQBwAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGwAcABhAGMAYQBzAFwAIgAsACAAMAAuADIANAAsACAAXAAiAFMAaABlAGUAcABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABvAHIAcwBlAHMAXAAiACwAIAAwAC4AMQA5ACwAIABcACIARgBlAGUAZABsAG8AdAAsACAAUABhAHMAdAB1AHIAZQAgAGIAZQBlAGYAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AdQBsAGUAcwAvAGEAcwBzAGUAcwBcACIALAAgADAALgAyADQALAAgAFwAIgBTAGgAZQBlAHAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAbQB1AHMALwBvAHMAdAByAGkAYwBoAGUAcwBcACIALAAgADAALgAzADYALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAALQAgAG0AZQBhAHQAIABjAGgAaQBjAGsAZQBuAHMAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMARwBBAFMATQBTAG8AaQBsAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABmAHIAbwBtACAAdQByAGkAbgBlACAAYQBuAGQAIABmAGEAZQBjAGUAcwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGYAcgBvAG0AIAB1AHIAaQBuAGUAIABhAG4AZAAgAGYAYQBlAGMAZQBzACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMARwBBAFMATQBzAG8AaQBsAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4ASAAzAC0ATgAgACsAIABOAE8AeAAtAE4AKQAvAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4ANwAuADIALgAzACAAQwBPAE4AUwBUAEEATgBUAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMARwBBAFMATQBTAG8AaQBsAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4AMgAxACkAOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADMALgA2ADoAIABFAG4AdABlAHIAaQBjACAATQBlAHQAaABhAG4AZQAgAC0AIABPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMwAuADYALgAxAC4AMQAgAE0AZQB0AGgAbwBkACAAMQAgAC0AIABFAG4AdABlAHIAaQBjACAATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAzAF8ANgBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBcAG4AVABvAHQAYQBsACAAYQBuAG4AdQBhAGwAIABtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABlAG4AdABlAHIAaQBjACAAZgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AIABpAG4AIABvAHQAaABlAHIAIABsAGkAdgBlAHMAdABvAGMAawBcAG4ARQBfAGUAbgB0AGUAcgBpAGMAXABuAHQAIABDAEgANABcAG4ARQBfAHsAZQBuAHQAZQByAGkAYwB9AD0AXABcAHMAdQBtAF8AagAoAE4AXwBqAFwAXAB0AGkAbQBlAHMAIABNAF8AagApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBOAF8AagAgAD0AIABuAHUAbQBiAGUAcgAgAG8AZgAgAGwAaQB2AGUAcwB0AG8AYwBrACAAbwBmACAAZQBhAGMAaAAgAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQAgAGoAIAAoAGgAZQBhAGQAKQBcAG4ATQBfAGoAIAA9ACAAZQBuAHQAZQByAGkAYwAgAGYAZQByAG0AZQBuAHQAYQB0AGkAbwBuACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIAAoAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAHkAZQBhAHIAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAzAF8ANgBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABOAF8AagAsACAATQBfAGoALABcAG4AIAAgACAAIABTAFUATQAoAE4AXwBqACAAKgAgAE0AXwBqACkAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwA2AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBUAG8AdABhAGwAIABhAG4AbgB1AGEAbAAgAG0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAGUAbgB0AGUAcgBpAGMAIABmAGUAcgBtAGUAbgB0AGEAdABpAG8AbgAgAGkAbgAgAG8AdABoAGUAcgAgAGwAaQB2AGUAcwB0AG8AYwBrAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8ANgBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAGUAbgB0AGUAcgBpAGMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwA2AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMASAA0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8ANgBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAzAC4ANgAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADYAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwA2AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsAZQBuAHQAZQByAGkAYwB9AD0AXABcAHMAdQBtAF8AagAoAE4AXwBqAFwAXAB0AGkAbQBlAHMAIABNAF8AagApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8ANgBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAF8AagBcACIALAAgAFwAIgBuAHUAbQBiAGUAcgAgAG8AZgAgAGwAaQB2AGUAcwB0AG8AYwBrACAAbwBmACAAZQBhAGMAaAAgAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQAgAGoAXAAiACwAIABcACIAaABlAGEAZABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AXwBqAFwAIgAsACAAXAAiAGUAbgB0AGUAcgBpAGMAIABmAGUAcgBtAGUAbgB0AGEAdABpAG8AbgAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAHkAZQBhAHIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBqAFwAIgAsACAAXAAiAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMQBfADIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADMAXwA0ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAbwBkAHUAYwBlAGQAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAG8AZAB1AGMAZQBkAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBvAGQAdQBjAGUAZABfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAG8AZAB1AGMAZQBkAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAG8AZAB1AGMAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAG8AZAB1AGMAZQBkAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMAdABpAG8AbgBXAGEAcwB0AGUASQBuAE0ATQBTAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwB0AGkAbwBuAFcAYQBzAHQAZQBJAG4ATQBNAFMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAHQAaQBvAG4AVwBhAHMAdABlAEkAbgBNAE0AUwBfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAHQAaQBvAG4AVwBhAHMAdABlAEkAbgBNAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwB0AGkAbwBuAFcAYQBzAHQAZQBJAG4ATQBNAFMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMAdABpAG8AbgBXAGEAcwB0AGUASQBuAE0ATQBTAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8ARABhAHQAYQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwA2AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADYAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8ANgBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwA2AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVQBuAGkAdAAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwA2AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8ANgBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADYAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADYAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBBAHIAZwB1AG0AZQBuAHQAcwAiAF0ALAAiAGwAbwBjAGEAbABlACIAOgB7ACIAbABpAHMAdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHIAbwB3AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAYwBvAGwAdQBtAG4AUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFAAbwBzAGkAdABpAG8AbgBzACIAOgBbADMAXQAsACIAZABlAGMAaQBtAGEAbABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAuACIALAAiAGQAYQB0AGUATwByAGQAZQByACIAOgAiAEQATQBZACIALAAiAGMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbAAiADoAIgAkACIALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwATABlAGEAZAAiADoAdAByAHUAZQAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAGUAcABCAHkAUwBwAGEAYwBlACIAOgBmAGEAbABzAGUALAAiAHIAbwB3AEwAZQB0AHQAZQByACIAOgAiAFIAIgAsACIAYwBvAGwAdQBtAG4ATABlAHQAdABlAHIAIgA6ACIAQwAiACwAIgByAGMATABlAGYAdABCAHIAYQBjAGsAZQB0ACIAOgAiAFsAIgAsACIAcgBjAFIAaQBnAGgAdABCAHIAYQBjAGsAZQB0ACIAOgAiAF0AIgAsACIAcwB0AGEAdABlAG0AZQBuAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBsAG8AYwBhAGwAZQBOAGEAbQBlACIAOgAiAGUAbgAtAHUAcwAiAH0AfQA=</AFEJSONBlob>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
+    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809E3D44-A88D-4EBF-A307-6B8CE77A3361}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -20445,25 +20416,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
-    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
   <ds:schemaRefs>

--- a/Excel/3_6_Enteric_OtherLivestock_WIP_v01.xlsx
+++ b/Excel/3_6_Enteric_OtherLivestock_WIP_v01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{975F5477-615C-4E31-A68B-C5D43F400110}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C81702B8-4F57-49AC-B39F-97B65B3C9083}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1650" yWindow="1410" windowWidth="36255" windowHeight="19140" firstSheet="1" activeTab="5" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="1350" yWindow="360" windowWidth="36255" windowHeight="19140" firstSheet="1" activeTab="5" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -180,6 +180,7 @@
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Unit">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Variable">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Variation">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VARIATION OF SOURCE DATA:";"Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.";"Fixed typo - Changed 'Fry' to 'Dry'."}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData_DensityOfMethane_Data">'Constants - Common'!$D$175</definedName>
     <definedName name="CommonLivestock_InputFunctions.AverageLiveweightEndOfMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart,_xlpm.LiveweightAtStart,_xlpm.LiveweightGain, [0]!CommonLivestock_InputFunctions.LivestockMovement_ProportionalAverageLiveweightAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStart) + [0]!CommonLivestock_InputFunctions.LivestockMovement_ProportionalAverageLiveweightRemainingAtEndOfMonth(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStart, _xlpm.LiveweightAtStart, _xlpm.LiveweightGain))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_AverageLiveweightAddedDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR([0]!CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass) / [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_GetMovementLiveweightGain" localSheetId="7">_xlfn.LAMBDA(_xlpm.LivestockClass,_xlpm.MovementDate, _xlfn.LET(_xlpm.ym, TEXT(_xlpm.MovementDate, "yyyymm"), IFERROR(INDEX(_xlfn._xlws.FILTER(#REF!, (TEXT(#REF!, "yyyymm") = _xlpm.ym) * (#REF! = _xlpm.LivestockClass)), 1), "")))</definedName>
@@ -4945,7 +4946,7 @@
     <tableColumn id="1" xr3:uid="{D57CB9BE-4423-4B3C-8812-0053460E9FD4}" name="Other livestock type">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_EntericFermentationEmissionFactor_Data(),Table_SourceData_OtherLivestock_EntericEF[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{076CA99E-B6FF-4452-AA90-21B8618FF161}" name="Mj" dataDxfId="18" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{076CA99E-B6FF-4452-AA90-21B8618FF161}" name="Mj" dataDxfId="54" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_EntericFermentationEmissionFactor_Data(),Table_SourceData_OtherLivestock_EntericEF[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5007,49 +5008,49 @@
     <tableColumn id="1" xr3:uid="{C1368F08-D067-4EEC-B0CC-D2E1F6D93274}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{773305BF-D908-4C35-A934-C13BC9D3D8FF}" name="MAT" totalsRowDxfId="54" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{773305BF-D908-4C35-A934-C13BC9D3D8FF}" name="MAT" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{DF05DA85-723A-420A-AA03-0A716BECCE22}" name="MAP" totalsRowDxfId="53" totalsRowCellStyle="Content bold">
+    <tableColumn id="3" xr3:uid="{DF05DA85-723A-420A-AA03-0A716BECCE22}" name="MAP" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{8B8F9D2B-3A8F-44F1-9417-280165AE86AB}" name="Frost days per year" totalsRowDxfId="52" totalsRowCellStyle="Content bold">
+    <tableColumn id="4" xr3:uid="{8B8F9D2B-3A8F-44F1-9417-280165AE86AB}" name="Frost days per year" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{31B1CBF8-C757-4A17-AD4E-3FED04A08D97}" name="Elevation" totalsRowDxfId="51" totalsRowCellStyle="Content bold">
+    <tableColumn id="5" xr3:uid="{31B1CBF8-C757-4A17-AD4E-3FED04A08D97}" name="Elevation" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{9F5D51C1-ECC4-49B6-A4BE-AE3B3C663E64}" name="MAP:PET" totalsRowDxfId="50" totalsRowCellStyle="Content bold">
+    <tableColumn id="6" xr3:uid="{9F5D51C1-ECC4-49B6-A4BE-AE3B3C663E64}" name="MAP:PET" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{874F3D25-0748-4359-BEF3-58E34D4DFAA6}" name="Min temp" totalsRowDxfId="49" totalsRowCellStyle="Content bold">
+    <tableColumn id="7" xr3:uid="{874F3D25-0748-4359-BEF3-58E34D4DFAA6}" name="Min temp" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{79652299-3198-47E6-B342-A54F0A0B3674}" name="Max temp" totalsRowDxfId="48" totalsRowCellStyle="Content bold">
+    <tableColumn id="8" xr3:uid="{79652299-3198-47E6-B342-A54F0A0B3674}" name="Max temp" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{A0139A89-1186-4484-B833-03C424C4D2C4}" name="Min rainfall" totalsRowDxfId="47" totalsRowCellStyle="Content bold">
+    <tableColumn id="9" xr3:uid="{A0139A89-1186-4484-B833-03C424C4D2C4}" name="Min rainfall" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{BD7A797C-3EEA-481F-9533-984ECCA62AC3}" name="Max rainfall" totalsRowDxfId="46" totalsRowCellStyle="Content bold">
+    <tableColumn id="10" xr3:uid="{BD7A797C-3EEA-481F-9533-984ECCA62AC3}" name="Max rainfall" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{29123C0E-9E60-43AB-8679-2AC0908200D0}" name="Min frost days" totalsRowDxfId="45" totalsRowCellStyle="Content bold">
+    <tableColumn id="11" xr3:uid="{29123C0E-9E60-43AB-8679-2AC0908200D0}" name="Min frost days" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{04AF6D35-FBEF-4E38-B28D-0C23F8EDC5F6}" name="Max frost days" totalsRowDxfId="44" totalsRowCellStyle="Content bold">
+    <tableColumn id="15" xr3:uid="{04AF6D35-FBEF-4E38-B28D-0C23F8EDC5F6}" name="Max frost days" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{475991F7-F3B5-4EEA-966A-7AA8BC301814}" name="Min elevation" totalsRowDxfId="43" totalsRowCellStyle="Content bold">
+    <tableColumn id="12" xr3:uid="{475991F7-F3B5-4EEA-966A-7AA8BC301814}" name="Min elevation" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{767BBD4C-C554-4460-AAD8-ECADA490C9C0}" name="Max elevation" totalsRowDxfId="42" totalsRowCellStyle="Content bold">
+    <tableColumn id="16" xr3:uid="{767BBD4C-C554-4460-AAD8-ECADA490C9C0}" name="Max elevation" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{65D9D85B-649F-4683-B866-BF022CDF3E13}" name="Min MAP:PET" totalsRowDxfId="41" totalsRowCellStyle="Content bold">
+    <tableColumn id="13" xr3:uid="{65D9D85B-649F-4683-B866-BF022CDF3E13}" name="Min MAP:PET" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{969B2D30-E5CD-48F6-AF2A-DAC6295F1FF1}" name="Max MAP:PET" totalsRowDxfId="40" totalsRowCellStyle="Content bold">
+    <tableColumn id="17" xr3:uid="{969B2D30-E5CD-48F6-AF2A-DAC6295F1FF1}" name="Max MAP:PET" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5067,7 +5068,7 @@
     <tableColumn id="1" xr3:uid="{26F7317C-9F68-4F62-B737-D7ABF2DFF387}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{229B1B14-5629-4B1C-9602-463A80BF745E}" name="Wet or Dry Zone" totalsRowDxfId="39" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{229B1B14-5629-4B1C-9602-463A80BF745E}" name="Wet or Dry Zone" totalsRowDxfId="20" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5173,7 +5174,7 @@
     <tableColumn id="1" xr3:uid="{C06588B3-DEB9-485D-8845-44DC96AA1C03}" name="Is in leaching zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{0CB971CE-8314-492D-B32B-05442AFAE65D}" name="FracWET" dataDxfId="38">
+    <tableColumn id="2" xr3:uid="{0CB971CE-8314-492D-B32B-05442AFAE65D}" name="FracWET" dataDxfId="19">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5221,7 +5222,7 @@
     <tableColumn id="1" xr3:uid="{E69E76C7-3ABC-4D33-A248-F4FD8C78DC75}" name="Irrigation type i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{30062886-D624-44B9-A4D6-8172FDB32ACC}" name="FracWET" dataDxfId="37" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{30062886-D624-44B9-A4D6-8172FDB32ACC}" name="FracWET" dataDxfId="18" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5230,16 +5231,16 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{75649617-63F2-4A80-A5EB-06A3280A3C57}" name="Table_SourceData_OtherLivestock_VolatileSolids" displayName="Table_SourceData_OtherLivestock_VolatileSolids" ref="D24:E32" totalsRowShown="0" dataDxfId="17" dataCellStyle="Content normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{75649617-63F2-4A80-A5EB-06A3280A3C57}" name="Table_SourceData_OtherLivestock_VolatileSolids" displayName="Table_SourceData_OtherLivestock_VolatileSolids" ref="D24:E32" totalsRowShown="0" dataDxfId="53" dataCellStyle="Content normal">
   <autoFilter ref="D24:E32" xr:uid="{75649617-63F2-4A80-A5EB-06A3280A3C57}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{3E3B834E-0F7A-47D3-954A-A57B2234370A}" name="Other livestock type" dataDxfId="16" dataCellStyle="Content normal">
+    <tableColumn id="1" xr3:uid="{3E3B834E-0F7A-47D3-954A-A57B2234370A}" name="Other livestock type" dataDxfId="52" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_VolatileSolidsProduced_Data(),Table_SourceData_OtherLivestock_VolatileSolids[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{0BCFF128-A246-43C6-BB57-DC9448A80579}" name="VSj" dataDxfId="15" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{0BCFF128-A246-43C6-BB57-DC9448A80579}" name="VSj" dataDxfId="51" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_VolatileSolidsProduced_Data(),Table_SourceData_OtherLivestock_VolatileSolids[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5257,7 +5258,7 @@
     <tableColumn id="1" xr3:uid="{1236BDD8-AEEC-4D8A-AEFB-ED9356DF3DD1}" name="Climate zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{F6888293-D606-47A6-8932-E2CD434BD8A5}" name="EFPRP" dataDxfId="36" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{F6888293-D606-47A6-8932-E2CD434BD8A5}" name="EFPRP" dataDxfId="17" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5275,7 +5276,7 @@
     <tableColumn id="1" xr3:uid="{082A87F0-D13A-4480-8492-F3D2503C41E2}" name="Month">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{3A38DFCE-8BC1-411E-9649-BA3B242C5C67}" name="Season" dataDxfId="35" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{3A38DFCE-8BC1-411E-9649-BA3B242C5C67}" name="Season" dataDxfId="16" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5307,49 +5308,49 @@
     <tableColumn id="1" xr3:uid="{74BFEBA4-3487-4BE5-88B9-85DB7D433F74}" name="Temperature zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{EE7A79F3-7EC2-470C-8060-08333EAEE5D6}" name="MAT (ºC)" dataDxfId="34" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{EE7A79F3-7EC2-470C-8060-08333EAEE5D6}" name="MAT (ºC)" dataDxfId="15" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{FB41F6A9-5353-48F8-BBE2-FDDAFFCEC3DF}" name="Anaerobic lagoon" dataDxfId="33" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{FB41F6A9-5353-48F8-BBE2-FDDAFFCEC3DF}" name="Anaerobic lagoon" dataDxfId="14" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{46BC84F5-D586-4491-8920-08D8E8254F8B}" name="Digester / covered lagoons" dataDxfId="32" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{46BC84F5-D586-4491-8920-08D8E8254F8B}" name="Digester / covered lagoons" dataDxfId="13" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{48357028-DF7D-43C1-8693-BE3CCAEDC19B}" name="Liquid systems" dataDxfId="31" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{48357028-DF7D-43C1-8693-BE3CCAEDC19B}" name="Liquid systems" dataDxfId="12" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{46A64015-6571-40C8-8B97-9ACD24D0FDFF}" name="Daily spread" dataDxfId="30" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{46A64015-6571-40C8-8B97-9ACD24D0FDFF}" name="Daily spread" dataDxfId="11" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{BE8A0DB7-DA22-4D11-8D6E-5B03E95383E1}" name="Composting (passive windrow)" dataDxfId="29" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{BE8A0DB7-DA22-4D11-8D6E-5B03E95383E1}" name="Composting (passive windrow)" dataDxfId="10" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{8E9FF3D7-C170-4D01-8CAA-D667E3762352}" name="Solid storage" dataDxfId="28" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{8E9FF3D7-C170-4D01-8CAA-D667E3762352}" name="Solid storage" dataDxfId="9" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{EE8195E9-7EB7-4255-B88A-1A7D661007AC}" name="Pit storage" dataDxfId="27" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{EE8195E9-7EB7-4255-B88A-1A7D661007AC}" name="Pit storage" dataDxfId="8" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{E8290DA2-F81B-417D-8DFF-811E04AE5CD6}" name="Deep litter" dataDxfId="26" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{E8290DA2-F81B-417D-8DFF-811E04AE5CD6}" name="Deep litter" dataDxfId="7" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{8556C44B-D53C-43B5-AFA8-775CF9A97C5A}" name="Poultry manure with bedding" dataDxfId="25" dataCellStyle="Content normal">
+    <tableColumn id="11" xr3:uid="{8556C44B-D53C-43B5-AFA8-775CF9A97C5A}" name="Poultry manure with bedding" dataDxfId="6" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{6D7005A7-1332-4775-A075-04932CE4CB0C}" name="Poultry manure without bedding" dataDxfId="24" dataCellStyle="Content normal">
+    <tableColumn id="12" xr3:uid="{6D7005A7-1332-4775-A075-04932CE4CB0C}" name="Poultry manure without bedding" dataDxfId="5" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{CD24F3C7-0171-4241-9095-F217ACFB21FD}" name="Direct processing" dataDxfId="23" dataCellStyle="Content normal">
+    <tableColumn id="13" xr3:uid="{CD24F3C7-0171-4241-9095-F217ACFB21FD}" name="Direct processing" dataDxfId="4" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{B9A1E1BC-6DAC-4A86-933B-0394729DEF0D}" name="Direct application" dataDxfId="22" dataCellStyle="Content normal">
+    <tableColumn id="14" xr3:uid="{B9A1E1BC-6DAC-4A86-933B-0394729DEF0D}" name="Direct application" dataDxfId="3" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{D37545E7-3A7F-4E1D-9175-AF768DF5CDBB}" name="Pasture range and paddock" dataDxfId="21" dataCellStyle="Content normal">
+    <tableColumn id="15" xr3:uid="{D37545E7-3A7F-4E1D-9175-AF768DF5CDBB}" name="Pasture range and paddock" dataDxfId="2" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{01BDA555-814C-4F57-A554-B9E8D1197D3B}" name="MAT raw" dataDxfId="20" dataCellStyle="Content normal">
+    <tableColumn id="16" xr3:uid="{01BDA555-814C-4F57-A554-B9E8D1197D3B}" name="MAT raw" dataDxfId="1" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5367,7 +5368,7 @@
     <tableColumn id="1" xr3:uid="{FD1030A0-8423-4F54-A208-B8E2F9F2CCAF}" name="Climate Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{5D7849B7-3122-4868-94E6-53DB0ADF4E31}" name="EFNi &amp; EFN2Oi" dataDxfId="19" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{5D7849B7-3122-4868-94E6-53DB0ADF4E31}" name="EFNi &amp; EFN2Oi" dataDxfId="0" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5376,16 +5377,16 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{522C94C8-449D-4574-AF4D-39C274C53A6F}" name="Table_SourceData_OtherLivestock_NitrogenExcreted" displayName="Table_SourceData_OtherLivestock_NitrogenExcreted" ref="D39:E47" totalsRowShown="0" dataDxfId="14" dataCellStyle="Content normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{522C94C8-449D-4574-AF4D-39C274C53A6F}" name="Table_SourceData_OtherLivestock_NitrogenExcreted" displayName="Table_SourceData_OtherLivestock_NitrogenExcreted" ref="D39:E47" totalsRowShown="0" dataDxfId="50" dataCellStyle="Content normal">
   <autoFilter ref="D39:E47" xr:uid="{522C94C8-449D-4574-AF4D-39C274C53A6F}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{92CD5559-01AC-4144-B6DC-7F856864840C}" name="Other livestock type" dataDxfId="13" dataCellStyle="Content normal">
+    <tableColumn id="1" xr3:uid="{92CD5559-01AC-4144-B6DC-7F856864840C}" name="Other livestock type" dataDxfId="49" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_NitrogenExcreted_Data(),Table_SourceData_OtherLivestock_NitrogenExcreted[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{A4955FC2-927B-4DF6-B94C-068E74A6FF39}" name="NEj" dataDxfId="12" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{A4955FC2-927B-4DF6-B94C-068E74A6FF39}" name="NEj" dataDxfId="48" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_NitrogenExcreted_Data(),Table_SourceData_OtherLivestock_NitrogenExcreted[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5394,20 +5395,20 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{08C66B47-C28A-4E61-BD61-AB59792A938B}" name="Table_SourceData_OtherLivestock_AverageLiveweight" displayName="Table_SourceData_OtherLivestock_AverageLiveweight" ref="D54:F64" totalsRowShown="0" dataDxfId="11" dataCellStyle="Content normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{08C66B47-C28A-4E61-BD61-AB59792A938B}" name="Table_SourceData_OtherLivestock_AverageLiveweight" displayName="Table_SourceData_OtherLivestock_AverageLiveweight" ref="D54:F64" totalsRowShown="0" dataDxfId="47" dataCellStyle="Content normal">
   <autoFilter ref="D54:F64" xr:uid="{08C66B47-C28A-4E61-BD61-AB59792A938B}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{92B26601-57E2-4637-B097-133483C8744F}" name="Other livestock type" dataDxfId="10" dataCellStyle="Content normal">
+    <tableColumn id="1" xr3:uid="{92B26601-57E2-4637-B097-133483C8744F}" name="Other livestock type" dataDxfId="46" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_AverageLiveweight_Data(),Table_SourceData_OtherLivestock_AverageLiveweight[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{6D10B565-469B-4476-91DD-3E192D501AEC}" name="Wco" dataDxfId="9" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{6D10B565-469B-4476-91DD-3E192D501AEC}" name="Wco" dataDxfId="45" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_AverageLiveweight_Data(),Table_SourceData_OtherLivestock_AverageLiveweight[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{4285ACF1-A507-45A9-B06F-3C8A119CF7C4}" name="Wco2" dataDxfId="8" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{4285ACF1-A507-45A9-B06F-3C8A119CF7C4}" name="Wco2" dataDxfId="44" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_AverageLiveweight_Data(),Table_SourceData_OtherLivestock_AverageLiveweight[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5416,20 +5417,20 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{717E53D2-4463-4A85-80B5-5691AD7D98C8}" name="Table_SourceData_OtherLivestock_FractionWasteInMMS" displayName="Table_SourceData_OtherLivestock_FractionWasteInMMS" ref="D71:F79" totalsRowShown="0" dataDxfId="7" dataCellStyle="Content normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{717E53D2-4463-4A85-80B5-5691AD7D98C8}" name="Table_SourceData_OtherLivestock_FractionWasteInMMS" displayName="Table_SourceData_OtherLivestock_FractionWasteInMMS" ref="D71:F79" totalsRowShown="0" dataDxfId="43" dataCellStyle="Content normal">
   <autoFilter ref="D71:F79" xr:uid="{717E53D2-4463-4A85-80B5-5691AD7D98C8}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{3C1197CD-1D52-441D-BBC2-CD949C23252D}" name="Other livestock type" dataDxfId="6" dataCellStyle="Content normal">
+    <tableColumn id="1" xr3:uid="{3C1197CD-1D52-441D-BBC2-CD949C23252D}" name="Other livestock type" dataDxfId="42" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_FractionWasteInMMS_Data(),Table_SourceData_OtherLivestock_FractionWasteInMMS[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{8073D8FF-B3DA-4F6A-932F-294E074768D7}" name="Pasture range and paddock" dataDxfId="5" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{8073D8FF-B3DA-4F6A-932F-294E074768D7}" name="Pasture range and paddock" dataDxfId="41" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_FractionWasteInMMS_Data(),Table_SourceData_OtherLivestock_FractionWasteInMMS[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{BE446918-69F7-4B13-8457-24AF8D4D48BC}" name="Uncovered anaerobic lagoon" dataDxfId="4" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{BE446918-69F7-4B13-8457-24AF8D4D48BC}" name="Uncovered anaerobic lagoon" dataDxfId="40" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_FractionWasteInMMS_Data(),Table_SourceData_OtherLivestock_FractionWasteInMMS[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5438,20 +5439,20 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{AFA04BB4-DA20-428E-BF28-5455856D0A35}" name="Table_SourceData_OtherLivestock_MCF" displayName="Table_SourceData_OtherLivestock_MCF" ref="D86:F94" totalsRowShown="0" dataDxfId="3" dataCellStyle="Content normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{AFA04BB4-DA20-428E-BF28-5455856D0A35}" name="Table_SourceData_OtherLivestock_MCF" displayName="Table_SourceData_OtherLivestock_MCF" ref="D86:F94" totalsRowShown="0" dataDxfId="39" dataCellStyle="Content normal">
   <autoFilter ref="D86:F94" xr:uid="{AFA04BB4-DA20-428E-BF28-5455856D0A35}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{378D0529-B2BA-4B26-B22D-9D5AE994C705}" name="Other livestock type" dataDxfId="2" dataCellStyle="Content normal">
+    <tableColumn id="1" xr3:uid="{378D0529-B2BA-4B26-B22D-9D5AE994C705}" name="Other livestock type" dataDxfId="38" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_MethaneConversionFactor_Data(),Table_SourceData_OtherLivestock_MCF[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{614FC5E3-9067-4D7A-9048-5C785284F6FC}" name="Pasture range and paddock" dataDxfId="1" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{614FC5E3-9067-4D7A-9048-5C785284F6FC}" name="Pasture range and paddock" dataDxfId="37" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_MethaneConversionFactor_Data(),Table_SourceData_OtherLivestock_MCF[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{9125F130-A695-42FD-984B-66D9A47F338B}" name="Uncovered anaerobic lagoon" dataDxfId="0" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{9125F130-A695-42FD-984B-66D9A47F338B}" name="Uncovered anaerobic lagoon" dataDxfId="36" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_MethaneConversionFactor_Data(),Table_SourceData_OtherLivestock_MCF[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -20171,12 +20172,7 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACkAKgAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADIAKQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAHQAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAC8AdABcAHUAMAAwADMAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAdQAwADAAMgA3AFwAIgAgAFwAdQAwADAAMgA2ACAAcwBoACAAXAB1ADAAMAAyADYAIABcACIAXAB1ADAAMAAyADcAIQBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgAFwAdQAwADAAMgA2ACAAXAAiACAAXAAiACAAXAB1ADAAMAAyADYAIABUAGkAdABsAGUAQwBlAGwAbABcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAiACwAIgB0AGUAeAB0ACIAOgAiAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuADEAOgAgAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAALQAgAEUAbgB0AGUAcgBpAGMAIABmAGUAcgBtAGUAbgB0AGEAdABpAG8AbgAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABlAGEAYwBoACAAbwB0AGgAZQByACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlACAAKABrAGcAIABDAEgANAAvAGgAZQBhAGQALwB5AGUAYQByACkAIAAoAE0AagApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAARQBuAHQAZQByAGkAYwAgAGYAZQByAG0AZQBuAHQAYQB0AGkAbwBuACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGUAYQBjAGgAIABvAHQAaABlAHIAIABsAGkAdgBlAHMAdABvAGMAawAgAHQAeQBwAGUAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBqAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABDAEgANAAgAC8AIABoAGUAYQBkACAALwAgAHkAZQBhAHIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADUALgAxAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAyACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAAVAB5AHAAZQBcACIALAAgAFwAIgBNAGoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBmAGYAYQBsAG8AXAAiACwAIAA2ADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBvAGEAdABzAFwAIgAsACAANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGUAZQByAFwAIgAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAYQBtAGUAbABzAFwAIgAsACAANAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbABwAGEAYwBhAHMAXAAiACwAIAA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHMAZQBzAFwAIgAsACAAMQA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AdQBsAGUAcwAvAGEAcwBzAGUAcwBcACIALAAgADEAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AdQBzAC8AbwBzAHQAcgBpAGMAaABlAHMAXAAiACwAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAbwBkAHUAYwBlAGQAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuADIAOgAgAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAALQAgAFYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAcAByAG8AZAB1AGMAZQBkACAAYgB5ACAAZQBhAGMAaAAgAG8AdABoAGUAcgAgAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQAgACgAawBnACAAVgBTAC8AaABlAGEAZAAvAGQAYQB5ACkAIAAoAFYAUwBqACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAbwBkAHUAYwBlAGQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAALQAgAFYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAcAByAG8AZAB1AGMAZQBkACAAYgB5ACAAZQBhAGMAaAAgAG8AdABoAGUAcgAgAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAbwBkAHUAYwBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAUwBqAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBvAGQAdQBjAGUAZABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAFYAUwAgAC8AIABoAGUAYQBkACAALwAgAGQAYQB5AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBvAGQAdQBjAGUAZABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADUALgAyAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBvAGQAdQBjAGUAZABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAbwBkAHUAYwBlAGQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMgAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawAgAFQAeQBwAGUAXAAiACwAIABcACIAVgBTAGoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBmAGYAYQBsAG8AXAAiACwAIAAyAC4ANwAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAbwBhAHQAcwBcACIALAAgADAALgAzADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGUAcgBcACIALAAgADAALgA5ADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBhAG0AZQBsAHMAXAAiACwAIAAyAC4ANwAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbABwAGEAYwBhAHMAXAAiACwAIAAwAC4AMwA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHMAZQBzAFwAIgAsACAAMgAuADcAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAHUAbABlAHMALwBhAHMAcwBlAHMAXAAiACwAIAAwAC4AOQAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAbQB1AHMALwBvAHMAdAByAGkAYwBoAGUAcwBcACIALAAgADAALgAzADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABcAG4AVABhAGIAbABlACAAQQAuADEALgA1AC4AMwA6ACAATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAATgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAZQBkACAAcABlAHIAIABsAGkAdgBlAHMAdABvAGMAawAgAHQAeQBwAGUAIAAoAGsAZwAgAE4AMgBPAC8AaABlAGEAZAAvAHkAZQBhAHIAKQAgACgATgBFAGoAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAATgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAZQBkACAAcABlAHIAIABsAGkAdgBlAHMAdABvAGMAawAgAHQAeQBwAGUAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAEUAagBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC8AIABoAGUAYQBkACAALwAgAHkAZQBhAHIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuADMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAyACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAAVAB5AHAAZQBcACIALAAgAFwAIgBOAEUAagBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgB1AGYAZgBhAGwAbwBcACIALAAgADMAOQAuADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBvAGEAdABzAFwAIgAsACAANwAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGUAcgBcACIALAAgADEAMwAuADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBhAG0AZQBsAHMAXAAiACwAIAAzADkALgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbABwAGEAYwBhAHMAXAAiACwAIAA3AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgBzAGUAcwBcACIALAAgADMAOQAuADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQB1AGwAZQBzAC8AYQBzAHMAZQBzAFwAIgAsACAAMQAzAC4AMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AdQBzAC8AbwBzAHQAcgBpAGMAaABlAHMAXAAiACwAIAA3AC4AMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuADQAOgAgAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAALQAgAEEAdgBlAHIAYQBnAGUAIABMAGkAdgBlAHcAZQBpAGcAaAB0AHMAIAAoAFcAYwBvACkAIAAoAGsAZwApACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAAQQB2AGUAcgBhAGcAZQAgAEwAaQB2AGUAdwBlAGkAZwBoAHQAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVwBjAG8AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA1AC4ANABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADEALAAgADMALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIABUAHkAcABlACAAagBcACIALAAgAFwAIgBBAHYAZQByAGEAZwBlACAATABpAHYAZQB3AGUAaQBnAGgAdABcACIALAAgAFwAIgBBAHYAZQByAGEAZwBlACAATABpAHYAZQB3AGUAaQBnAGgAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgB1AGYAZgBhAGwAbwBcACIALAAgADMAMwA2ACwAIABcACIALQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBvAGEAdABzAFwAIgAsACAAMwAzACwAIABcACIAMgA4AGsAZwAgAC0AIABsAG8AdwAgAHAAcgBvAGQAdQBjAHQAaQB2AGkAdAB5ACAAcwB5AHMAdABlAG0AcwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBvAGEAdABzAFwAIgAsACAAMwAzACwAIABcACIANQAwAGsAZwAgAC0AIABoAGkAZwBoACAAcAByAG8AZAB1AGMAdABpAHYAaQB0AHkAIABzAHkAcwB0AGUAbQBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGUAZQByAFwAIgAsACAAMQAyADAALAAgADEAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAYQBtAGUAbABzAFwAIgAsACAAMgAxADcALAAgADUANwAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbABwAGEAYwBhAHMAXAAiACwAIABcACIALQBcACIALAAgADYANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgBzAGUAcwBcACIALAAgADMANwA3ACwAIAA1ADUAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAHUAbABlAHMALwBhAHMAcwBlAHMAXAAiACwAIAAxADMAMAAsACAAMgA0ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAHUAcwAvAG8AcwB0AHIAaQBjAGgAZQBzAFwAIgAsACAAMQAyADAALAAgADEAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBmAGUAcgBlAG4AYwBlAFwAIgAsACAAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAVABhAGIAbABlACAAMQAwAEEALgA1ACAAWwAyAF0AXAAiACwAIABcACIASQBQAEMAQwAgADIAMAAxADkAIABUAGEAYgBsAGUAIAAxADAALgAxADAAIABbADIAXQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwB0AGkAbwBuAFcAYQBzAHQAZQBJAG4ATQBNAFMAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuADUAOgAgAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAALQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHcAYQBzAHQAZQAgAGkAbgAgAGUAYQBjAGgAIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAIABzAHkAcwB0AGUAbQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0ATQBTAG0AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwB0AGkAbwBuAFcAYQBzAHQAZQBJAG4ATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAALQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHcAYQBzAHQAZQAgAGkAbgAgAGUAYQBjAGgAIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAIABzAHkAcwB0AGUAbQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMAdABpAG8AbgBXAGEAcwB0AGUASQBuAE0ATQBTAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE0AUwBtAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwB0AGkAbwBuAFcAYQBzAHQAZQBJAG4ATQBNAFMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAHQAaQBvAG4AVwBhAHMAdABlAEkAbgBNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADUALgA1AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwB0AGkAbwBuAFcAYQBzAHQAZQBJAG4ATQBNAFMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAHQAaQBvAG4AVwBhAHMAdABlAEkAbgBNAE0AUwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAzACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQBcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBDAFQAXAAiACwAIAAgADkAOQAuADYANgAsACAAIAAwAC4AMwA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AUwBXAFwAIgAsACAAIAA5ADkALgA2ADYALAAgACAAMAAuADMANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFQAXAAiACwAIAAgADkAOQAuADYANgAsACAAIAAwAC4AMwA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEATABEAFwAIgAsACAAIAA5ADkALgA2ADYALAAgACAAMAAuADMANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEEAXAAiACwAIAAgADkAOQAuADYANgAsACAAIAAwAC4AMwA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAQQBTAFwAIgAsACAAIAA5ADkALgA2ADYALAAgACAAMAAuADMANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEkAQwBcACIALAAgACAAOQA5AC4ANgA2ACwAIAAgADAALgAzADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBBAFwAIgAsACAAIAA5ADkALgA2ADYALAAgACAAMAAuADMANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuADYAOgAgAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAALQAgAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAHIAZQBnAGkAbwBuACAAKABmAHIAYQBjAHQAaQBvAG4AKQAgACgATQBDAEYAaQBtACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAcgBlAGcAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AQwBGAGkAbQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADUALgA2AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXAAiACwAIABcACIAVQBuAGMAbwB2AGUAcgBlAGQAIABBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAEMAVABcACIALAAgACAAMAAuADAAMAA0ADcALAAgACAAMAAuADcAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFMAVwBcACIALAAgACAAMAAuADAAMAA0ADcALAAgACAAMAAuADcANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFQAXAAiACwAIAAgADAALgAwADAANAA3ACwAIAAgADAALgA4ADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBMAEQAXAAiACwAIAAgADAALgAwADAANAA3ACwAIAAgADAALgA3ADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBAFwAIgAsACAAIAAwAC4AMAAwADQANwAsACAAIAAwAC4ANwA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAQQBTAFwAIgAsACAAIAAwAC4AMAAwADQANwAsACAAIAAwAC4ANwAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYASQBDAFwAIgAsACAAIAAwAC4AMAAwADQANwAsACAAIAAwAC4ANwA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAQQBcACIALAAgACAAMAAuADAAMAA0ADcALAAgACAAMAAuADcANgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADUALgBYADoAIABPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawAgAC0AIABNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbAAgACgAbQAzACAAQwBIADQAIAAvACAAawBnACAAVgBTACkAIAAoAEIATwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawAgAC0AIABNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEIATwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBtADMAIABDAEgANAAgAC8AIABrAGcAIABWAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuAFgAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgAgAFQAaABlAHIAZQAgAHcAZQByAGUAIABuAG8AIAB2AGEAbAB1AGUAcwAgAGkAbgAgAFYARQBFAFIARwAgAHMAbwAgAHQAaABpAHMAIABkAGEAdABhACAAaABhAHMAIABiAGUAZQBuACAAZwBlAG4AZQByAGEAdABlAGQAIABiAHkAIAB1AHMAaQBuAGcAIABkAG8AYwB1AG0AZQBuAHQAZQBkACAAQgBPACAAdgBhAGwAdQBlAHMAIABmAHIAbwBtACAAbwB0AGgAZQByACAAbABpAHYAZQBzAHQAbwBjAGsAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIABUAHkAcABlAFwAIgAsACAAXAAiAEIATwBcACIALAAgAFwAIgBUAGEAawBlAG4AIABmAHIAbwBtAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAHUAZgBmAGEAbABvAFwAIgAsACAAMAAuADEAOQAsACAAXAAiAEYAZQBlAGQAbABvAHQALAAgAFAAYQBzAHQAdQByAGUAIABiAGUAZQBmAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAG8AYQB0AHMAXAAiACwAIAAwAC4AMgA0ACwAIABcACIAUwBoAGUAZQBwAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGUAZQByAFwAIgAsACAAMAAuADIANAAsACAAXAAiAFMAaABlAGUAcABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBhAG0AZQBsAHMAXAAiACwAIAAwAC4AMgA0ACwAIABcACIAUwBoAGUAZQBwAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGwAcABhAGMAYQBzAFwAIgAsACAAMAAuADIANAAsACAAXAAiAFMAaABlAGUAcABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABvAHIAcwBlAHMAXAAiACwAIAAwAC4AMQA5ACwAIABcACIARgBlAGUAZABsAG8AdAAsACAAUABhAHMAdAB1AHIAZQAgAGIAZQBlAGYAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AdQBsAGUAcwAvAGEAcwBzAGUAcwBcACIALAAgADAALgAyADQALAAgAFwAIgBTAGgAZQBlAHAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAbQB1AHMALwBvAHMAdAByAGkAYwBoAGUAcwBcACIALAAgADAALgAzADYALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAALQAgAG0AZQBhAHQAIABjAGgAaQBjAGsAZQBuAHMAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMARwBBAFMATQBTAG8AaQBsAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABmAHIAbwBtACAAdQByAGkAbgBlACAAYQBuAGQAIABmAGEAZQBjAGUAcwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGYAcgBvAG0AIAB1AHIAaQBuAGUAIABhAG4AZAAgAGYAYQBlAGMAZQBzACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMARwBBAFMATQBzAG8AaQBsAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4ASAAzAC0ATgAgACsAIABOAE8AeAAtAE4AKQAvAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4ANwAuADIALgAzACAAQwBPAE4AUwBUAEEATgBUAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMARwBBAFMATQBTAG8AaQBsAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4AMgAxACkAOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADMALgA2ADoAIABFAG4AdABlAHIAaQBjACAATQBlAHQAaABhAG4AZQAgAC0AIABPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMwAuADYALgAxAC4AMQAgAE0AZQB0AGgAbwBkACAAMQAgAC0AIABFAG4AdABlAHIAaQBjACAATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAzAF8ANgBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBcAG4AVABvAHQAYQBsACAAYQBuAG4AdQBhAGwAIABtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABlAG4AdABlAHIAaQBjACAAZgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AIABpAG4AIABvAHQAaABlAHIAIABsAGkAdgBlAHMAdABvAGMAawBcAG4ARQBfAGUAbgB0AGUAcgBpAGMAXABuAHQAIABDAEgANABcAG4ARQBfAHsAZQBuAHQAZQByAGkAYwB9AD0AXABcAHMAdQBtAF8AagAoAE4AXwBqAFwAXAB0AGkAbQBlAHMAIABNAF8AagApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBOAF8AagAgAD0AIABuAHUAbQBiAGUAcgAgAG8AZgAgAGwAaQB2AGUAcwB0AG8AYwBrACAAbwBmACAAZQBhAGMAaAAgAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQAgAGoAIAAoAGgAZQBhAGQAKQBcAG4ATQBfAGoAIAA9ACAAZQBuAHQAZQByAGkAYwAgAGYAZQByAG0AZQBuAHQAYQB0AGkAbwBuACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIAAoAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAHkAZQBhAHIAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAzAF8ANgBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABOAF8AagAsACAATQBfAGoALABcAG4AIAAgACAAIABTAFUATQAoAE4AXwBqACAAKgAgAE0AXwBqACkAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwA2AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBUAG8AdABhAGwAIABhAG4AbgB1AGEAbAAgAG0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAGUAbgB0AGUAcgBpAGMAIABmAGUAcgBtAGUAbgB0AGEAdABpAG8AbgAgAGkAbgAgAG8AdABoAGUAcgAgAGwAaQB2AGUAcwB0AG8AYwBrAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8ANgBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAGUAbgB0AGUAcgBpAGMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwA2AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMASAA0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8ANgBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAzAC4ANgAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADYAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwA2AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsAZQBuAHQAZQByAGkAYwB9AD0AXABcAHMAdQBtAF8AagAoAE4AXwBqAFwAXAB0AGkAbQBlAHMAIABNAF8AagApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8ANgBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAF8AagBcACIALAAgAFwAIgBuAHUAbQBiAGUAcgAgAG8AZgAgAGwAaQB2AGUAcwB0AG8AYwBrACAAbwBmACAAZQBhAGMAaAAgAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQAgAGoAXAAiACwAIABcACIAaABlAGEAZABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AXwBqAFwAIgAsACAAXAAiAGUAbgB0AGUAcgBpAGMAIABmAGUAcgBtAGUAbgB0AGEAdABpAG8AbgAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAHkAZQBhAHIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBqAFwAIgAsACAAXAAiAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMQBfADIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADMAXwA0ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAbwBkAHUAYwBlAGQAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAG8AZAB1AGMAZQBkAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBvAGQAdQBjAGUAZABfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAG8AZAB1AGMAZQBkAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAG8AZAB1AGMAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAG8AZAB1AGMAZQBkAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMAdABpAG8AbgBXAGEAcwB0AGUASQBuAE0ATQBTAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwB0AGkAbwBuAFcAYQBzAHQAZQBJAG4ATQBNAFMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAHQAaQBvAG4AVwBhAHMAdABlAEkAbgBNAE0AUwBfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAHQAaQBvAG4AVwBhAHMAdABlAEkAbgBNAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwB0AGkAbwBuAFcAYQBzAHQAZQBJAG4ATQBNAFMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMAdABpAG8AbgBXAGEAcwB0AGUASQBuAE0ATQBTAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8ARABhAHQAYQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwA2AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADYAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8ANgBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwA2AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVQBuAGkAdAAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwA2AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8ANgBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADYAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADYAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBBAHIAZwB1AG0AZQBuAHQAcwAiAF0ALAAiAGwAbwBjAGEAbABlACIAOgB7ACIAbABpAHMAdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHIAbwB3AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAYwBvAGwAdQBtAG4AUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFAAbwBzAGkAdABpAG8AbgBzACIAOgBbADMAXQAsACIAZABlAGMAaQBtAGEAbABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAuACIALAAiAGQAYQB0AGUATwByAGQAZQByACIAOgAiAEQATQBZACIALAAiAGMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbAAiADoAIgAkACIALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwATABlAGEAZAAiADoAdAByAHUAZQAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAGUAcABCAHkAUwBwAGEAYwBlACIAOgBmAGEAbABzAGUALAAiAHIAbwB3AEwAZQB0AHQAZQByACIAOgAiAFIAIgAsACIAYwBvAGwAdQBtAG4ATABlAHQAdABlAHIAIgA6ACIAQwAiACwAIgByAGMATABlAGYAdABCAHIAYQBjAGsAZQB0ACIAOgAiAFsAIgAsACIAcgBjAFIAaQBnAGgAdABCAHIAYQBjAGsAZQB0ACIAOgAiAF0AIgAsACIAcwB0AGEAdABlAG0AZQBuAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBsAG8AYwBhAGwAZQBOAGEAbQBlACIAOgAiAGUAbgAtAHUAcwAiAH0AfQA=</AFEJSONBlob>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -20375,7 +20371,12 @@
 </file>
 
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACkAKgAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADIAKQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAHQAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAC8AdABcAHUAMAAwADMAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAdQAwADAAMgA3AFwAIgAgAFwAdQAwADAAMgA2ACAAcwBoACAAXAB1ADAAMAAyADYAIABcACIAXAB1ADAAMAAyADcAIQBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgAFwAdQAwADAAMgA2ACAAXAAiACAAXAAiACAAXAB1ADAAMAAyADYAIABUAGkAdABsAGUAQwBlAGwAbABcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAiACwAIgB0AGUAeAB0ACIAOgAiAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuADEAOgAgAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAALQAgAEUAbgB0AGUAcgBpAGMAIABmAGUAcgBtAGUAbgB0AGEAdABpAG8AbgAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABlAGEAYwBoACAAbwB0AGgAZQByACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlACAAKABrAGcAIABDAEgANAAvAGgAZQBhAGQALwB5AGUAYQByACkAIAAoAE0AagApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAARQBuAHQAZQByAGkAYwAgAGYAZQByAG0AZQBuAHQAYQB0AGkAbwBuACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGUAYQBjAGgAIABvAHQAaABlAHIAIABsAGkAdgBlAHMAdABvAGMAawAgAHQAeQBwAGUAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBqAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABDAEgANAAgAC8AIABoAGUAYQBkACAALwAgAHkAZQBhAHIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADUALgAxAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAyACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAAVAB5AHAAZQBcACIALAAgAFwAIgBNAGoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBmAGYAYQBsAG8AXAAiACwAIAA2ADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBvAGEAdABzAFwAIgAsACAANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGUAZQByAFwAIgAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAYQBtAGUAbABzAFwAIgAsACAANAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbABwAGEAYwBhAHMAXAAiACwAIAA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHMAZQBzAFwAIgAsACAAMQA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AdQBsAGUAcwAvAGEAcwBzAGUAcwBcACIALAAgADEAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AdQBzAC8AbwBzAHQAcgBpAGMAaABlAHMAXAAiACwAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAbwBkAHUAYwBlAGQAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuADIAOgAgAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAALQAgAFYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAcAByAG8AZAB1AGMAZQBkACAAYgB5ACAAZQBhAGMAaAAgAG8AdABoAGUAcgAgAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQAgACgAawBnACAAVgBTAC8AaABlAGEAZAAvAGQAYQB5ACkAIAAoAFYAUwBqACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAbwBkAHUAYwBlAGQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAALQAgAFYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAcAByAG8AZAB1AGMAZQBkACAAYgB5ACAAZQBhAGMAaAAgAG8AdABoAGUAcgAgAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAbwBkAHUAYwBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAUwBqAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBvAGQAdQBjAGUAZABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAFYAUwAgAC8AIABoAGUAYQBkACAALwAgAGQAYQB5AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBvAGQAdQBjAGUAZABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADUALgAyAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBvAGQAdQBjAGUAZABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAbwBkAHUAYwBlAGQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMgAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawAgAFQAeQBwAGUAXAAiACwAIABcACIAVgBTAGoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBmAGYAYQBsAG8AXAAiACwAIAAyAC4ANwAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAbwBhAHQAcwBcACIALAAgADAALgAzADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGUAcgBcACIALAAgADAALgA5ADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBhAG0AZQBsAHMAXAAiACwAIAAyAC4ANwAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbABwAGEAYwBhAHMAXAAiACwAIAAwAC4AMwA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHMAZQBzAFwAIgAsACAAMgAuADcAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAHUAbABlAHMALwBhAHMAcwBlAHMAXAAiACwAIAAwAC4AOQAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAbQB1AHMALwBvAHMAdAByAGkAYwBoAGUAcwBcACIALAAgADAALgAzADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABcAG4AVABhAGIAbABlACAAQQAuADEALgA1AC4AMwA6ACAATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAATgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAZQBkACAAcABlAHIAIABsAGkAdgBlAHMAdABvAGMAawAgAHQAeQBwAGUAIAAoAGsAZwAgAE4AMgBPAC8AaABlAGEAZAAvAHkAZQBhAHIAKQAgACgATgBFAGoAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAATgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAZQBkACAAcABlAHIAIABsAGkAdgBlAHMAdABvAGMAawAgAHQAeQBwAGUAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAEUAagBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC8AIABoAGUAYQBkACAALwAgAHkAZQBhAHIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuADMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAyACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAAVAB5AHAAZQBcACIALAAgAFwAIgBOAEUAagBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgB1AGYAZgBhAGwAbwBcACIALAAgADMAOQAuADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBvAGEAdABzAFwAIgAsACAANwAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGUAcgBcACIALAAgADEAMwAuADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBhAG0AZQBsAHMAXAAiACwAIAAzADkALgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbABwAGEAYwBhAHMAXAAiACwAIAA3AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgBzAGUAcwBcACIALAAgADMAOQAuADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQB1AGwAZQBzAC8AYQBzAHMAZQBzAFwAIgAsACAAMQAzAC4AMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AdQBzAC8AbwBzAHQAcgBpAGMAaABlAHMAXAAiACwAIAA3AC4AMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuADQAOgAgAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAALQAgAEEAdgBlAHIAYQBnAGUAIABMAGkAdgBlAHcAZQBpAGcAaAB0AHMAIAAoAFcAYwBvACkAIAAoAGsAZwApACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAAQQB2AGUAcgBhAGcAZQAgAEwAaQB2AGUAdwBlAGkAZwBoAHQAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVwBjAG8AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA1AC4ANABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADEALAAgADMALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIABUAHkAcABlACAAagBcACIALAAgAFwAIgBBAHYAZQByAGEAZwBlACAATABpAHYAZQB3AGUAaQBnAGgAdABcACIALAAgAFwAIgBBAHYAZQByAGEAZwBlACAATABpAHYAZQB3AGUAaQBnAGgAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgB1AGYAZgBhAGwAbwBcACIALAAgADMAMwA2ACwAIABcACIALQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBvAGEAdABzAFwAIgAsACAAMwAzACwAIABcACIAMgA4AGsAZwAgAC0AIABsAG8AdwAgAHAAcgBvAGQAdQBjAHQAaQB2AGkAdAB5ACAAcwB5AHMAdABlAG0AcwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBvAGEAdABzAFwAIgAsACAAMwAzACwAIABcACIANQAwAGsAZwAgAC0AIABoAGkAZwBoACAAcAByAG8AZAB1AGMAdABpAHYAaQB0AHkAIABzAHkAcwB0AGUAbQBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGUAZQByAFwAIgAsACAAMQAyADAALAAgADEAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAYQBtAGUAbABzAFwAIgAsACAAMgAxADcALAAgADUANwAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbABwAGEAYwBhAHMAXAAiACwAIABcACIALQBcACIALAAgADYANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgBzAGUAcwBcACIALAAgADMANwA3ACwAIAA1ADUAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAHUAbABlAHMALwBhAHMAcwBlAHMAXAAiACwAIAAxADMAMAAsACAAMgA0ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAHUAcwAvAG8AcwB0AHIAaQBjAGgAZQBzAFwAIgAsACAAMQAyADAALAAgADEAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBmAGUAcgBlAG4AYwBlAFwAIgAsACAAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAVABhAGIAbABlACAAMQAwAEEALgA1ACAAWwAyAF0AXAAiACwAIABcACIASQBQAEMAQwAgADIAMAAxADkAIABUAGEAYgBsAGUAIAAxADAALgAxADAAIABbADIAXQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwB0AGkAbwBuAFcAYQBzAHQAZQBJAG4ATQBNAFMAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuADUAOgAgAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAALQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHcAYQBzAHQAZQAgAGkAbgAgAGUAYQBjAGgAIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAIABzAHkAcwB0AGUAbQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0ATQBTAG0AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwB0AGkAbwBuAFcAYQBzAHQAZQBJAG4ATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAALQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHcAYQBzAHQAZQAgAGkAbgAgAGUAYQBjAGgAIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAIABzAHkAcwB0AGUAbQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMAdABpAG8AbgBXAGEAcwB0AGUASQBuAE0ATQBTAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE0AUwBtAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwB0AGkAbwBuAFcAYQBzAHQAZQBJAG4ATQBNAFMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAHQAaQBvAG4AVwBhAHMAdABlAEkAbgBNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADUALgA1AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwB0AGkAbwBuAFcAYQBzAHQAZQBJAG4ATQBNAFMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAHQAaQBvAG4AVwBhAHMAdABlAEkAbgBNAE0AUwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAzACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQBcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBDAFQAXAAiACwAIAAgADkAOQAuADYANgAsACAAIAAwAC4AMwA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AUwBXAFwAIgAsACAAIAA5ADkALgA2ADYALAAgACAAMAAuADMANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFQAXAAiACwAIAAgADkAOQAuADYANgAsACAAIAAwAC4AMwA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEATABEAFwAIgAsACAAIAA5ADkALgA2ADYALAAgACAAMAAuADMANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEEAXAAiACwAIAAgADkAOQAuADYANgAsACAAIAAwAC4AMwA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAQQBTAFwAIgAsACAAIAA5ADkALgA2ADYALAAgACAAMAAuADMANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEkAQwBcACIALAAgACAAOQA5AC4ANgA2ACwAIAAgADAALgAzADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBBAFwAIgAsACAAIAA5ADkALgA2ADYALAAgACAAMAAuADMANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuADYAOgAgAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAALQAgAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAHIAZQBnAGkAbwBuACAAKABmAHIAYQBjAHQAaQBvAG4AKQAgACgATQBDAEYAaQBtACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAcgBlAGcAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AQwBGAGkAbQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADUALgA2AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXAAiACwAIABcACIAVQBuAGMAbwB2AGUAcgBlAGQAIABBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAEMAVABcACIALAAgACAAMAAuADAAMAA0ADcALAAgACAAMAAuADcAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFMAVwBcACIALAAgACAAMAAuADAAMAA0ADcALAAgACAAMAAuADcANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFQAXAAiACwAIAAgADAALgAwADAANAA3ACwAIAAgADAALgA4ADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBMAEQAXAAiACwAIAAgADAALgAwADAANAA3ACwAIAAgADAALgA3ADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBAFwAIgAsACAAIAAwAC4AMAAwADQANwAsACAAIAAwAC4ANwA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAQQBTAFwAIgAsACAAIAAwAC4AMAAwADQANwAsACAAIAAwAC4ANwAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYASQBDAFwAIgAsACAAIAAwAC4AMAAwADQANwAsACAAIAAwAC4ANwA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAQQBcACIALAAgACAAMAAuADAAMAA0ADcALAAgACAAMAAuADcANgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADUALgBYADoAIABPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawAgAC0AIABNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbAAgACgAbQAzACAAQwBIADQAIAAvACAAawBnACAAVgBTACkAIAAoAEIATwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawAgAC0AIABNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEIATwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBtADMAIABDAEgANAAgAC8AIABrAGcAIABWAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuAFgAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgAgAFQAaABlAHIAZQAgAHcAZQByAGUAIABuAG8AIAB2AGEAbAB1AGUAcwAgAGkAbgAgAFYARQBFAFIARwAgAHMAbwAgAHQAaABpAHMAIABkAGEAdABhACAAaABhAHMAIABiAGUAZQBuACAAZwBlAG4AZQByAGEAdABlAGQAIABiAHkAIAB1AHMAaQBuAGcAIABkAG8AYwB1AG0AZQBuAHQAZQBkACAAQgBPACAAdgBhAGwAdQBlAHMAIABmAHIAbwBtACAAbwB0AGgAZQByACAAbABpAHYAZQBzAHQAbwBjAGsAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIABUAHkAcABlAFwAIgAsACAAXAAiAEIATwBcACIALAAgAFwAIgBUAGEAawBlAG4AIABmAHIAbwBtAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAHUAZgBmAGEAbABvAFwAIgAsACAAMAAuADEAOQAsACAAXAAiAEYAZQBlAGQAbABvAHQALAAgAFAAYQBzAHQAdQByAGUAIABiAGUAZQBmAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAG8AYQB0AHMAXAAiACwAIAAwAC4AMgA0ACwAIABcACIAUwBoAGUAZQBwAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGUAZQByAFwAIgAsACAAMAAuADIANAAsACAAXAAiAFMAaABlAGUAcABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBhAG0AZQBsAHMAXAAiACwAIAAwAC4AMgA0ACwAIABcACIAUwBoAGUAZQBwAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGwAcABhAGMAYQBzAFwAIgAsACAAMAAuADIANAAsACAAXAAiAFMAaABlAGUAcABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABvAHIAcwBlAHMAXAAiACwAIAAwAC4AMQA5ACwAIABcACIARgBlAGUAZABsAG8AdAAsACAAUABhAHMAdAB1AHIAZQAgAGIAZQBlAGYAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AdQBsAGUAcwAvAGEAcwBzAGUAcwBcACIALAAgADAALgAyADQALAAgAFwAIgBTAGgAZQBlAHAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAbQB1AHMALwBvAHMAdAByAGkAYwBoAGUAcwBcACIALAAgADAALgAzADYALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAALQAgAG0AZQBhAHQAIABjAGgAaQBjAGsAZQBuAHMAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMARwBBAFMATQBTAG8AaQBsAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABmAHIAbwBtACAAdQByAGkAbgBlACAAYQBuAGQAIABmAGEAZQBjAGUAcwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGYAcgBvAG0AIAB1AHIAaQBuAGUAIABhAG4AZAAgAGYAYQBlAGMAZQBzACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMARwBBAFMATQBzAG8AaQBsAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4ASAAzAC0ATgAgACsAIABOAE8AeAAtAE4AKQAvAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4ANwAuADIALgAzACAAQwBPAE4AUwBUAEEATgBUAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMARwBBAFMATQBTAG8AaQBsAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4AMgAxACkAOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADMALgA2ADoAIABFAG4AdABlAHIAaQBjACAATQBlAHQAaABhAG4AZQAgAC0AIABPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMwAuADYALgAxAC4AMQAgAE0AZQB0AGgAbwBkACAAMQAgAC0AIABFAG4AdABlAHIAaQBjACAATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAzAF8ANgBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBcAG4AVABvAHQAYQBsACAAYQBuAG4AdQBhAGwAIABtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABlAG4AdABlAHIAaQBjACAAZgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AIABpAG4AIABvAHQAaABlAHIAIABsAGkAdgBlAHMAdABvAGMAawBcAG4ARQBfAGUAbgB0AGUAcgBpAGMAXABuAHQAIABDAEgANABcAG4ARQBfAHsAZQBuAHQAZQByAGkAYwB9AD0AXABcAHMAdQBtAF8AagAoAE4AXwBqAFwAXAB0AGkAbQBlAHMAIABNAF8AagApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBOAF8AagAgAD0AIABuAHUAbQBiAGUAcgAgAG8AZgAgAGwAaQB2AGUAcwB0AG8AYwBrACAAbwBmACAAZQBhAGMAaAAgAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQAgAGoAIAAoAGgAZQBhAGQAKQBcAG4ATQBfAGoAIAA9ACAAZQBuAHQAZQByAGkAYwAgAGYAZQByAG0AZQBuAHQAYQB0AGkAbwBuACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIAAoAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAHkAZQBhAHIAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAzAF8ANgBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABOAF8AagAsACAATQBfAGoALABcAG4AIAAgACAAIABTAFUATQAoAE4AXwBqACAAKgAgAE0AXwBqACkAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwA2AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBUAG8AdABhAGwAIABhAG4AbgB1AGEAbAAgAG0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAGUAbgB0AGUAcgBpAGMAIABmAGUAcgBtAGUAbgB0AGEAdABpAG8AbgAgAGkAbgAgAG8AdABoAGUAcgAgAGwAaQB2AGUAcwB0AG8AYwBrAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8ANgBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAGUAbgB0AGUAcgBpAGMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwA2AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMASAA0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8ANgBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAzAC4ANgAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADYAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwA2AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsAZQBuAHQAZQByAGkAYwB9AD0AXABcAHMAdQBtAF8AagAoAE4AXwBqAFwAXAB0AGkAbQBlAHMAIABNAF8AagApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8ANgBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAF8AagBcACIALAAgAFwAIgBuAHUAbQBiAGUAcgAgAG8AZgAgAGwAaQB2AGUAcwB0AG8AYwBrACAAbwBmACAAZQBhAGMAaAAgAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQAgAGoAXAAiACwAIABcACIAaABlAGEAZABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AXwBqAFwAIgAsACAAXAAiAGUAbgB0AGUAcgBpAGMAIABmAGUAcgBtAGUAbgB0AGEAdABpAG8AbgAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAHkAZQBhAHIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBqAFwAIgAsACAAXAAiAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMQBfADIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADMAXwA0ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAbwBkAHUAYwBlAGQAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAG8AZAB1AGMAZQBkAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBvAGQAdQBjAGUAZABfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAG8AZAB1AGMAZQBkAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAG8AZAB1AGMAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAG8AZAB1AGMAZQBkAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMAdABpAG8AbgBXAGEAcwB0AGUASQBuAE0ATQBTAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwB0AGkAbwBuAFcAYQBzAHQAZQBJAG4ATQBNAFMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAHQAaQBvAG4AVwBhAHMAdABlAEkAbgBNAE0AUwBfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAHQAaQBvAG4AVwBhAHMAdABlAEkAbgBNAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwB0AGkAbwBuAFcAYQBzAHQAZQBJAG4ATQBNAFMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMAdABpAG8AbgBXAGEAcwB0AGUASQBuAE0ATQBTAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8ARABhAHQAYQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwA2AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADYAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8ANgBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwA2AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVQBuAGkAdAAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwA2AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8ANgBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADYAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADYAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBBAHIAZwB1AG0AZQBuAHQAcwAiAF0ALAAiAGwAbwBjAGEAbABlACIAOgB7ACIAbABpAHMAdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHIAbwB3AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAYwBvAGwAdQBtAG4AUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFAAbwBzAGkAdABpAG8AbgBzACIAOgBbADMAXQAsACIAZABlAGMAaQBtAGEAbABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAuACIALAAiAGQAYQB0AGUATwByAGQAZQByACIAOgAiAEQATQBZACIALAAiAGMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbAAiADoAIgAkACIALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwATABlAGEAZAAiADoAdAByAHUAZQAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAGUAcABCAHkAUwBwAGEAYwBlACIAOgBmAGEAbABzAGUALAAiAHIAbwB3AEwAZQB0AHQAZQByACIAOgAiAFIAIgAsACIAYwBvAGwAdQBtAG4ATABlAHQAdABlAHIAIgA6ACIAQwAiACwAIgByAGMATABlAGYAdABCAHIAYQBjAGsAZQB0ACIAOgAiAFsAIgAsACIAcgBjAFIAaQBnAGgAdABCAHIAYQBjAGsAZQB0ACIAOgAiAF0AIgAsACIAcwB0AGEAdABlAG0AZQBuAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBsAG8AYwBhAGwAZQBOAGEAbQBlACIAOgAiAGUAbgAtAHUAcwAiAH0AfQA=</AFEJSONBlob>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -20390,9 +20391,9 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -20417,9 +20418,9 @@
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Excel/3_6_Enteric_OtherLivestock_WIP_v01.xlsx
+++ b/Excel/3_6_Enteric_OtherLivestock_WIP_v01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C81702B8-4F57-49AC-B39F-97B65B3C9083}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5D35173-58DB-4542-9057-97609E4CE684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1350" yWindow="360" windowWidth="36255" windowHeight="19140" firstSheet="1" activeTab="5" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="5070" yWindow="5070" windowWidth="28800" windowHeight="15345" firstSheet="7" activeTab="7" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -20,10 +20,13 @@
     <sheet name="Input - Other Livestock" sheetId="70" r:id="rId5"/>
     <sheet name="3.6.1.1-2 Enteric Methane" sheetId="69" r:id="rId6"/>
     <sheet name="Constants - Other Livestock" sheetId="79" r:id="rId7"/>
-    <sheet name="Constants - Common" sheetId="102" r:id="rId8"/>
+    <sheet name="Constants - Common" sheetId="103" r:id="rId8"/>
     <sheet name="Acknowledgements" sheetId="72" r:id="rId9"/>
     <sheet name="Tab template" sheetId="74" r:id="rId10"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId11"/>
+  </externalReferences>
   <definedNames>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e">_xlfn.LAMBDA(_xlpm.E_CH4,_xlpm.GWP_CH4, _xlpm.E_CH4 * _xlpm.GWP_CH4)</definedName>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"ECH4","Methane emissions (t CH4)";"GWPCH4","Global warming potential for methane (t CO2-e / t CH4)"}, _xlpm.r, _xlpm.c))))</definedName>
@@ -4872,6 +4875,26 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Home"/>
+      <sheetName val="Constants - Common"/>
+      <sheetName val="Acknowledgements"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
 <rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
   <global>
@@ -4955,7 +4978,7 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{971AF780-EF58-40FF-A830-4A54D473212F}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{F8907E06-24A3-4B63-9B35-35544CF85B8C}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
   <autoFilter ref="D47:H54" xr:uid="{C1F562BB-DAA6-45BB-951A-7BAFA5B64B45}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4964,19 +4987,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{FA2AB5E5-72DD-48EA-A441-7826E274BEFA}" name="Gas">
+    <tableColumn id="1" xr3:uid="{F10AEE33-33A1-4784-A103-45A46FF00750}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{C069A4B0-ECBC-487A-9D3E-D40BCB3AFE2D}" name="Conversion factor">
+    <tableColumn id="5" xr3:uid="{FB985C6C-9A57-4728-8A1D-A4B334EAB2D3}" name="Conversion factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{6F9E09B3-0380-428A-9CB8-C5355F18AB24}" name="Conversion factor 1">
+    <tableColumn id="2" xr3:uid="{39778934-D8C3-4849-8ED2-BA00D76EDCDD}" name="Conversion factor 1">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{D99DCAD2-B15F-455D-A39D-C0CB7872FAC8}" name="Conversion factor 2">
+    <tableColumn id="3" xr3:uid="{53884F08-CB41-4605-96D1-9F4C10B9CED2}" name="Conversion factor 2">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{479D1385-10B4-4C3D-812C-B3ADC8B6446F}" name="Conversion factor combined">
+    <tableColumn id="4" xr3:uid="{2F5081F7-E116-40DC-A617-AC8C21BB4CCE}" name="Conversion factor combined">
       <calculatedColumnFormula>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4985,7 +5008,7 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{C571E06B-2FB6-4DCB-9306-6E8B7E50DF11}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{6DD7CF1D-5318-4AB4-8F15-2AFBBC8A683C}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
   <autoFilter ref="D89:S97" xr:uid="{5A437AE9-7724-4CF2-ACCF-291078682FB9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5005,52 +5028,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{C1368F08-D067-4EEC-B0CC-D2E1F6D93274}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{7E71225E-2AD7-4A13-9EBB-B77F4079285C}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{773305BF-D908-4C35-A934-C13BC9D3D8FF}" name="MAT" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{A2DABE99-D6E4-4F5F-8878-5C1A1B6DCCBE}" name="MAT" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{DF05DA85-723A-420A-AA03-0A716BECCE22}" name="MAP" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
+    <tableColumn id="3" xr3:uid="{1B47ADC6-A8AF-44F6-9AC5-EAD632F652DF}" name="MAP" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{8B8F9D2B-3A8F-44F1-9417-280165AE86AB}" name="Frost days per year" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
+    <tableColumn id="4" xr3:uid="{DE25E49E-3CF4-484F-8E89-D3FA3D6646DC}" name="Frost days per year" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{31B1CBF8-C757-4A17-AD4E-3FED04A08D97}" name="Elevation" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
+    <tableColumn id="5" xr3:uid="{DAFC64A1-71DE-411E-BC93-E39255D47108}" name="Elevation" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{9F5D51C1-ECC4-49B6-A4BE-AE3B3C663E64}" name="MAP:PET" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
+    <tableColumn id="6" xr3:uid="{47FF84A2-6ECF-4E1E-897C-42257F6A9039}" name="MAP:PET" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{874F3D25-0748-4359-BEF3-58E34D4DFAA6}" name="Min temp" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
+    <tableColumn id="7" xr3:uid="{3E12B9C0-0D6B-456A-BF36-2B1551835148}" name="Min temp" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{79652299-3198-47E6-B342-A54F0A0B3674}" name="Max temp" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
+    <tableColumn id="8" xr3:uid="{D9AE84AF-8B12-46DD-ABEA-2CE6983DE305}" name="Max temp" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{A0139A89-1186-4484-B833-03C424C4D2C4}" name="Min rainfall" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
+    <tableColumn id="9" xr3:uid="{99F753C3-10C2-4AC4-B605-80BD63E4793E}" name="Min rainfall" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{BD7A797C-3EEA-481F-9533-984ECCA62AC3}" name="Max rainfall" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
+    <tableColumn id="10" xr3:uid="{4D621138-C2ED-4858-BE43-B60126D7AE6D}" name="Max rainfall" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{29123C0E-9E60-43AB-8679-2AC0908200D0}" name="Min frost days" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
+    <tableColumn id="11" xr3:uid="{D0553375-7408-4726-A780-70F59A49CEBA}" name="Min frost days" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{04AF6D35-FBEF-4E38-B28D-0C23F8EDC5F6}" name="Max frost days" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
+    <tableColumn id="15" xr3:uid="{74E64BFF-B8FC-419E-8F74-484BBCE09FE7}" name="Max frost days" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{475991F7-F3B5-4EEA-966A-7AA8BC301814}" name="Min elevation" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
+    <tableColumn id="12" xr3:uid="{D47CB08C-DF83-4939-AEF0-82A4FA878F89}" name="Min elevation" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{767BBD4C-C554-4460-AAD8-ECADA490C9C0}" name="Max elevation" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
+    <tableColumn id="16" xr3:uid="{927942D3-9732-4B14-B047-72AD90A713EC}" name="Max elevation" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{65D9D85B-649F-4683-B866-BF022CDF3E13}" name="Min MAP:PET" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
+    <tableColumn id="13" xr3:uid="{3096D6DC-E1EC-4C1B-9F1C-ED4C1687545C}" name="Min MAP:PET" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{969B2D30-E5CD-48F6-AF2A-DAC6295F1FF1}" name="Max MAP:PET" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
+    <tableColumn id="17" xr3:uid="{52FE9F47-7322-43C7-A986-BC8D24B6A4DF}" name="Max MAP:PET" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5059,16 +5082,16 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{DDDF37ED-9327-4273-B740-938A1214436F}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{ADAFFE97-F414-4A1C-95BF-7E241C2AF545}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
   <autoFilter ref="D63:E77" xr:uid="{3597E019-B21E-4B76-BCC8-D02D497BCFA9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{26F7317C-9F68-4F62-B737-D7ABF2DFF387}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{CFB94993-7174-41FB-A95E-C8EB63EEBCF2}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{229B1B14-5629-4B1C-9602-463A80BF745E}" name="Wet or Dry Zone" totalsRowDxfId="20" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{159EDF8D-44CA-4285-BE19-435BFAD5D869}" name="Wet or Dry Zone" totalsRowDxfId="20" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5077,7 +5100,7 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{190E8CDE-696F-471D-B4F7-D0F3BE6AD6E3}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{198DD7C1-717B-47ED-B033-072E92325DC7}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
   <autoFilter ref="D109:G112" xr:uid="{AB16FEAB-AB03-45E1-BBD4-66D29CD412DF}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5085,16 +5108,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{A767FA53-E454-4115-A4B3-DED062EED278}" name="Temperature Zone">
+    <tableColumn id="1" xr3:uid="{15249D77-C527-4243-BDC5-D85B90EBEDCF}" name="Temperature Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{28532D1E-227F-4FEB-818C-7F2BC92126D0}" name="MAT">
+    <tableColumn id="2" xr3:uid="{1BEF6A38-01E7-41BD-AEDC-585B9A3BE1A2}" name="MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{45E163CE-3902-4B82-B9CC-59620B4E4ED4}" name="Min MAT">
+    <tableColumn id="3" xr3:uid="{235583DE-24C1-4222-BD4E-12AF5DD005EF}" name="Min MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{96F2EA78-ED18-493D-8A43-55427191118E}" name="Max MAT">
+    <tableColumn id="4" xr3:uid="{E933E30D-BF18-4A78-A58E-69788473C25D}" name="Max MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5103,7 +5126,7 @@
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{78354839-706C-4F2B-BF62-2EF4D3DA4D6A}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{14180E87-4968-49CD-9FBA-89BD7CED69EF}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
   <autoFilter ref="D119:G121" xr:uid="{E08772F3-2E8C-40A8-B755-08A5BBDF4130}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5111,16 +5134,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{587CE355-CB72-4F48-96ED-6DC9E1A54DA9}" name="Rainfall Zone">
+    <tableColumn id="1" xr3:uid="{6CFAD644-5E39-4A56-A1A1-5EF1589A5431}" name="Rainfall Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{CF57602B-CA70-4AA7-94E6-9CE1D9C8C294}" name="Annual rainfall">
+    <tableColumn id="2" xr3:uid="{362EBAFC-9548-4309-BCD4-98188FD0C698}" name="Annual rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{6165D635-272A-4C24-B337-38B8A33057DA}" name="Min rainfall">
+    <tableColumn id="3" xr3:uid="{F4EA4661-A080-4541-B198-F3C458976718}" name="Min rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{02DC014A-F442-41A1-82FF-EFC4545791D6}" name="Max rainfall">
+    <tableColumn id="4" xr3:uid="{55B3C3CC-6CE3-49C8-B07D-7BA34EE71329}" name="Max rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5129,16 +5152,16 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{38538017-FC63-4011-82EC-704266C8D2C4}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{30557839-31F1-4F02-8584-29899F4EE7C2}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
   <autoFilter ref="D127:E129" xr:uid="{A159E140-02ED-4547-B6E1-6695D8B16A11}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{DFAA5237-AAFB-4DF9-9DA3-DCD93FAB1DC5}" name="Leaching Zone">
+    <tableColumn id="1" xr3:uid="{7734C83F-429E-4CD6-91B1-AC88CC9A0866}" name="Leaching Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{A09764E1-6E11-4B1C-B1F1-FEBC49B8E8D3}" name="Leaching criteria">
+    <tableColumn id="2" xr3:uid="{31653424-A28F-4826-B497-6FD9EEFA4766}" name="Leaching criteria">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5147,16 +5170,16 @@
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{1853BA63-FF03-4462-8DF7-1B181A1E988D}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{17D93532-9A05-4CD2-B456-9152AFC9664E}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
   <autoFilter ref="D153:E158" xr:uid="{133D42B0-F6D2-470A-858A-37E6A7F5EC2B}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{42863E7D-F37C-4BA5-9E68-29F1E38F6FDA}" name="Data source">
+    <tableColumn id="1" xr3:uid="{9DC23329-7FE9-4DD5-8F53-FA51BCC60E67}" name="Data source">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{4991511C-C30A-414A-A986-F9F2B5CC50FF}" name="Data score">
+    <tableColumn id="2" xr3:uid="{71DCDCF6-5937-42CC-B176-B8837A5370B2}" name="Data score">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5165,16 +5188,16 @@
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="33" xr:uid="{73AEE5E4-934C-4F38-B902-F08C65D152AC}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{6A955474-12E6-4289-9F11-178BEF9B65C8}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
   <autoFilter ref="D134:E136" xr:uid="{308E99BE-FE1F-47A4-B2CA-97217277C4E9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{C06588B3-DEB9-485D-8845-44DC96AA1C03}" name="Is in leaching zone">
+    <tableColumn id="1" xr3:uid="{81AD69B2-0790-418B-B2FC-CDA6FAB17038}" name="Is in leaching zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{0CB971CE-8314-492D-B32B-05442AFAE65D}" name="FracWET" dataDxfId="19">
+    <tableColumn id="2" xr3:uid="{0C4BCEEC-FFEA-4FEA-BB22-952F61FA30A4}" name="FracWET" dataDxfId="19">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5183,7 +5206,7 @@
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="34" xr:uid="{BC204499-D622-48C9-BC09-4C59BFEF7A12}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="26" xr:uid="{5914F9B2-3CA3-48D0-8053-731F9F9B7498}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
   <autoFilter ref="D186:H199" xr:uid="{D41FBEA4-8379-4DF7-A068-BF94D364F1A2}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5192,19 +5215,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{FE9A6402-9F17-45D6-81C9-B41AC3C7954F}" name="Production system j">
+    <tableColumn id="1" xr3:uid="{7C4A3CE7-1CA8-4451-993D-15E254957C08}" name="Production system j">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{7CE8B532-E797-4359-A943-59732EBA406D}" name="EFN2O">
+    <tableColumn id="2" xr3:uid="{805DE6F9-B22F-42BE-8E41-1179C1C48FB2}" name="EFN2O">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{A318BF51-4D2E-48DE-BE88-1E4A8ED19B82}" name="Production system only">
+    <tableColumn id="3" xr3:uid="{0D764405-F3E7-4659-BB57-108C92E41744}" name="Production system only">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{2C6FADCF-C3FB-4DD1-9001-F40AFA0E89CC}" name="Irrigation method">
+    <tableColumn id="4" xr3:uid="{C9719947-1D8A-4FBD-A73A-D5D1894B7E7A}" name="Irrigation method">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{8487FBC9-6B3C-4956-B063-649C33304B05}" name="Rainfall zone">
+    <tableColumn id="5" xr3:uid="{C7FA17AD-66D8-47E0-AA92-DC5C8D6D47EC}" name="Rainfall zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5213,16 +5236,16 @@
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="35" xr:uid="{51ECE1AA-22EA-44EA-9C2E-4882AFCB4FA8}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{33080794-3C9B-4B09-AA81-0425249F0A72}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
   <autoFilter ref="D142:E147" xr:uid="{1F48CA34-50DE-46D5-B32A-BB3A1E818E37}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{E69E76C7-3ABC-4D33-A248-F4FD8C78DC75}" name="Irrigation type i">
+    <tableColumn id="1" xr3:uid="{95008387-7F3F-4485-8FCE-8A32794362E3}" name="Irrigation type i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{30062886-D624-44B9-A4D6-8172FDB32ACC}" name="FracWET" dataDxfId="18" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{059DE7C8-0474-44E0-BD18-285A24CB1466}" name="FracWET" dataDxfId="18" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5249,16 +5272,16 @@
 </file>
 
 <file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="36" xr:uid="{6C67BE23-86D2-4A05-B2BC-EE396C2C0C0E}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="28" xr:uid="{3B427198-14B8-467E-990A-983CD43A4A88}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
   <autoFilter ref="D206:E208" xr:uid="{D5BE3F89-D70E-4C53-A71C-E756622DEF38}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{1236BDD8-AEEC-4D8A-AEFB-ED9356DF3DD1}" name="Climate zone">
+    <tableColumn id="1" xr3:uid="{77155640-BD72-4B68-B35F-A4CD6E6A62A8}" name="Climate zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{F6888293-D606-47A6-8932-E2CD434BD8A5}" name="EFPRP" dataDxfId="17" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{BBB29331-C081-48C9-9091-18B6ED4A9A17}" name="EFPRP" dataDxfId="17" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5267,16 +5290,16 @@
 </file>
 
 <file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="37" xr:uid="{AFCD272F-7568-43A4-AF7A-23066986692E}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{62A1374D-8C01-438D-8C6B-A7BD4CA9FD20}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
   <autoFilter ref="D212:E224" xr:uid="{97796C3A-D95E-4077-AA20-A8FE4145DAAD}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{082A87F0-D13A-4480-8492-F3D2503C41E2}" name="Month">
+    <tableColumn id="1" xr3:uid="{A7C99355-7BA1-47DA-875F-F4E6F476DBB2}" name="Month">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{3A38DFCE-8BC1-411E-9649-BA3B242C5C67}" name="Season" dataDxfId="16" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{F5F84847-B5B7-4FC3-A009-BA14974E995A}" name="Season" dataDxfId="16" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5285,7 +5308,7 @@
 </file>
 
 <file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="39" xr:uid="{A9D87315-F27A-46A3-A327-DB14F89DB92B}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="30" xr:uid="{8943DEAC-8ED6-400F-BBCF-60D2FDF7C77F}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
   <autoFilter ref="D231:S250" xr:uid="{1D72DD9B-C8FA-48F4-9A11-20231FF87B5A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5305,52 +5328,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{74BFEBA4-3487-4BE5-88B9-85DB7D433F74}" name="Temperature zone">
+    <tableColumn id="1" xr3:uid="{BD957EFF-7EDC-40CC-A55D-B999F7D7743A}" name="Temperature zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{EE7A79F3-7EC2-470C-8060-08333EAEE5D6}" name="MAT (ºC)" dataDxfId="15" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{706B8784-ACBC-4772-B3C9-65B92B3A16EB}" name="MAT (ºC)" dataDxfId="15" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{FB41F6A9-5353-48F8-BBE2-FDDAFFCEC3DF}" name="Anaerobic lagoon" dataDxfId="14" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{795ACF8C-E7E4-418E-98A0-B225F9A843E6}" name="Anaerobic lagoon" dataDxfId="14" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{46BC84F5-D586-4491-8920-08D8E8254F8B}" name="Digester / covered lagoons" dataDxfId="13" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{5BC1CAF8-6FF1-4B12-B99F-E7A50945C898}" name="Digester / covered lagoons" dataDxfId="13" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{48357028-DF7D-43C1-8693-BE3CCAEDC19B}" name="Liquid systems" dataDxfId="12" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{62BE04D5-5EFB-47DF-AB60-61BDB28DADDE}" name="Liquid systems" dataDxfId="12" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{46A64015-6571-40C8-8B97-9ACD24D0FDFF}" name="Daily spread" dataDxfId="11" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{A6953F4C-4946-402C-9E9D-C1687F72E6ED}" name="Daily spread" dataDxfId="11" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{BE8A0DB7-DA22-4D11-8D6E-5B03E95383E1}" name="Composting (passive windrow)" dataDxfId="10" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{F371C1CC-B865-4590-8F58-947D0346A2D7}" name="Composting (passive windrow)" dataDxfId="10" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{8E9FF3D7-C170-4D01-8CAA-D667E3762352}" name="Solid storage" dataDxfId="9" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{835C2A85-C159-4037-BFBB-BCA899795E46}" name="Solid storage" dataDxfId="9" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{EE8195E9-7EB7-4255-B88A-1A7D661007AC}" name="Pit storage" dataDxfId="8" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{E69E8BF3-C20A-4351-9D54-945913459B31}" name="Pit storage" dataDxfId="8" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{E8290DA2-F81B-417D-8DFF-811E04AE5CD6}" name="Deep litter" dataDxfId="7" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{BFF7CD12-0D20-4D89-89E3-AF17D018FBE6}" name="Deep litter" dataDxfId="7" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{8556C44B-D53C-43B5-AFA8-775CF9A97C5A}" name="Poultry manure with bedding" dataDxfId="6" dataCellStyle="Content normal">
+    <tableColumn id="11" xr3:uid="{5EA7DE27-C6BB-4D98-965F-2EC7E4ACCB5D}" name="Poultry manure with bedding" dataDxfId="6" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{6D7005A7-1332-4775-A075-04932CE4CB0C}" name="Poultry manure without bedding" dataDxfId="5" dataCellStyle="Content normal">
+    <tableColumn id="12" xr3:uid="{D1543B60-2A2B-42CA-B137-3673CEC6300F}" name="Poultry manure without bedding" dataDxfId="5" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{CD24F3C7-0171-4241-9095-F217ACFB21FD}" name="Direct processing" dataDxfId="4" dataCellStyle="Content normal">
+    <tableColumn id="13" xr3:uid="{1C2B15FC-BC70-40B4-8E54-FFABE75F58F5}" name="Direct processing" dataDxfId="4" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{B9A1E1BC-6DAC-4A86-933B-0394729DEF0D}" name="Direct application" dataDxfId="3" dataCellStyle="Content normal">
+    <tableColumn id="14" xr3:uid="{D7F32FFE-532A-43B4-A90F-AE77D9C2BB29}" name="Direct application" dataDxfId="3" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{D37545E7-3A7F-4E1D-9175-AF768DF5CDBB}" name="Pasture range and paddock" dataDxfId="2" dataCellStyle="Content normal">
+    <tableColumn id="15" xr3:uid="{EB06045B-53A5-41D6-A443-5F04AE98854B}" name="Pasture range and paddock" dataDxfId="2" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{01BDA555-814C-4F57-A554-B9E8D1197D3B}" name="MAT raw" dataDxfId="1" dataCellStyle="Content normal">
+    <tableColumn id="16" xr3:uid="{1A325EB4-E55C-4501-99C8-99066B0DF479}" name="MAT raw" dataDxfId="1" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5359,16 +5382,16 @@
 </file>
 
 <file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="40" xr:uid="{918D91AC-F0D7-45AF-888F-8CCD5245EE64}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="38" xr:uid="{995B35A1-A568-4275-B29B-5ECF3661FE92}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
   <autoFilter ref="D257:E259" xr:uid="{56E01C14-1BB8-4015-9158-4CEB4D3B605C}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{FD1030A0-8423-4F54-A208-B8E2F9F2CCAF}" name="Climate Zone">
+    <tableColumn id="1" xr3:uid="{EFA2DB88-B766-4C17-A7C4-B6FAAD5B5EDD}" name="Climate Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{5D7849B7-3122-4868-94E6-53DB0ADF4E31}" name="EFNi &amp; EFN2Oi" dataDxfId="0" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{FE55D07E-17C7-451F-9E3F-9EEB68806A59}" name="EFNi &amp; EFN2Oi" dataDxfId="0" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5461,20 +5484,20 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{3CE089AD-2CC8-4A13-B28C-D1C37F1413FD}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{74F13BDC-7FF7-4613-AC03-CEDF53BD7761}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
   <autoFilter ref="D6:F14" xr:uid="{E0906749-7FC7-47DE-82F6-F796C4463018}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{5C8F314E-448B-4DFB-9FB6-24EB1C068822}" name="State/Territory">
+    <tableColumn id="1" xr3:uid="{124FDBBC-A38E-43C8-84F1-D3D579FE617F}" name="State/Territory">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{0CDE5FB6-156E-4C8F-BE5E-AE847E4623E5}" name="Common Name">
+    <tableColumn id="2" xr3:uid="{89C47681-C094-4C42-9372-56A2DB1DB0D7}" name="Common Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{48462493-A4EA-444E-992B-54CD236800AC}" name="Abbreviation">
+    <tableColumn id="3" xr3:uid="{B960BF1C-0CFE-473A-8E33-9235A918184A}" name="Abbreviation">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5483,12 +5506,12 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{277630A7-A8D1-4F5F-B575-BC9FABFD34E8}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{3F845A1E-3324-4B98-817F-8212AA8DA998}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
   <autoFilter ref="D20:D30" xr:uid="{5FA81339-C6C8-4D36-BEEA-6C4AEDD9E676}">
     <filterColumn colId="0" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{D18F34C1-11FB-4248-811F-713D855F6948}" name="SA 4 Name">
+    <tableColumn id="1" xr3:uid="{BA8E7FE9-C1B6-4727-B900-A887EB080F5E}" name="SA 4 Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5497,16 +5520,16 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{A11C6061-9DBF-4C48-A0C9-EF5912EE11FB}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{4CD83261-FF7D-417B-A63C-710DDA6E4ABB}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
   <autoFilter ref="D36:E43" xr:uid="{B8E87A66-3E41-4AD3-925D-01EE21B43D7A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{D1260DFE-7F08-4477-ADE7-CA810E99F721}" name="Gas">
+    <tableColumn id="1" xr3:uid="{92E40B26-E4F1-4DAA-BE12-BE52A959B151}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{E52C9195-EBCB-4DA9-9E83-AFF26E2BF1B7}" name="CO2-e factor">
+    <tableColumn id="2" xr3:uid="{7C9B8178-798B-4B12-9F1E-D79019815C89}" name="CO2-e factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -16154,7 +16177,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61A98245-077D-4620-A68F-E98BAE61B1C4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A957E153-9436-4045-97D1-6CFB485C783B}">
   <dimension ref="A1:BY259"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -20161,6 +20184,10 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACkAKgAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADIAKQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAHQAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAC8AdABcAHUAMAAwADMAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAdQAwADAAMgA3AFwAIgAgAFwAdQAwADAAMgA2ACAAcwBoACAAXAB1ADAAMAAyADYAIABcACIAXAB1ADAAMAAyADcAIQBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFUATgBEACgAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIAAwACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAE0ATQBTACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAaQB0AGwAZQBDAGUAbABsACwAIABTAG8AdQByAGMAZQBDAGUAbABsACwAXABuACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAEwARQBGAFQAKABTAG8AdQByAGMAZQBDAGUAbABsACwAIABGAEkATgBEACgAXAAiACwAXAAiACwAIABTAG8AdQByAGMAZQBDAGUAbABsACkAIAAtADEAKQAsACAAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFwAIgAsACAAXAAiAFwAIgApACAAXAB1ADAAMAAyADYAIABcACIAIABcACIAIABcAHUAMAAwADIANgAgAFQAaQB0AGwAZQBDAGUAbABsAFwAbgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBcAG4AVABhAGIAbABlACAAQQAuADEALgA1AC4AMQA6ACAATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAARQBuAHQAZQByAGkAYwAgAGYAZQByAG0AZQBuAHQAYQB0AGkAbwBuACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGUAYQBjAGgAIABvAHQAaABlAHIAIABsAGkAdgBlAHMAdABvAGMAawAgAHQAeQBwAGUAIAAoAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAHkAZQBhAHIAKQAgACgATQBqACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawAgAC0AIABFAG4AdABlAHIAaQBjACAAZgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZQBhAGMAaAAgAG8AdABoAGUAcgAgAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGoAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAEMASAA0ACAALwAgAGgAZQBhAGQAIAAvACAAeQBlAGEAcgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuADEAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADIALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIABUAHkAcABlAFwAIgAsACAAXAAiAE0AagBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgB1AGYAZgBhAGwAbwBcACIALAAgADYAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAG8AYQB0AHMAXAAiACwAIAA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBlAHIAXAAiACwAIAAyADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBhAG0AZQBsAHMAXAAiACwAIAA0ADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBsAHAAYQBjAGEAcwBcACIALAAgADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABvAHIAcwBlAHMAXAAiACwAIAAxADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQB1AGwAZQBzAC8AYQBzAHMAZQBzAFwAIgAsACAAMQAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAbQB1AHMALwBvAHMAdAByAGkAYwBoAGUAcwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBvAGQAdQBjAGUAZABcAG4AVABhAGIAbABlACAAQQAuADEALgA1AC4AMgA6ACAATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAAVgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIABwAHIAbwBkAHUAYwBlAGQAIABiAHkAIABlAGEAYwBoACAAbwB0AGgAZQByACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlACAAKABrAGcAIABWAFMALwBoAGUAYQBkAC8AZABhAHkAKQAgACgAVgBTAGoAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBvAGQAdQBjAGUAZABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAAVgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIABwAHIAbwBkAHUAYwBlAGQAIABiAHkAIABlAGEAYwBoACAAbwB0AGgAZQByACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBvAGQAdQBjAGUAZABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBTAGoAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAG8AZAB1AGMAZQBkAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAAVgBTACAALwAgAGgAZQBhAGQAIAAvACAAZABhAHkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAG8AZAB1AGMAZQBkAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuADIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAG8AZAB1AGMAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBvAGQAdQBjAGUAZABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAyACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAAVAB5AHAAZQBcACIALAAgAFwAIgBWAFMAagBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgB1AGYAZgBhAGwAbwBcACIALAAgADIALgA3ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBvAGEAdABzAFwAIgAsACAAMAAuADMANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGUAZQByAFwAIgAsACAAMAAuADkAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAbQBlAGwAcwBcACIALAAgADIALgA3ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBsAHAAYQBjAGEAcwBcACIALAAgADAALgAzADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABvAHIAcwBlAHMAXAAiACwAIAAyAC4ANwAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AdQBsAGUAcwAvAGEAcwBzAGUAcwBcACIALAAgADAALgA5ADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAHUAcwAvAG8AcwB0AHIAaQBjAGgAZQBzAFwAIgAsACAAMAAuADMANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADUALgAzADoAIABPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawAgAC0AIABOAGkAdAByAG8AZwBlAG4AIABlAHgAYwByAGUAdABlAGQAIABwAGUAcgAgAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQAgACgAawBnACAATgAyAE8ALwBoAGUAYQBkAC8AeQBlAGEAcgApACAAKABOAEUAagApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawAgAC0AIABOAGkAdAByAG8AZwBlAG4AIABlAHgAYwByAGUAdABlAGQAIABwAGUAcgAgAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4ARQBqAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALwAgAGgAZQBhAGQAIAAvACAAeQBlAGEAcgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA1AC4AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADIALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIABUAHkAcABlAFwAIgAsACAAXAAiAE4ARQBqAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAHUAZgBmAGEAbABvAFwAIgAsACAAMwA5AC4ANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAG8AYQB0AHMAXAAiACwAIAA3AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGUAZQByAFwAIgAsACAAMQAzAC4AMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAbQBlAGwAcwBcACIALAAgADMAOQAuADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBsAHAAYQBjAGEAcwBcACIALAAgADcALgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHMAZQBzAFwAIgAsACAAMwA5AC4ANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAHUAbABlAHMALwBhAHMAcwBlAHMAXAAiACwAIAAxADMALgAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAbQB1AHMALwBvAHMAdAByAGkAYwBoAGUAcwBcACIALAAgADcALgAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABcAG4AVABhAGIAbABlACAAQQAuADEALgA1AC4ANAA6ACAATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAAQQB2AGUAcgBhAGcAZQAgAEwAaQB2AGUAdwBlAGkAZwBoAHQAcwAgACgAVwBjAG8AKQAgACgAawBnACkAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawAgAC0AIABBAHYAZQByAGEAZwBlACAATABpAHYAZQB3AGUAaQBnAGgAdABzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBXAGMAbwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADUALgA0AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMwAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawAgAFQAeQBwAGUAIABqAFwAIgAsACAAXAAiAEEAdgBlAHIAYQBnAGUAIABMAGkAdgBlAHcAZQBpAGcAaAB0AFwAIgAsACAAXAAiAEEAdgBlAHIAYQBnAGUAIABMAGkAdgBlAHcAZQBpAGcAaAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAHUAZgBmAGEAbABvAFwAIgAsACAAMwAzADYALAAgAFwAIgAtAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAG8AYQB0AHMAXAAiACwAIAAzADMALAAgAFwAIgAyADgAawBnACAALQAgAGwAbwB3ACAAcAByAG8AZAB1AGMAdABpAHYAaQB0AHkAIABzAHkAcwB0AGUAbQBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAG8AYQB0AHMAXAAiACwAIAAzADMALAAgAFwAIgA1ADAAawBnACAALQAgAGgAaQBnAGgAIABwAHIAbwBkAHUAYwB0AGkAdgBpAHQAeQAgAHMAeQBzAHQAZQBtAHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBlAHIAXAAiACwAIAAxADIAMAAsACAAMQAyADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBhAG0AZQBsAHMAXAAiACwAIAAyADEANwAsACAANQA3ADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBsAHAAYQBjAGEAcwBcACIALAAgAFwAIgAtAFwAIgAsACAANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHMAZQBzAFwAIgAsACAAMwA3ADcALAAgADUANQAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AdQBsAGUAcwAvAGEAcwBzAGUAcwBcACIALAAgADEAMwAwACwAIAAyADQANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AdQBzAC8AbwBzAHQAcgBpAGMAaABlAHMAXAAiACwAIAAxADIAMAAsACAAMQAyADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBlAGYAZQByAGUAbgBjAGUAXAAiACwAIABcACIASQBQAEMAQwAgADIAMAAxADkAIABUAGEAYgBsAGUAIAAxADAAQQAuADUAIABbADIAXQBcACIALAAgAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFQAYQBiAGwAZQAgADEAMAAuADEAMAAgAFsAMgBdAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAHQAaQBvAG4AVwBhAHMAdABlAEkAbgBNAE0AUwBcAG4AVABhAGIAbABlACAAQQAuADEALgA1AC4ANQA6ACAATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAARgByAGEAYwB0AGkAbwBuACAAbwBmACAAdwBhAHMAdABlACAAaQBuACAAZQBhAGMAaAAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdAAgAHMAeQBzAHQAZQBtACAAKABmAHIAYQBjAHQAaQBvAG4AKQAgACgATQBNAFMAbQApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAHQAaQBvAG4AVwBhAHMAdABlAEkAbgBNAE0AUwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAARgByAGEAYwB0AGkAbwBuACAAbwBmACAAdwBhAHMAdABlACAAaQBuACAAZQBhAGMAaAAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdAAgAHMAeQBzAHQAZQBtAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwB0AGkAbwBuAFcAYQBzAHQAZQBJAG4ATQBNAFMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATQBTAG0AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAHQAaQBvAG4AVwBhAHMAdABlAEkAbgBNAE0AUwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMAdABpAG8AbgBXAGEAcwB0AGUASQBuAE0ATQBTAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuADUAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAHQAaQBvAG4AVwBhAHMAdABlAEkAbgBNAE0AUwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMAdABpAG8AbgBXAGEAcwB0AGUASQBuAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXAAiACwAIABcACIAVQBuAGMAbwB2AGUAcgBlAGQAIABBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAEMAVABcACIALAAgACAAOQA5AC4ANgA2ACwAIAAgADAALgAzADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBTAFcAXAAiACwAIAAgADkAOQAuADYANgAsACAAIAAwAC4AMwA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AVABcACIALAAgACAAOQA5AC4ANgA2ACwAIAAgADAALgAzADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBMAEQAXAAiACwAIAAgADkAOQAuADYANgAsACAAIAAwAC4AMwA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAQQBcACIALAAgACAAOQA5AC4ANgA2ACwAIAAgADAALgAzADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABBAFMAXAAiACwAIAAgADkAOQAuADYANgAsACAAIAAwAC4AMwA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYASQBDAFwAIgAsACAAIAA5ADkALgA2ADYALAAgACAAMAAuADMANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAEEAXAAiACwAIAAgADkAOQAuADYANgAsACAAIAAwAC4AMwA0AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBcAG4AVABhAGIAbABlACAAQQAuADEALgA1AC4ANgA6ACAATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAcgBlAGcAaQBvAG4AIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawAgAC0AIABNAGUAdABoAGEAbgBlACAAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAcABlAHIAIAByAGUAZwBpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBDAEYAaQBtAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuADYAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMwAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAQwBUAFwAIgAsACAAIAAwAC4AMAAwADQANwAsACAAIAAwAC4ANwAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AUwBXAFwAIgAsACAAIAAwAC4AMAAwADQANwAsACAAIAAwAC4ANwA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AVABcACIALAAgACAAMAAuADAAMAA0ADcALAAgACAAMAAuADgAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAEwARABcACIALAAgACAAMAAuADAAMAA0ADcALAAgACAAMAAuADcAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEEAXAAiACwAIAAgADAALgAwADAANAA3ACwAIAAgADAALgA3ADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABBAFMAXAAiACwAIAAgADAALgAwADAANAA3ACwAIAAgADAALgA3ADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBJAEMAXAAiACwAIAAgADAALgAwADAANAA3ACwAIAAgADAALgA3ADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBBAFwAIgAsACAAIAAwAC4AMAAwADQANwAsACAAIAAwAC4ANwA2AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuAFgAOgAgAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAALQAgAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAKABtADMAIABDAEgANAAgAC8AIABrAGcAIABWAFMAKQAgACgAQgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAALQAgAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHAAbwB0AGUAbgB0AGkAYQBsAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQgBPAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAG0AMwAgAEMASAA0ACAALwAgAGsAZwAgAFYAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA1AC4AWABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6ACAAVABoAGUAcgBlACAAdwBlAHIAZQAgAG4AbwAgAHYAYQBsAHUAZQBzACAAaQBuACAAVgBFAEUAUgBHACAAcwBvACAAdABoAGkAcwAgAGQAYQB0AGEAIABoAGEAcwAgAGIAZQBlAG4AIABnAGUAbgBlAHIAYQB0AGUAZAAgAGIAeQAgAHUAcwBpAG4AZwAgAGQAbwBjAHUAbQBlAG4AdABlAGQAIABCAE8AIAB2AGEAbAB1AGUAcwAgAGYAcgBvAG0AIABvAHQAaABlAHIAIABsAGkAdgBlAHMAdABvAGMAawBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMwAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawAgAFQAeQBwAGUAXAAiACwAIABcACIAQgBPAFwAIgAsACAAXAAiAFQAYQBrAGUAbgAgAGYAcgBvAG0AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBmAGYAYQBsAG8AXAAiACwAIAAwAC4AMQA5ACwAIABcACIARgBlAGUAZABsAG8AdAAsACAAUABhAHMAdAB1AHIAZQAgAGIAZQBlAGYAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAbwBhAHQAcwBcACIALAAgADAALgAyADQALAAgAFwAIgBTAGgAZQBlAHAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBlAHIAXAAiACwAIAAwAC4AMgA0ACwAIABcACIAUwBoAGUAZQBwAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAbQBlAGwAcwBcACIALAAgADAALgAyADQALAAgAFwAIgBTAGgAZQBlAHAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbABwAGEAYwBhAHMAXAAiACwAIAAwAC4AMgA0ACwAIABcACIAUwBoAGUAZQBwAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgBzAGUAcwBcACIALAAgADAALgAxADkALAAgAFwAIgBGAGUAZQBkAGwAbwB0ACwAIABQAGEAcwB0AHUAcgBlACAAYgBlAGUAZgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQB1AGwAZQBzAC8AYQBzAHMAZQBzAFwAIgAsACAAMAAuADIANAAsACAAXAAiAFMAaABlAGUAcABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAHUAcwAvAG8AcwB0AHIAaQBjAGgAZQBzAFwAIgAsACAAMAAuADMANgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIAAtACAAbQBlAGEAdAAgAGMAaABpAGMAawBlAG4AcwBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGYAcgBvAG0AIAB1AHIAaQBuAGUAIABhAG4AZAAgAGYAYQBlAGMAZQBzACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAZgByAG8AbQAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZgBhAGUAYwBlAHMAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBHAEEAUwBNAHMAbwBpAGwAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgBIADMALQBOACAAKwAgAE4ATwB4AC0ATgApAC8AawBnACAATgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMARwBBAFMATQBTAG8AaQBsAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgA3AC4AMgAuADMAIABDAE8ATgBTAFQAQQBOAFQAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMARwBBAFMATQBTAG8AaQBsAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgAyADEAKQA7AFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMwAuADYAOgAgAEUAbgB0AGUAcgBpAGMAIABNAGUAdABoAGEAbgBlACAALQAgAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAzAC4ANgAuADEALgAxACAATQBlAHQAaABvAGQAIAAxACAALQAgAEUAbgB0AGUAcgBpAGMAIABPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADMAXwA2AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAFwAbgBUAG8AdABhAGwAIABhAG4AbgB1AGEAbAAgAG0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAGUAbgB0AGUAcgBpAGMAIABmAGUAcgBtAGUAbgB0AGEAdABpAG8AbgAgAGkAbgAgAG8AdABoAGUAcgAgAGwAaQB2AGUAcwB0AG8AYwBrAFwAbgBFAF8AZQBuAHQAZQByAGkAYwBcAG4AdAAgAEMASAA0AFwAbgBFAF8AewBlAG4AdABlAHIAaQBjAH0APQBcAFwAcwB1AG0AXwBqACgATgBfAGoAXABcAHQAaQBtAGUAcwAgAE0AXwBqACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXABuAE4AXwBqACAAPQAgAG4AdQBtAGIAZQByACAAbwBmACAAbABpAHYAZQBzAHQAbwBjAGsAIABvAGYAIABlAGEAYwBoACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlACAAagAgACgAaABlAGEAZAApAFwAbgBNAF8AagAgAD0AIABlAG4AdABlAHIAaQBjACAAZgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgACgAawBnACAAQwBIADQALwBoAGUAYQBkAC8AeQBlAGEAcgApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADMAXwA2AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE4AXwBqACwAIABNAF8AagAsAFwAbgAgACAAIAAgAFMAVQBNACgATgBfAGoAIAAqACAATQBfAGoAKQAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADYAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAbwB0AGEAbAAgAGEAbgBuAHUAYQBsACAAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAZQBuAHQAZQByAGkAYwAgAGYAZQByAG0AZQBuAHQAYQB0AGkAbwBuACAAaQBuACAAbwB0AGgAZQByACAAbABpAHYAZQBzAHQAbwBjAGsAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwA2AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AZQBuAHQAZQByAGkAYwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADYAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBIADQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwA2AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADMALgA2AC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8ANgBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADYAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewBlAG4AdABlAHIAaQBjAH0APQBcAFwAcwB1AG0AXwBqACgATgBfAGoAXABcAHQAaQBtAGUAcwAgAE0AXwBqACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwA2AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AXwBqAFwAIgAsACAAXAAiAG4AdQBtAGIAZQByACAAbwBmACAAbABpAHYAZQBzAHQAbwBjAGsAIABvAGYAIABlAGEAYwBoACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlACAAagBcACIALAAgAFwAIgBoAGUAYQBkAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBfAGoAXAAiACwAIABcACIAZQBuAHQAZQByAGkAYwAgAGYAZQByAG0AZQBuAHQAYQB0AGkAbwBuACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAXAAiACwAIABcACIAawBnACAAQwBIADQALwBoAGUAYQBkAC8AeQBlAGEAcgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGoAXAAiACwAIABcACIAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMwBfADQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEcAZQB0AE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBvAGQAdQBjAGUAZABfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAbwBkAHUAYwBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAG8AZAB1AGMAZQBkAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAbwBkAHUAYwBlAGQAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAbwBkAHUAYwBlAGQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAbwBkAHUAYwBlAGQAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwB0AGkAbwBuAFcAYQBzAHQAZQBJAG4ATQBNAFMAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAHQAaQBvAG4AVwBhAHMAdABlAEkAbgBNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMAdABpAG8AbgBXAGEAcwB0AGUASQBuAE0ATQBTAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMAdABpAG8AbgBXAGEAcwB0AGUASQBuAE0ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAHQAaQBvAG4AVwBhAHMAdABlAEkAbgBNAE0AUwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwB0AGkAbwBuAFcAYQBzAHQAZQBJAG4ATQBNAFMAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBEAGEAdABhACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADYAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8ANgBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFQAaQB0AGwAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwA2AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADYAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADYAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwA2AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8ANgBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8ANgBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAcgBnAHUAbQBlAG4AdABzACIAXQAsACIAbABvAGMAYQBsAGUAIgA6AHsAIgBsAGkAcwB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAcgBvAHcAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBjAG8AbAB1AG0AbgBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUABvAHMAaQB0AGkAbwBuAHMAIgA6AFsAMwBdACwAIgBkAGUAYwBpAG0AYQBsAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiAC4AIgAsACIAZABhAHQAZQBPAHIAZABlAHIAIgA6ACIARABNAFkAIgAsACIAYwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsACIAOgAiACQAIgAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbABMAGUAYQBkACIAOgB0AHIAdQBlACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAZQBwAEIAeQBTAHAAYQBjAGUAIgA6AGYAYQBsAHMAZQAsACIAcgBvAHcATABlAHQAdABlAHIAIgA6ACIAUgAiACwAIgBjAG8AbAB1AG0AbgBMAGUAdAB0AGUAcgAiADoAIgBDACIALAAiAHIAYwBMAGUAZgB0AEIAcgBhAGMAawBlAHQAIgA6ACIAWwAiACwAIgByAGMAUgBpAGcAaAB0AEIAcgBhAGMAawBlAHQAIgA6ACIAXQAiACwAIgBzAHQAYQB0AGUAbQBlAG4AdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGwAbwBjAGEAbABlAE4AYQBtAGUAIgA6ACIAZQBuAC0AdQBzACIAfQB9AA==</AFEJSONBlob>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
@@ -20171,11 +20198,16 @@
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACkAKgAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADIAKQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAHQAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAC8AdABcAHUAMAAwADMAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAdQAwADAAMgA3AFwAIgAgAFwAdQAwADAAMgA2ACAAcwBoACAAXAB1ADAAMAAyADYAIABcACIAXAB1ADAAMAAyADcAIQBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgAFwAdQAwADAAMgA2ACAAXAAiACAAXAAiACAAXAB1ADAAMAAyADYAIABUAGkAdABsAGUAQwBlAGwAbABcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAiACwAIgB0AGUAeAB0ACIAOgAiAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuADEAOgAgAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAALQAgAEUAbgB0AGUAcgBpAGMAIABmAGUAcgBtAGUAbgB0AGEAdABpAG8AbgAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABlAGEAYwBoACAAbwB0AGgAZQByACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlACAAKABrAGcAIABDAEgANAAvAGgAZQBhAGQALwB5AGUAYQByACkAIAAoAE0AagApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAARQBuAHQAZQByAGkAYwAgAGYAZQByAG0AZQBuAHQAYQB0AGkAbwBuACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGUAYQBjAGgAIABvAHQAaABlAHIAIABsAGkAdgBlAHMAdABvAGMAawAgAHQAeQBwAGUAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBqAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABDAEgANAAgAC8AIABoAGUAYQBkACAALwAgAHkAZQBhAHIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADUALgAxAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAyACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAAVAB5AHAAZQBcACIALAAgAFwAIgBNAGoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBmAGYAYQBsAG8AXAAiACwAIAA2ADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBvAGEAdABzAFwAIgAsACAANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGUAZQByAFwAIgAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAYQBtAGUAbABzAFwAIgAsACAANAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbABwAGEAYwBhAHMAXAAiACwAIAA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHMAZQBzAFwAIgAsACAAMQA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AdQBsAGUAcwAvAGEAcwBzAGUAcwBcACIALAAgADEAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AdQBzAC8AbwBzAHQAcgBpAGMAaABlAHMAXAAiACwAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAbwBkAHUAYwBlAGQAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuADIAOgAgAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAALQAgAFYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAcAByAG8AZAB1AGMAZQBkACAAYgB5ACAAZQBhAGMAaAAgAG8AdABoAGUAcgAgAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQAgACgAawBnACAAVgBTAC8AaABlAGEAZAAvAGQAYQB5ACkAIAAoAFYAUwBqACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAbwBkAHUAYwBlAGQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAALQAgAFYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAcAByAG8AZAB1AGMAZQBkACAAYgB5ACAAZQBhAGMAaAAgAG8AdABoAGUAcgAgAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAbwBkAHUAYwBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAUwBqAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBvAGQAdQBjAGUAZABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAFYAUwAgAC8AIABoAGUAYQBkACAALwAgAGQAYQB5AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBvAGQAdQBjAGUAZABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADUALgAyAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBvAGQAdQBjAGUAZABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAbwBkAHUAYwBlAGQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMgAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawAgAFQAeQBwAGUAXAAiACwAIABcACIAVgBTAGoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBmAGYAYQBsAG8AXAAiACwAIAAyAC4ANwAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAbwBhAHQAcwBcACIALAAgADAALgAzADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGUAcgBcACIALAAgADAALgA5ADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBhAG0AZQBsAHMAXAAiACwAIAAyAC4ANwAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbABwAGEAYwBhAHMAXAAiACwAIAAwAC4AMwA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHMAZQBzAFwAIgAsACAAMgAuADcAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAHUAbABlAHMALwBhAHMAcwBlAHMAXAAiACwAIAAwAC4AOQAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAbQB1AHMALwBvAHMAdAByAGkAYwBoAGUAcwBcACIALAAgADAALgAzADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABcAG4AVABhAGIAbABlACAAQQAuADEALgA1AC4AMwA6ACAATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAATgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAZQBkACAAcABlAHIAIABsAGkAdgBlAHMAdABvAGMAawAgAHQAeQBwAGUAIAAoAGsAZwAgAE4AMgBPAC8AaABlAGEAZAAvAHkAZQBhAHIAKQAgACgATgBFAGoAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAATgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAZQBkACAAcABlAHIAIABsAGkAdgBlAHMAdABvAGMAawAgAHQAeQBwAGUAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAEUAagBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC8AIABoAGUAYQBkACAALwAgAHkAZQBhAHIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuADMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAyACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAAVAB5AHAAZQBcACIALAAgAFwAIgBOAEUAagBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgB1AGYAZgBhAGwAbwBcACIALAAgADMAOQAuADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBvAGEAdABzAFwAIgAsACAANwAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGUAcgBcACIALAAgADEAMwAuADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBhAG0AZQBsAHMAXAAiACwAIAAzADkALgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbABwAGEAYwBhAHMAXAAiACwAIAA3AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgBzAGUAcwBcACIALAAgADMAOQAuADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQB1AGwAZQBzAC8AYQBzAHMAZQBzAFwAIgAsACAAMQAzAC4AMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AdQBzAC8AbwBzAHQAcgBpAGMAaABlAHMAXAAiACwAIAA3AC4AMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuADQAOgAgAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAALQAgAEEAdgBlAHIAYQBnAGUAIABMAGkAdgBlAHcAZQBpAGcAaAB0AHMAIAAoAFcAYwBvACkAIAAoAGsAZwApACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAAQQB2AGUAcgBhAGcAZQAgAEwAaQB2AGUAdwBlAGkAZwBoAHQAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVwBjAG8AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA1AC4ANABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADEALAAgADMALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIABUAHkAcABlACAAagBcACIALAAgAFwAIgBBAHYAZQByAGEAZwBlACAATABpAHYAZQB3AGUAaQBnAGgAdABcACIALAAgAFwAIgBBAHYAZQByAGEAZwBlACAATABpAHYAZQB3AGUAaQBnAGgAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgB1AGYAZgBhAGwAbwBcACIALAAgADMAMwA2ACwAIABcACIALQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBvAGEAdABzAFwAIgAsACAAMwAzACwAIABcACIAMgA4AGsAZwAgAC0AIABsAG8AdwAgAHAAcgBvAGQAdQBjAHQAaQB2AGkAdAB5ACAAcwB5AHMAdABlAG0AcwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBvAGEAdABzAFwAIgAsACAAMwAzACwAIABcACIANQAwAGsAZwAgAC0AIABoAGkAZwBoACAAcAByAG8AZAB1AGMAdABpAHYAaQB0AHkAIABzAHkAcwB0AGUAbQBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGUAZQByAFwAIgAsACAAMQAyADAALAAgADEAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAYQBtAGUAbABzAFwAIgAsACAAMgAxADcALAAgADUANwAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbABwAGEAYwBhAHMAXAAiACwAIABcACIALQBcACIALAAgADYANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgBzAGUAcwBcACIALAAgADMANwA3ACwAIAA1ADUAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAHUAbABlAHMALwBhAHMAcwBlAHMAXAAiACwAIAAxADMAMAAsACAAMgA0ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAHUAcwAvAG8AcwB0AHIAaQBjAGgAZQBzAFwAIgAsACAAMQAyADAALAAgADEAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBmAGUAcgBlAG4AYwBlAFwAIgAsACAAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAVABhAGIAbABlACAAMQAwAEEALgA1ACAAWwAyAF0AXAAiACwAIABcACIASQBQAEMAQwAgADIAMAAxADkAIABUAGEAYgBsAGUAIAAxADAALgAxADAAIABbADIAXQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwB0AGkAbwBuAFcAYQBzAHQAZQBJAG4ATQBNAFMAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuADUAOgAgAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAALQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHcAYQBzAHQAZQAgAGkAbgAgAGUAYQBjAGgAIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAIABzAHkAcwB0AGUAbQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0ATQBTAG0AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwB0AGkAbwBuAFcAYQBzAHQAZQBJAG4ATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAALQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHcAYQBzAHQAZQAgAGkAbgAgAGUAYQBjAGgAIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAIABzAHkAcwB0AGUAbQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMAdABpAG8AbgBXAGEAcwB0AGUASQBuAE0ATQBTAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE0AUwBtAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwB0AGkAbwBuAFcAYQBzAHQAZQBJAG4ATQBNAFMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAHQAaQBvAG4AVwBhAHMAdABlAEkAbgBNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADUALgA1AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwB0AGkAbwBuAFcAYQBzAHQAZQBJAG4ATQBNAFMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAHQAaQBvAG4AVwBhAHMAdABlAEkAbgBNAE0AUwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAzACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQBcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBDAFQAXAAiACwAIAAgADkAOQAuADYANgAsACAAIAAwAC4AMwA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AUwBXAFwAIgAsACAAIAA5ADkALgA2ADYALAAgACAAMAAuADMANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFQAXAAiACwAIAAgADkAOQAuADYANgAsACAAIAAwAC4AMwA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEATABEAFwAIgAsACAAIAA5ADkALgA2ADYALAAgACAAMAAuADMANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEEAXAAiACwAIAAgADkAOQAuADYANgAsACAAIAAwAC4AMwA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAQQBTAFwAIgAsACAAIAA5ADkALgA2ADYALAAgACAAMAAuADMANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEkAQwBcACIALAAgACAAOQA5AC4ANgA2ACwAIAAgADAALgAzADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBBAFwAIgAsACAAIAA5ADkALgA2ADYALAAgACAAMAAuADMANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuADYAOgAgAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAALQAgAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAHIAZQBnAGkAbwBuACAAKABmAHIAYQBjAHQAaQBvAG4AKQAgACgATQBDAEYAaQBtACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAcgBlAGcAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AQwBGAGkAbQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADUALgA2AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXAAiACwAIABcACIAVQBuAGMAbwB2AGUAcgBlAGQAIABBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAEMAVABcACIALAAgACAAMAAuADAAMAA0ADcALAAgACAAMAAuADcAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFMAVwBcACIALAAgACAAMAAuADAAMAA0ADcALAAgACAAMAAuADcANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFQAXAAiACwAIAAgADAALgAwADAANAA3ACwAIAAgADAALgA4ADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBMAEQAXAAiACwAIAAgADAALgAwADAANAA3ACwAIAAgADAALgA3ADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBAFwAIgAsACAAIAAwAC4AMAAwADQANwAsACAAIAAwAC4ANwA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAQQBTAFwAIgAsACAAIAAwAC4AMAAwADQANwAsACAAIAAwAC4ANwAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYASQBDAFwAIgAsACAAIAAwAC4AMAAwADQANwAsACAAIAAwAC4ANwA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAQQBcACIALAAgACAAMAAuADAAMAA0ADcALAAgACAAMAAuADcANgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADUALgBYADoAIABPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawAgAC0AIABNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbAAgACgAbQAzACAAQwBIADQAIAAvACAAawBnACAAVgBTACkAIAAoAEIATwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawAgAC0AIABNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEIATwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBtADMAIABDAEgANAAgAC8AIABrAGcAIABWAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuAFgAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgAgAFQAaABlAHIAZQAgAHcAZQByAGUAIABuAG8AIAB2AGEAbAB1AGUAcwAgAGkAbgAgAFYARQBFAFIARwAgAHMAbwAgAHQAaABpAHMAIABkAGEAdABhACAAaABhAHMAIABiAGUAZQBuACAAZwBlAG4AZQByAGEAdABlAGQAIABiAHkAIAB1AHMAaQBuAGcAIABkAG8AYwB1AG0AZQBuAHQAZQBkACAAQgBPACAAdgBhAGwAdQBlAHMAIABmAHIAbwBtACAAbwB0AGgAZQByACAAbABpAHYAZQBzAHQAbwBjAGsAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIABUAHkAcABlAFwAIgAsACAAXAAiAEIATwBcACIALAAgAFwAIgBUAGEAawBlAG4AIABmAHIAbwBtAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAHUAZgBmAGEAbABvAFwAIgAsACAAMAAuADEAOQAsACAAXAAiAEYAZQBlAGQAbABvAHQALAAgAFAAYQBzAHQAdQByAGUAIABiAGUAZQBmAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAG8AYQB0AHMAXAAiACwAIAAwAC4AMgA0ACwAIABcACIAUwBoAGUAZQBwAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGUAZQByAFwAIgAsACAAMAAuADIANAAsACAAXAAiAFMAaABlAGUAcABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBhAG0AZQBsAHMAXAAiACwAIAAwAC4AMgA0ACwAIABcACIAUwBoAGUAZQBwAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGwAcABhAGMAYQBzAFwAIgAsACAAMAAuADIANAAsACAAXAAiAFMAaABlAGUAcABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABvAHIAcwBlAHMAXAAiACwAIAAwAC4AMQA5ACwAIABcACIARgBlAGUAZABsAG8AdAAsACAAUABhAHMAdAB1AHIAZQAgAGIAZQBlAGYAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AdQBsAGUAcwAvAGEAcwBzAGUAcwBcACIALAAgADAALgAyADQALAAgAFwAIgBTAGgAZQBlAHAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAbQB1AHMALwBvAHMAdAByAGkAYwBoAGUAcwBcACIALAAgADAALgAzADYALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAALQAgAG0AZQBhAHQAIABjAGgAaQBjAGsAZQBuAHMAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMARwBBAFMATQBTAG8AaQBsAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABmAHIAbwBtACAAdQByAGkAbgBlACAAYQBuAGQAIABmAGEAZQBjAGUAcwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGYAcgBvAG0AIAB1AHIAaQBuAGUAIABhAG4AZAAgAGYAYQBlAGMAZQBzACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMARwBBAFMATQBzAG8AaQBsAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4ASAAzAC0ATgAgACsAIABOAE8AeAAtAE4AKQAvAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4ANwAuADIALgAzACAAQwBPAE4AUwBUAEEATgBUAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMARwBBAFMATQBTAG8AaQBsAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4AMgAxACkAOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADMALgA2ADoAIABFAG4AdABlAHIAaQBjACAATQBlAHQAaABhAG4AZQAgAC0AIABPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMwAuADYALgAxAC4AMQAgAE0AZQB0AGgAbwBkACAAMQAgAC0AIABFAG4AdABlAHIAaQBjACAATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAzAF8ANgBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBcAG4AVABvAHQAYQBsACAAYQBuAG4AdQBhAGwAIABtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABlAG4AdABlAHIAaQBjACAAZgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AIABpAG4AIABvAHQAaABlAHIAIABsAGkAdgBlAHMAdABvAGMAawBcAG4ARQBfAGUAbgB0AGUAcgBpAGMAXABuAHQAIABDAEgANABcAG4ARQBfAHsAZQBuAHQAZQByAGkAYwB9AD0AXABcAHMAdQBtAF8AagAoAE4AXwBqAFwAXAB0AGkAbQBlAHMAIABNAF8AagApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBOAF8AagAgAD0AIABuAHUAbQBiAGUAcgAgAG8AZgAgAGwAaQB2AGUAcwB0AG8AYwBrACAAbwBmACAAZQBhAGMAaAAgAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQAgAGoAIAAoAGgAZQBhAGQAKQBcAG4ATQBfAGoAIAA9ACAAZQBuAHQAZQByAGkAYwAgAGYAZQByAG0AZQBuAHQAYQB0AGkAbwBuACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIAAoAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAHkAZQBhAHIAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAzAF8ANgBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABOAF8AagAsACAATQBfAGoALABcAG4AIAAgACAAIABTAFUATQAoAE4AXwBqACAAKgAgAE0AXwBqACkAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwA2AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBUAG8AdABhAGwAIABhAG4AbgB1AGEAbAAgAG0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAGUAbgB0AGUAcgBpAGMAIABmAGUAcgBtAGUAbgB0AGEAdABpAG8AbgAgAGkAbgAgAG8AdABoAGUAcgAgAGwAaQB2AGUAcwB0AG8AYwBrAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8ANgBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAGUAbgB0AGUAcgBpAGMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwA2AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMASAA0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8ANgBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAzAC4ANgAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADYAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwA2AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsAZQBuAHQAZQByAGkAYwB9AD0AXABcAHMAdQBtAF8AagAoAE4AXwBqAFwAXAB0AGkAbQBlAHMAIABNAF8AagApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8ANgBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAF8AagBcACIALAAgAFwAIgBuAHUAbQBiAGUAcgAgAG8AZgAgAGwAaQB2AGUAcwB0AG8AYwBrACAAbwBmACAAZQBhAGMAaAAgAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQAgAGoAXAAiACwAIABcACIAaABlAGEAZABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AXwBqAFwAIgAsACAAXAAiAGUAbgB0AGUAcgBpAGMAIABmAGUAcgBtAGUAbgB0AGEAdABpAG8AbgAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAHkAZQBhAHIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBqAFwAIgAsACAAXAAiAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMQBfADIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADMAXwA0ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAbwBkAHUAYwBlAGQAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAG8AZAB1AGMAZQBkAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBvAGQAdQBjAGUAZABfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAG8AZAB1AGMAZQBkAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAG8AZAB1AGMAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAG8AZAB1AGMAZQBkAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMAdABpAG8AbgBXAGEAcwB0AGUASQBuAE0ATQBTAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwB0AGkAbwBuAFcAYQBzAHQAZQBJAG4ATQBNAFMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAHQAaQBvAG4AVwBhAHMAdABlAEkAbgBNAE0AUwBfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAHQAaQBvAG4AVwBhAHMAdABlAEkAbgBNAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwB0AGkAbwBuAFcAYQBzAHQAZQBJAG4ATQBNAFMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMAdABpAG8AbgBXAGEAcwB0AGUASQBuAE0ATQBTAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8ARABhAHQAYQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwA2AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADYAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8ANgBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwA2AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVQBuAGkAdAAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwA2AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8ANgBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADYAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADYAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBBAHIAZwB1AG0AZQBuAHQAcwAiAF0ALAAiAGwAbwBjAGEAbABlACIAOgB7ACIAbABpAHMAdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHIAbwB3AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAYwBvAGwAdQBtAG4AUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFAAbwBzAGkAdABpAG8AbgBzACIAOgBbADMAXQAsACIAZABlAGMAaQBtAGEAbABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAuACIALAAiAGQAYQB0AGUATwByAGQAZQByACIAOgAiAEQATQBZACIALAAiAGMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbAAiADoAIgAkACIALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwATABlAGEAZAAiADoAdAByAHUAZQAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAGUAcABCAHkAUwBwAGEAYwBlACIAOgBmAGEAbABzAGUALAAiAHIAbwB3AEwAZQB0AHQAZQByACIAOgAiAFIAIgAsACIAYwBvAGwAdQBtAG4ATABlAHQAdABlAHIAIgA6ACIAQwAiACwAIgByAGMATABlAGYAdABCAHIAYQBjAGsAZQB0ACIAOgAiAFsAIgAsACIAcgBjAFIAaQBnAGgAdABCAHIAYQBjAGsAZQB0ACIAOgAiAF0AIgAsACIAcwB0AGEAdABlAG0AZQBuAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBsAG8AYwBhAGwAZQBOAGEAbQBlACIAOgAiAGUAbgAtAHUAcwAiAH0AfQA=</AFEJSONBlob>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -20370,16 +20402,15 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -20390,15 +20421,15 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809E3D44-A88D-4EBF-A307-6B8CE77A3361}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -20415,12 +20446,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Excel/3_6_Enteric_OtherLivestock_WIP_v01.xlsx
+++ b/Excel/3_6_Enteric_OtherLivestock_WIP_v01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5D35173-58DB-4542-9057-97609E4CE684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F8AC14A-A2BF-4936-9A48-9098B7815CD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5070" yWindow="5070" windowWidth="28800" windowHeight="15345" firstSheet="7" activeTab="7" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="1350" yWindow="360" windowWidth="36255" windowHeight="19140" firstSheet="7" activeTab="7" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -24,9 +24,6 @@
     <sheet name="Acknowledgements" sheetId="72" r:id="rId9"/>
     <sheet name="Tab template" sheetId="74" r:id="rId10"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId11"/>
-  </externalReferences>
   <definedNames>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e">_xlfn.LAMBDA(_xlpm.E_CH4,_xlpm.GWP_CH4, _xlpm.E_CH4 * _xlpm.GWP_CH4)</definedName>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"ECH4","Methane emissions (t CH4)";"GWPCH4","Global warming potential for methane (t CO2-e / t CH4)"}, _xlpm.r, _xlpm.c))))</definedName>
@@ -42,7 +39,17 @@
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Title">_xlfn.LAMBDA("Convert nitrous oxide emissions to carbon dioxide equivalent emissions")</definedName>
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Unit">_xlfn.LAMBDA("t CO2e")</definedName>
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Variable">_xlfn.LAMBDA("EN2O CO2e")</definedName>
-    <definedName name="Common_InputFunctions.Common_GetMCFTemperatureZone">_xlfn.LAMBDA(_xlpm.Temperature,_xlpm.MMS,_xlpm.TemperatureArray,_xlpm.MMSArray,_xlpm.ReturnArray, _xlfn.XLOOKUP(MEDIAN(_xlpm.Temperature, MIN(_xlpm.TemperatureArray), MAX(_xlpm.TemperatureArray)), _xlpm.TemperatureArray, _xlfn.XLOOKUP(_xlpm.MMS, _xlpm.MMSArray, _xlpm.ReturnArray)))</definedName>
+    <definedName name="Common_InputFunctions.Common_GetMCFTemperatureZone">_xlfn.LAMBDA(_xlpm.Temperature,_xlpm.MMS,_xlpm.TemperatureArray,_xlpm.MMSArray,_xlpm.ReturnArray,
+    _xlfn.XLOOKUP(
+        MEDIAN(
+            ROUND(_xlpm.Temperature, 0),
+            MIN(_xlpm.TemperatureArray),
+            MAX(_xlpm.TemperatureArray)
+        ),
+        _xlpm.TemperatureArray,
+        _xlfn.XLOOKUP(_xlpm.MMS, _xlpm.MMSArray, _xlpm.ReturnArray)
+    )
+)</definedName>
     <definedName name="Common_InputFunctions.CommonCropping_GetFracWET">_xlfn.LAMBDA(_xlpm.LeachingZone,_xlpm.ProductionSystem,_xlpm.LeachingZoneLookup,_xlpm.LeachingZoneFracWETLookup,_xlpm.ProductionSystemLookup,_xlpm.ProductionSystemFracWETLookup, _xlfn.LET(_xlpm.LeachingZoneFracWET, Common_InputFunctions.Utility_LookupValueInTableNumber(_xlpm.LeachingZone, _xlpm.LeachingZoneLookup, _xlpm.LeachingZoneFracWETLookup), _xlpm.ProductionSystemFracWET, Common_InputFunctions.Utility_LookupValueInTableNumber(_xlpm.ProductionSystem, _xlpm.ProductionSystemLookup, _xlpm.ProductionSystemFracWETLookup), IF(_xlpm.LeachingZoneFracWET + _xlpm.ProductionSystemFracWET &gt; 0, 1, 0)))</definedName>
     <definedName name="Common_InputFunctions.getOverlappingReportingCycles">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingCycleStart, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, MONTH(_xlpm.ReportingCycleStart), _xlpm.d, DAY(_xlpm.ReportingCycleStart), _xlpm.PeriodEnd, _xlfn.LAMBDA(_xlpm.st, EDATE(_xlpm.st, 12) - 1), _xlpm.A, _xlpm.S - 365, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (_xlpm.PeriodEnd(DATE(_xlpm.ya, _xlpm.m, _xlpm.d)) &lt; _xlpm.S), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1)))</definedName>
     <definedName name="Common_InputFunctions.getOverlappingReportingPeriods">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingCycleStart, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, MONTH(_xlpm.ReportingCycleStart), _xlpm.d, DAY(_xlpm.ReportingCycleStart), _xlpm.PeriodEnd, _xlfn.LAMBDA(_xlpm.st, EDATE(_xlpm.st, 12) - 1), _xlpm.A, _xlpm.S - 365, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (_xlpm.PeriodEnd(DATE(_xlpm.ya, _xlpm.m, _xlpm.d)) &lt; _xlpm.S), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), _xlpm.n, MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1), _xlpm.yrs, _xlfn.SEQUENCE(_xlpm.n, 1, _xlpm.firstYear, 1), _xlpm.starts, DATE(_xlpm.yrs, _xlpm.m, _xlpm.d), _xlpm.ends, _xlfn.MAP(_xlpm.starts, _xlpm.PeriodEnd), _xlpm.tag, IF(_xlpm.starts = _xlpm.ReportingCycleStart, " (This reporting cycle)", ""), _xlpm.startsText, TEXT(_xlpm.starts, "dd mmm yyyy"), _xlpm.endsText, TEXT(_xlpm.ends, "dd mmm yyyy"), IF(_xlpm.n = 0, "", _xlfn.HSTACK(_xlpm.startsText &amp; " to " &amp; _xlpm.endsText &amp; _xlpm.tag))))</definedName>
@@ -58,9 +65,28 @@
     <definedName name="Common_InputFunctions.Utility_LookupN2OEFFromProdIrrigationRainfall">_xlfn.LAMBDA(_xlpm.ProductionSystem,_xlpm.IrrigationMethod,_xlpm.RainfallZone,_xlpm.ProductionSystemArray,_xlpm.IrrigationMethodArray,_xlpm.RainfallZoneArray,_xlpm.ReturnArray, _xlfn.LET(_xlpm.IrrigationMethod, IF(_xlpm.IrrigationMethod = "Not irrigated", "Not irrigated", "Any"), _xlpm.RainfallZone, IF(_xlpm.IrrigationMethod = "Not irrigated", _xlpm.RainfallZone, "Any"), _xlfn.XLOOKUP(1, (_xlpm.ProductionSystemArray = _xlpm.ProductionSystem) * (_xlpm.IrrigationMethodArray = _xlpm.IrrigationMethod) * (_xlpm.RainfallZoneArray = _xlpm.RainfallZone), _xlpm.ReturnArray)))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupValueInTable">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.LookupArray,_xlpm.ReturnArray, _xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, ""))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupValueInTableNumber">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.LookupArray,_xlpm.ReturnArray, IF(ISNUMBER(_xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, "")), _xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, ""), 0))</definedName>
-    <definedName name="Common_InputFunctions.Utility_LookupValueInTableOneColumnAndHeader">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray, _xlfn.XLOOKUP(_xlpm.LookupValue1, _xlpm.LookupArray1, _xlfn.XLOOKUP(_xlpm.LookupValue2, _xlpm.LookupArray2, _xlpm.ReturnArray)))</definedName>
-    <definedName name="Common_InputFunctions.Utility_LookupValueInTableTwoColumns">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray, _xlfn.XLOOKUP(1, (_xlpm.LookupArray1 = _xlpm.LookupValue1) * (_xlpm.LookupArray2 = _xlpm.LookupValue2), _xlpm.ReturnArray, ""))</definedName>
+    <definedName name="Common_InputFunctions.Utility_LookupValueInTableOneColumnAndHeader">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray,_xlop.ValueIfFalse,
+    IFERROR(
+        _xlfn.XLOOKUP(_xlpm.LookupValue1, _xlpm.LookupArray1,
+            _xlfn.XLOOKUP(_xlpm.LookupValue2, _xlpm.LookupArray2, _xlpm.ReturnArray)
+        ),
+        IF(_xlfn.ISOMITTED(_xlpm.ValueIfFalse), "", _xlpm.ValueIfFalse)
+    )
+)</definedName>
+    <definedName name="Common_InputFunctions.Utility_LookupValueInTableTwoColumns">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray,_xlop.ValueIFFalse,
+    _xlfn.XLOOKUP(1, (_xlpm.LookupArray1=_xlpm.LookupValue1)*(_xlpm.LookupArray2=_xlpm.LookupValue2), _xlpm.ReturnArray, IF(_xlfn.ISOMITTED(_xlpm.ValueIFFalse), "", _xlpm.ValueIFFalse))
+)</definedName>
+    <definedName name="Common_InputFunctions.Utility_ResultsItemFromEquationTitleAndSource">_xlfn.LAMBDA(_xlpm.TitleCell,_xlpm.SourceCell,
+    SUBSTITUTE(LEFT(_xlpm.SourceCell, FIND(",", _xlpm.SourceCell) -1), "VEERG 2026: ", "") &amp; " " &amp; _xlpm.TitleCell
+)</definedName>
     <definedName name="Common_InputFunctions.Utility_SourceHyperlink">_xlfn.LAMBDA(_xlpm.TargetCell, _xlfn.LET(_xlpm.sh, _xlfn.TEXTAFTER(CELL("filename", _xlpm.TargetCell), "]"), _xlpm.addr, CELL("address", _xlpm.TargetCell), "#'" &amp; _xlpm.sh &amp; "'!" &amp; _xlpm.addr))</definedName>
+    <definedName name="Common_InputFunctions.Utility_SourceHyperlinkDifferentSheet">_xlfn.LAMBDA(_xlpm.TargetCell,
+  _xlfn.LET(
+    _xlpm.sh, _xlfn.TEXTAFTER(CELL("filename", _xlpm.TargetCell), "]"),
+    _xlpm.addr, CELL("address", _xlpm.TargetCell),
+    "#" &amp; _xlpm.addr
+  )
+)</definedName>
     <definedName name="Common_InputFunctions.Utility_SplitStringIntoArray">_xlfn.LAMBDA(_xlpm.Cell,_xlpm.Delimiter,_xlop.CharacterToRemove1,_xlop.CharacterToRemove2, _xlfn.FILTERXML("&lt;t&gt;&lt;s&gt;" &amp; SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.Cell, _xlpm.CharacterToRemove1, ""), _xlpm.CharacterToRemove2, ""), _xlpm.Delimiter, "&lt;/s&gt;&lt;s&gt;") &amp; "&lt;/s&gt;&lt;/t&gt;", "//s"))</definedName>
     <definedName name="Common_InputFunctions.Utility_SumQuantityFromCriteria">_xlfn.LAMBDA(_xlpm.Criteria1,_xlpm.Criteria1TypeArray,_xlpm.Quantity,_xlop.Multiplier,_xlop.Criteria2,_xlop.Criteria2Array, _xlfn.LET(_xlpm.multiplier, IF(_xlfn.ISOMITTED(_xlpm.Multiplier), 1, _xlpm.Multiplier), _xlpm.quantity, _xlpm.Quantity * _xlpm.multiplier, _xlpm.criteria1, --(_xlpm.Criteria1TypeArray = _xlpm.Criteria1), _xlpm.criteria2, IF(_xlfn.ISOMITTED(_xlpm.Criteria2), 1, --(_xlpm.Criteria2Array = _xlpm.Criteria2)), SUMPRODUCT(_xlpm.criteria1 * _xlpm.criteria2 * _xlpm.quantity)))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(9, 3, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"State/Territory","Common Name","Abbreviation";"New South Wales","New South Wales","NSW";"Australian Capital Territory","ACT","ACT";"Victoria","Victoria","VIC";"Queensland","Queensland","QLD";"South Australia","South Australia","SA";"Western Australia","Western Australia","WA";"Tasmania","Tasmania","TAS";"Northern Territory","Northern Territory","NT"}, _xlpm.r, _xlpm.c))))</definedName>
@@ -245,19 +271,49 @@
     <definedName name="SourceData_OtherLivestock.SourceData_OtherLivestock_EntericFermentationEmissionFactor_Unit">_xlfn.LAMBDA("kg CH4 / head / year")</definedName>
     <definedName name="SourceData_OtherLivestock.SourceData_OtherLivestock_EntericFermentationEmissionFactor_Variable">_xlfn.LAMBDA("Mj")</definedName>
     <definedName name="SourceData_OtherLivestock.SourceData_OtherLivestock_EntericFermentationEmissionFactor_Variation">_xlfn.LAMBDA("")</definedName>
+    <definedName name="SourceData_OtherLivestock.SourceData_OtherLivestock_FracGASMSoil_Data">_xlfn.LAMBDA(0.21)</definedName>
+    <definedName name="SourceData_OtherLivestock.SourceData_OtherLivestock_FracGASMSoil_Source">_xlfn.LAMBDA("VEERG 2026: 4.7.2.3 CONSTANTS")</definedName>
+    <definedName name="SourceData_OtherLivestock.SourceData_OtherLivestock_FracGASMSoil_Title">_xlfn.LAMBDA("Fraction of nitrogen volatilised from urine and faeces deposited on pasture")</definedName>
+    <definedName name="SourceData_OtherLivestock.SourceData_OtherLivestock_FracGASMSoil_Unit">_xlfn.LAMBDA("(kg NH3-N + NOx-N)/kg N")</definedName>
+    <definedName name="SourceData_OtherLivestock.SourceData_OtherLivestock_FracGASMSoil_Variable">_xlfn.LAMBDA("FracGASMsoil")</definedName>
+    <definedName name="SourceData_OtherLivestock.SourceData_OtherLivestock_FracGASMSoil_Variation">_xlfn.LAMBDA("")</definedName>
     <definedName name="SourceData_OtherLivestock.SourceData_OtherLivestock_FractionWasteInMMS_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(9, 3, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"State","Pasture range and paddock","Uncovered Anaerobic lagoon";"ACT",99.66,0.34;"NSW",99.66,0.34;"NT",99.66,0.34;"QLD",99.66,0.34;"SA",99.66,0.34;"TAS",99.66,0.34;"VIC",99.66,0.34;"WA",99.66,0.34}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="SourceData_OtherLivestock.SourceData_OtherLivestock_FractionWasteInMMS_Source">_xlfn.LAMBDA("VEERG 2026: Table A.1.5.5")</definedName>
     <definedName name="SourceData_OtherLivestock.SourceData_OtherLivestock_FractionWasteInMMS_Title">_xlfn.LAMBDA("Other Livestock - Fraction of waste in each manure management system")</definedName>
     <definedName name="SourceData_OtherLivestock.SourceData_OtherLivestock_FractionWasteInMMS_Unit">_xlfn.LAMBDA("fraction")</definedName>
     <definedName name="SourceData_OtherLivestock.SourceData_OtherLivestock_FractionWasteInMMS_Variable">_xlfn.LAMBDA("MMSm")</definedName>
     <definedName name="SourceData_OtherLivestock.SourceData_OtherLivestock_FractionWasteInMMS_Variation">_xlfn.LAMBDA("")</definedName>
-    <definedName name="SourceData_OtherLivestock.SourceData_OtherLivestock_MethaneConversionFactor_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(9, 3, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"State","Pasture range and paddock","Uncovered Anaerobic lagoon";"ACT",0.0047,0.71;"NSW",0.0047,0.75;"NT",0.0047,0.8;"QLD",0.0047,0.78;"SA",0.0047,0.74;"TAS",0.0047,0.7;"VIC",0.0047,0.74;"WA",0.0047,0.76}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="SourceData_OtherLivestock.SourceData_OtherLivestock_MethaneConversionFactor_Data">_xlfn.LAMBDA(
+    _xlfn.MAKEARRAY(9, 3,
+      _xlfn.LAMBDA(_xlpm.r,_xlpm.c,
+        INDEX({"State","Pasture range and paddock","Uncovered Anaerobic lagoon";"ACT",0.0047,0.71;"NSW",0.0047,0.75;"NT",0.0047,0.8;"QLD",0.0047,0.78;"SA",0.0047,0.74;"TAS",0.0047,0.7;"VIC",0.0047,0.74;"WA",0.0047,0.76}, _xlpm.r, _xlpm.c)
+      )
+    )
+  )</definedName>
     <definedName name="SourceData_OtherLivestock.SourceData_OtherLivestock_MethaneConversionFactor_Source">_xlfn.LAMBDA("VEERG 2026: Table A.1.5.6")</definedName>
     <definedName name="SourceData_OtherLivestock.SourceData_OtherLivestock_MethaneConversionFactor_Title">_xlfn.LAMBDA("Other Livestock - Methane conversion factor per region")</definedName>
     <definedName name="SourceData_OtherLivestock.SourceData_OtherLivestock_MethaneConversionFactor_Unit">_xlfn.LAMBDA("fraction")</definedName>
     <definedName name="SourceData_OtherLivestock.SourceData_OtherLivestock_MethaneConversionFactor_Variable">_xlfn.LAMBDA("MCFim")</definedName>
     <definedName name="SourceData_OtherLivestock.SourceData_OtherLivestock_MethaneConversionFactor_Variation">_xlfn.LAMBDA("")</definedName>
-    <definedName name="SourceData_OtherLivestock.SourceData_OtherLivestock_NitrogenExcreted_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(9, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Other Livestock Type","NEj";"Buffalo",39.5;"Goats",7;"Deer",13.2;"Camels",39.5;"Alpacas",7;"Horses",39.5;"Mules/asses",13.2;"Emus/ostriches",7}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="SourceData_OtherLivestock.SourceData_OtherLivestock_MethaneEmissionsPotential_Data">_xlfn.LAMBDA(
+    _xlfn.MAKEARRAY(9, 3,
+      _xlfn.LAMBDA(_xlpm.r,_xlpm.c,
+        INDEX({"Other Livestock Type","BO","Taken from";"Buffalo",0.19,"Feedlot, Pasture beef";"Goats",0.24,"Sheep";"Deer",0.24,"Sheep";"Camels",0.24,"Sheep";"Alpacas",0.24,"Sheep";"Horses",0.19,"Feedlot, Pasture beef";"Mules/asses",0.24,"Sheep";"Emus/ostriches",0.36,"Poultry - meat chickens"}, _xlpm.r, _xlpm.c)
+      )
+    )
+  )</definedName>
+    <definedName name="SourceData_OtherLivestock.SourceData_OtherLivestock_MethaneEmissionsPotential_Source">_xlfn.LAMBDA("VEERG 2026: Table A.1.5.X")</definedName>
+    <definedName name="SourceData_OtherLivestock.SourceData_OtherLivestock_MethaneEmissionsPotential_Title">_xlfn.LAMBDA("Other Livestock - Methane emissions potential")</definedName>
+    <definedName name="SourceData_OtherLivestock.SourceData_OtherLivestock_MethaneEmissionsPotential_Unit">_xlfn.LAMBDA("m3 CH4 / kg VS")</definedName>
+    <definedName name="SourceData_OtherLivestock.SourceData_OtherLivestock_MethaneEmissionsPotential_Variable">_xlfn.LAMBDA("BO")</definedName>
+    <definedName name="SourceData_OtherLivestock.SourceData_OtherLivestock_MethaneEmissionsPotential_Variation">_xlfn.LAMBDA("VARIATION ON SOURCE: There were no values in VEERG so this data has been generated by using documented BO values from other livestock")</definedName>
+    <definedName name="SourceData_OtherLivestock.SourceData_OtherLivestock_NitrogenExcreted_Data">_xlfn.LAMBDA(
+    _xlfn.MAKEARRAY(9, 2,
+      _xlfn.LAMBDA(_xlpm.r,_xlpm.c,
+        INDEX({"Other Livestock Type","NEj";"Buffalo",39.5;"Goats",7;"Deer",13.2;"Camels",39.5;"Alpacas",7;"Horses",39.5;"Mules/asses",13.2;"Emus/ostriches",7}, _xlpm.r, _xlpm.c)
+      )
+    )
+  )</definedName>
     <definedName name="SourceData_OtherLivestock.SourceData_OtherLivestock_NitrogenExcreted_Source">_xlfn.LAMBDA("VEERG 2026: Table A.1.5.3")</definedName>
     <definedName name="SourceData_OtherLivestock.SourceData_OtherLivestock_NitrogenExcreted_Title">_xlfn.LAMBDA("Other Livestock - Nitrogen excreted per livestock type")</definedName>
     <definedName name="SourceData_OtherLivestock.SourceData_OtherLivestock_NitrogenExcreted_Unit">_xlfn.LAMBDA("kg N2O / head / year")</definedName>
@@ -4875,26 +4931,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Home"/>
-      <sheetName val="Constants - Common"/>
-      <sheetName val="Acknowledgements"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
 <rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
   <global>
@@ -4969,7 +5005,7 @@
     <tableColumn id="1" xr3:uid="{D57CB9BE-4423-4B3C-8812-0053460E9FD4}" name="Other livestock type">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_EntericFermentationEmissionFactor_Data(),Table_SourceData_OtherLivestock_EntericEF[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{076CA99E-B6FF-4452-AA90-21B8618FF161}" name="Mj" dataDxfId="54" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{076CA99E-B6FF-4452-AA90-21B8618FF161}" name="Mj" dataDxfId="18" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_EntericFermentationEmissionFactor_Data(),Table_SourceData_OtherLivestock_EntericEF[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5031,49 +5067,49 @@
     <tableColumn id="1" xr3:uid="{7E71225E-2AD7-4A13-9EBB-B77F4079285C}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{A2DABE99-D6E4-4F5F-8878-5C1A1B6DCCBE}" name="MAT" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{A2DABE99-D6E4-4F5F-8878-5C1A1B6DCCBE}" name="MAT" totalsRowDxfId="54" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{1B47ADC6-A8AF-44F6-9AC5-EAD632F652DF}" name="MAP" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
+    <tableColumn id="3" xr3:uid="{1B47ADC6-A8AF-44F6-9AC5-EAD632F652DF}" name="MAP" totalsRowDxfId="53" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{DE25E49E-3CF4-484F-8E89-D3FA3D6646DC}" name="Frost days per year" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
+    <tableColumn id="4" xr3:uid="{DE25E49E-3CF4-484F-8E89-D3FA3D6646DC}" name="Frost days per year" totalsRowDxfId="52" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{DAFC64A1-71DE-411E-BC93-E39255D47108}" name="Elevation" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
+    <tableColumn id="5" xr3:uid="{DAFC64A1-71DE-411E-BC93-E39255D47108}" name="Elevation" totalsRowDxfId="51" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{47FF84A2-6ECF-4E1E-897C-42257F6A9039}" name="MAP:PET" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
+    <tableColumn id="6" xr3:uid="{47FF84A2-6ECF-4E1E-897C-42257F6A9039}" name="MAP:PET" totalsRowDxfId="50" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{3E12B9C0-0D6B-456A-BF36-2B1551835148}" name="Min temp" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
+    <tableColumn id="7" xr3:uid="{3E12B9C0-0D6B-456A-BF36-2B1551835148}" name="Min temp" totalsRowDxfId="49" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{D9AE84AF-8B12-46DD-ABEA-2CE6983DE305}" name="Max temp" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
+    <tableColumn id="8" xr3:uid="{D9AE84AF-8B12-46DD-ABEA-2CE6983DE305}" name="Max temp" totalsRowDxfId="48" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{99F753C3-10C2-4AC4-B605-80BD63E4793E}" name="Min rainfall" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
+    <tableColumn id="9" xr3:uid="{99F753C3-10C2-4AC4-B605-80BD63E4793E}" name="Min rainfall" totalsRowDxfId="47" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{4D621138-C2ED-4858-BE43-B60126D7AE6D}" name="Max rainfall" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
+    <tableColumn id="10" xr3:uid="{4D621138-C2ED-4858-BE43-B60126D7AE6D}" name="Max rainfall" totalsRowDxfId="46" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{D0553375-7408-4726-A780-70F59A49CEBA}" name="Min frost days" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
+    <tableColumn id="11" xr3:uid="{D0553375-7408-4726-A780-70F59A49CEBA}" name="Min frost days" totalsRowDxfId="45" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{74E64BFF-B8FC-419E-8F74-484BBCE09FE7}" name="Max frost days" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
+    <tableColumn id="15" xr3:uid="{74E64BFF-B8FC-419E-8F74-484BBCE09FE7}" name="Max frost days" totalsRowDxfId="44" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{D47CB08C-DF83-4939-AEF0-82A4FA878F89}" name="Min elevation" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
+    <tableColumn id="12" xr3:uid="{D47CB08C-DF83-4939-AEF0-82A4FA878F89}" name="Min elevation" totalsRowDxfId="43" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{927942D3-9732-4B14-B047-72AD90A713EC}" name="Max elevation" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
+    <tableColumn id="16" xr3:uid="{927942D3-9732-4B14-B047-72AD90A713EC}" name="Max elevation" totalsRowDxfId="42" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{3096D6DC-E1EC-4C1B-9F1C-ED4C1687545C}" name="Min MAP:PET" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
+    <tableColumn id="13" xr3:uid="{3096D6DC-E1EC-4C1B-9F1C-ED4C1687545C}" name="Min MAP:PET" totalsRowDxfId="41" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{52FE9F47-7322-43C7-A986-BC8D24B6A4DF}" name="Max MAP:PET" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
+    <tableColumn id="17" xr3:uid="{52FE9F47-7322-43C7-A986-BC8D24B6A4DF}" name="Max MAP:PET" totalsRowDxfId="40" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5091,7 +5127,7 @@
     <tableColumn id="1" xr3:uid="{CFB94993-7174-41FB-A95E-C8EB63EEBCF2}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{159EDF8D-44CA-4285-BE19-435BFAD5D869}" name="Wet or Dry Zone" totalsRowDxfId="20" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{159EDF8D-44CA-4285-BE19-435BFAD5D869}" name="Wet or Dry Zone" totalsRowDxfId="39" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5197,7 +5233,7 @@
     <tableColumn id="1" xr3:uid="{81AD69B2-0790-418B-B2FC-CDA6FAB17038}" name="Is in leaching zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{0C4BCEEC-FFEA-4FEA-BB22-952F61FA30A4}" name="FracWET" dataDxfId="19">
+    <tableColumn id="2" xr3:uid="{0C4BCEEC-FFEA-4FEA-BB22-952F61FA30A4}" name="FracWET" dataDxfId="38">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5245,7 +5281,7 @@
     <tableColumn id="1" xr3:uid="{95008387-7F3F-4485-8FCE-8A32794362E3}" name="Irrigation type i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{059DE7C8-0474-44E0-BD18-285A24CB1466}" name="FracWET" dataDxfId="18" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{059DE7C8-0474-44E0-BD18-285A24CB1466}" name="FracWET" dataDxfId="37" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5254,16 +5290,16 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{75649617-63F2-4A80-A5EB-06A3280A3C57}" name="Table_SourceData_OtherLivestock_VolatileSolids" displayName="Table_SourceData_OtherLivestock_VolatileSolids" ref="D24:E32" totalsRowShown="0" dataDxfId="53" dataCellStyle="Content normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{75649617-63F2-4A80-A5EB-06A3280A3C57}" name="Table_SourceData_OtherLivestock_VolatileSolids" displayName="Table_SourceData_OtherLivestock_VolatileSolids" ref="D24:E32" totalsRowShown="0" dataDxfId="17" dataCellStyle="Content normal">
   <autoFilter ref="D24:E32" xr:uid="{75649617-63F2-4A80-A5EB-06A3280A3C57}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{3E3B834E-0F7A-47D3-954A-A57B2234370A}" name="Other livestock type" dataDxfId="52" dataCellStyle="Content normal">
+    <tableColumn id="1" xr3:uid="{3E3B834E-0F7A-47D3-954A-A57B2234370A}" name="Other livestock type" dataDxfId="16" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_VolatileSolidsProduced_Data(),Table_SourceData_OtherLivestock_VolatileSolids[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{0BCFF128-A246-43C6-BB57-DC9448A80579}" name="VSj" dataDxfId="51" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{0BCFF128-A246-43C6-BB57-DC9448A80579}" name="VSj" dataDxfId="15" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_VolatileSolidsProduced_Data(),Table_SourceData_OtherLivestock_VolatileSolids[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5281,7 +5317,7 @@
     <tableColumn id="1" xr3:uid="{77155640-BD72-4B68-B35F-A4CD6E6A62A8}" name="Climate zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{BBB29331-C081-48C9-9091-18B6ED4A9A17}" name="EFPRP" dataDxfId="17" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{BBB29331-C081-48C9-9091-18B6ED4A9A17}" name="EFPRP" dataDxfId="36" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5299,7 +5335,7 @@
     <tableColumn id="1" xr3:uid="{A7C99355-7BA1-47DA-875F-F4E6F476DBB2}" name="Month">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{F5F84847-B5B7-4FC3-A009-BA14974E995A}" name="Season" dataDxfId="16" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{F5F84847-B5B7-4FC3-A009-BA14974E995A}" name="Season" dataDxfId="35" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5331,49 +5367,49 @@
     <tableColumn id="1" xr3:uid="{BD957EFF-7EDC-40CC-A55D-B999F7D7743A}" name="Temperature zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{706B8784-ACBC-4772-B3C9-65B92B3A16EB}" name="MAT (ºC)" dataDxfId="15" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{706B8784-ACBC-4772-B3C9-65B92B3A16EB}" name="MAT (ºC)" dataDxfId="34" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{795ACF8C-E7E4-418E-98A0-B225F9A843E6}" name="Anaerobic lagoon" dataDxfId="14" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{795ACF8C-E7E4-418E-98A0-B225F9A843E6}" name="Anaerobic lagoon" dataDxfId="33" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{5BC1CAF8-6FF1-4B12-B99F-E7A50945C898}" name="Digester / covered lagoons" dataDxfId="13" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{5BC1CAF8-6FF1-4B12-B99F-E7A50945C898}" name="Digester / covered lagoons" dataDxfId="32" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{62BE04D5-5EFB-47DF-AB60-61BDB28DADDE}" name="Liquid systems" dataDxfId="12" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{62BE04D5-5EFB-47DF-AB60-61BDB28DADDE}" name="Liquid systems" dataDxfId="31" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{A6953F4C-4946-402C-9E9D-C1687F72E6ED}" name="Daily spread" dataDxfId="11" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{A6953F4C-4946-402C-9E9D-C1687F72E6ED}" name="Daily spread" dataDxfId="30" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{F371C1CC-B865-4590-8F58-947D0346A2D7}" name="Composting (passive windrow)" dataDxfId="10" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{F371C1CC-B865-4590-8F58-947D0346A2D7}" name="Composting (passive windrow)" dataDxfId="29" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{835C2A85-C159-4037-BFBB-BCA899795E46}" name="Solid storage" dataDxfId="9" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{835C2A85-C159-4037-BFBB-BCA899795E46}" name="Solid storage" dataDxfId="28" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{E69E8BF3-C20A-4351-9D54-945913459B31}" name="Pit storage" dataDxfId="8" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{E69E8BF3-C20A-4351-9D54-945913459B31}" name="Pit storage" dataDxfId="27" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{BFF7CD12-0D20-4D89-89E3-AF17D018FBE6}" name="Deep litter" dataDxfId="7" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{BFF7CD12-0D20-4D89-89E3-AF17D018FBE6}" name="Deep litter" dataDxfId="26" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{5EA7DE27-C6BB-4D98-965F-2EC7E4ACCB5D}" name="Poultry manure with bedding" dataDxfId="6" dataCellStyle="Content normal">
+    <tableColumn id="11" xr3:uid="{5EA7DE27-C6BB-4D98-965F-2EC7E4ACCB5D}" name="Poultry manure with bedding" dataDxfId="25" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{D1543B60-2A2B-42CA-B137-3673CEC6300F}" name="Poultry manure without bedding" dataDxfId="5" dataCellStyle="Content normal">
+    <tableColumn id="12" xr3:uid="{D1543B60-2A2B-42CA-B137-3673CEC6300F}" name="Poultry manure without bedding" dataDxfId="24" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{1C2B15FC-BC70-40B4-8E54-FFABE75F58F5}" name="Direct processing" dataDxfId="4" dataCellStyle="Content normal">
+    <tableColumn id="13" xr3:uid="{1C2B15FC-BC70-40B4-8E54-FFABE75F58F5}" name="Direct processing" dataDxfId="23" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{D7F32FFE-532A-43B4-A90F-AE77D9C2BB29}" name="Direct application" dataDxfId="3" dataCellStyle="Content normal">
+    <tableColumn id="14" xr3:uid="{D7F32FFE-532A-43B4-A90F-AE77D9C2BB29}" name="Direct application" dataDxfId="22" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{EB06045B-53A5-41D6-A443-5F04AE98854B}" name="Pasture range and paddock" dataDxfId="2" dataCellStyle="Content normal">
+    <tableColumn id="15" xr3:uid="{EB06045B-53A5-41D6-A443-5F04AE98854B}" name="Pasture range and paddock" dataDxfId="21" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{1A325EB4-E55C-4501-99C8-99066B0DF479}" name="MAT raw" dataDxfId="1" dataCellStyle="Content normal">
+    <tableColumn id="16" xr3:uid="{1A325EB4-E55C-4501-99C8-99066B0DF479}" name="MAT raw" dataDxfId="20" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5391,7 +5427,7 @@
     <tableColumn id="1" xr3:uid="{EFA2DB88-B766-4C17-A7C4-B6FAAD5B5EDD}" name="Climate Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{FE55D07E-17C7-451F-9E3F-9EEB68806A59}" name="EFNi &amp; EFN2Oi" dataDxfId="0" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{FE55D07E-17C7-451F-9E3F-9EEB68806A59}" name="EFNi &amp; EFN2Oi" dataDxfId="19" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5400,16 +5436,16 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{522C94C8-449D-4574-AF4D-39C274C53A6F}" name="Table_SourceData_OtherLivestock_NitrogenExcreted" displayName="Table_SourceData_OtherLivestock_NitrogenExcreted" ref="D39:E47" totalsRowShown="0" dataDxfId="50" dataCellStyle="Content normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{522C94C8-449D-4574-AF4D-39C274C53A6F}" name="Table_SourceData_OtherLivestock_NitrogenExcreted" displayName="Table_SourceData_OtherLivestock_NitrogenExcreted" ref="D39:E47" totalsRowShown="0" dataDxfId="14" dataCellStyle="Content normal">
   <autoFilter ref="D39:E47" xr:uid="{522C94C8-449D-4574-AF4D-39C274C53A6F}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{92CD5559-01AC-4144-B6DC-7F856864840C}" name="Other livestock type" dataDxfId="49" dataCellStyle="Content normal">
+    <tableColumn id="1" xr3:uid="{92CD5559-01AC-4144-B6DC-7F856864840C}" name="Other livestock type" dataDxfId="13" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_NitrogenExcreted_Data(),Table_SourceData_OtherLivestock_NitrogenExcreted[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{A4955FC2-927B-4DF6-B94C-068E74A6FF39}" name="NEj" dataDxfId="48" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{A4955FC2-927B-4DF6-B94C-068E74A6FF39}" name="NEj" dataDxfId="12" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_NitrogenExcreted_Data(),Table_SourceData_OtherLivestock_NitrogenExcreted[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5418,20 +5454,20 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{08C66B47-C28A-4E61-BD61-AB59792A938B}" name="Table_SourceData_OtherLivestock_AverageLiveweight" displayName="Table_SourceData_OtherLivestock_AverageLiveweight" ref="D54:F64" totalsRowShown="0" dataDxfId="47" dataCellStyle="Content normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{08C66B47-C28A-4E61-BD61-AB59792A938B}" name="Table_SourceData_OtherLivestock_AverageLiveweight" displayName="Table_SourceData_OtherLivestock_AverageLiveweight" ref="D54:F64" totalsRowShown="0" dataDxfId="11" dataCellStyle="Content normal">
   <autoFilter ref="D54:F64" xr:uid="{08C66B47-C28A-4E61-BD61-AB59792A938B}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{92B26601-57E2-4637-B097-133483C8744F}" name="Other livestock type" dataDxfId="46" dataCellStyle="Content normal">
+    <tableColumn id="1" xr3:uid="{92B26601-57E2-4637-B097-133483C8744F}" name="Other livestock type" dataDxfId="10" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_AverageLiveweight_Data(),Table_SourceData_OtherLivestock_AverageLiveweight[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{6D10B565-469B-4476-91DD-3E192D501AEC}" name="Wco" dataDxfId="45" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{6D10B565-469B-4476-91DD-3E192D501AEC}" name="Wco" dataDxfId="9" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_AverageLiveweight_Data(),Table_SourceData_OtherLivestock_AverageLiveweight[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{4285ACF1-A507-45A9-B06F-3C8A119CF7C4}" name="Wco2" dataDxfId="44" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{4285ACF1-A507-45A9-B06F-3C8A119CF7C4}" name="Wco2" dataDxfId="8" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_AverageLiveweight_Data(),Table_SourceData_OtherLivestock_AverageLiveweight[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5440,20 +5476,20 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{717E53D2-4463-4A85-80B5-5691AD7D98C8}" name="Table_SourceData_OtherLivestock_FractionWasteInMMS" displayName="Table_SourceData_OtherLivestock_FractionWasteInMMS" ref="D71:F79" totalsRowShown="0" dataDxfId="43" dataCellStyle="Content normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{717E53D2-4463-4A85-80B5-5691AD7D98C8}" name="Table_SourceData_OtherLivestock_FractionWasteInMMS" displayName="Table_SourceData_OtherLivestock_FractionWasteInMMS" ref="D71:F79" totalsRowShown="0" dataDxfId="7" dataCellStyle="Content normal">
   <autoFilter ref="D71:F79" xr:uid="{717E53D2-4463-4A85-80B5-5691AD7D98C8}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{3C1197CD-1D52-441D-BBC2-CD949C23252D}" name="Other livestock type" dataDxfId="42" dataCellStyle="Content normal">
+    <tableColumn id="1" xr3:uid="{3C1197CD-1D52-441D-BBC2-CD949C23252D}" name="Other livestock type" dataDxfId="6" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_FractionWasteInMMS_Data(),Table_SourceData_OtherLivestock_FractionWasteInMMS[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{8073D8FF-B3DA-4F6A-932F-294E074768D7}" name="Pasture range and paddock" dataDxfId="41" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{8073D8FF-B3DA-4F6A-932F-294E074768D7}" name="Pasture range and paddock" dataDxfId="5" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_FractionWasteInMMS_Data(),Table_SourceData_OtherLivestock_FractionWasteInMMS[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{BE446918-69F7-4B13-8457-24AF8D4D48BC}" name="Uncovered anaerobic lagoon" dataDxfId="40" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{BE446918-69F7-4B13-8457-24AF8D4D48BC}" name="Uncovered anaerobic lagoon" dataDxfId="4" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_FractionWasteInMMS_Data(),Table_SourceData_OtherLivestock_FractionWasteInMMS[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5462,20 +5498,20 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{AFA04BB4-DA20-428E-BF28-5455856D0A35}" name="Table_SourceData_OtherLivestock_MCF" displayName="Table_SourceData_OtherLivestock_MCF" ref="D86:F94" totalsRowShown="0" dataDxfId="39" dataCellStyle="Content normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{AFA04BB4-DA20-428E-BF28-5455856D0A35}" name="Table_SourceData_OtherLivestock_MCF" displayName="Table_SourceData_OtherLivestock_MCF" ref="D86:F94" totalsRowShown="0" dataDxfId="3" dataCellStyle="Content normal">
   <autoFilter ref="D86:F94" xr:uid="{AFA04BB4-DA20-428E-BF28-5455856D0A35}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{378D0529-B2BA-4B26-B22D-9D5AE994C705}" name="Other livestock type" dataDxfId="38" dataCellStyle="Content normal">
+    <tableColumn id="1" xr3:uid="{378D0529-B2BA-4B26-B22D-9D5AE994C705}" name="Other livestock type" dataDxfId="2" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_MethaneConversionFactor_Data(),Table_SourceData_OtherLivestock_MCF[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{614FC5E3-9067-4D7A-9048-5C785284F6FC}" name="Pasture range and paddock" dataDxfId="37" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{614FC5E3-9067-4D7A-9048-5C785284F6FC}" name="Pasture range and paddock" dataDxfId="1" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_MethaneConversionFactor_Data(),Table_SourceData_OtherLivestock_MCF[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{9125F130-A695-42FD-984B-66D9A47F338B}" name="Uncovered anaerobic lagoon" dataDxfId="36" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{9125F130-A695-42FD-984B-66D9A47F338B}" name="Uncovered anaerobic lagoon" dataDxfId="0" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_OtherLivestock.SourceData_OtherLivestock_MethaneConversionFactor_Data(),Table_SourceData_OtherLivestock_MCF[[#Headers],[Other livestock type]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -20184,30 +20220,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACkAKgAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADIAKQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAHQAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAC8AdABcAHUAMAAwADMAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAdQAwADAAMgA3AFwAIgAgAFwAdQAwADAAMgA2ACAAcwBoACAAXAB1ADAAMAAyADYAIABcACIAXAB1ADAAMAAyADcAIQBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFUATgBEACgAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIAAwACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAE0ATQBTACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAaQB0AGwAZQBDAGUAbABsACwAIABTAG8AdQByAGMAZQBDAGUAbABsACwAXABuACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAEwARQBGAFQAKABTAG8AdQByAGMAZQBDAGUAbABsACwAIABGAEkATgBEACgAXAAiACwAXAAiACwAIABTAG8AdQByAGMAZQBDAGUAbABsACkAIAAtADEAKQAsACAAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFwAIgAsACAAXAAiAFwAIgApACAAXAB1ADAAMAAyADYAIABcACIAIABcACIAIABcAHUAMAAwADIANgAgAFQAaQB0AGwAZQBDAGUAbABsAFwAbgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBcAG4AVABhAGIAbABlACAAQQAuADEALgA1AC4AMQA6ACAATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAARQBuAHQAZQByAGkAYwAgAGYAZQByAG0AZQBuAHQAYQB0AGkAbwBuACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGUAYQBjAGgAIABvAHQAaABlAHIAIABsAGkAdgBlAHMAdABvAGMAawAgAHQAeQBwAGUAIAAoAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAHkAZQBhAHIAKQAgACgATQBqACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawAgAC0AIABFAG4AdABlAHIAaQBjACAAZgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZQBhAGMAaAAgAG8AdABoAGUAcgAgAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGoAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAEMASAA0ACAALwAgAGgAZQBhAGQAIAAvACAAeQBlAGEAcgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuADEAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADIALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIABUAHkAcABlAFwAIgAsACAAXAAiAE0AagBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgB1AGYAZgBhAGwAbwBcACIALAAgADYAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAG8AYQB0AHMAXAAiACwAIAA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBlAHIAXAAiACwAIAAyADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBhAG0AZQBsAHMAXAAiACwAIAA0ADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBsAHAAYQBjAGEAcwBcACIALAAgADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABvAHIAcwBlAHMAXAAiACwAIAAxADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQB1AGwAZQBzAC8AYQBzAHMAZQBzAFwAIgAsACAAMQAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAbQB1AHMALwBvAHMAdAByAGkAYwBoAGUAcwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBvAGQAdQBjAGUAZABcAG4AVABhAGIAbABlACAAQQAuADEALgA1AC4AMgA6ACAATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAAVgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIABwAHIAbwBkAHUAYwBlAGQAIABiAHkAIABlAGEAYwBoACAAbwB0AGgAZQByACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlACAAKABrAGcAIABWAFMALwBoAGUAYQBkAC8AZABhAHkAKQAgACgAVgBTAGoAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBvAGQAdQBjAGUAZABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAAVgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIABwAHIAbwBkAHUAYwBlAGQAIABiAHkAIABlAGEAYwBoACAAbwB0AGgAZQByACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBvAGQAdQBjAGUAZABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBTAGoAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAG8AZAB1AGMAZQBkAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAAVgBTACAALwAgAGgAZQBhAGQAIAAvACAAZABhAHkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAG8AZAB1AGMAZQBkAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuADIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAG8AZAB1AGMAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBvAGQAdQBjAGUAZABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAyACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAAVAB5AHAAZQBcACIALAAgAFwAIgBWAFMAagBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgB1AGYAZgBhAGwAbwBcACIALAAgADIALgA3ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBvAGEAdABzAFwAIgAsACAAMAAuADMANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGUAZQByAFwAIgAsACAAMAAuADkAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAbQBlAGwAcwBcACIALAAgADIALgA3ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBsAHAAYQBjAGEAcwBcACIALAAgADAALgAzADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABvAHIAcwBlAHMAXAAiACwAIAAyAC4ANwAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AdQBsAGUAcwAvAGEAcwBzAGUAcwBcACIALAAgADAALgA5ADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAHUAcwAvAG8AcwB0AHIAaQBjAGgAZQBzAFwAIgAsACAAMAAuADMANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADUALgAzADoAIABPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawAgAC0AIABOAGkAdAByAG8AZwBlAG4AIABlAHgAYwByAGUAdABlAGQAIABwAGUAcgAgAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQAgACgAawBnACAATgAyAE8ALwBoAGUAYQBkAC8AeQBlAGEAcgApACAAKABOAEUAagApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawAgAC0AIABOAGkAdAByAG8AZwBlAG4AIABlAHgAYwByAGUAdABlAGQAIABwAGUAcgAgAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4ARQBqAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALwAgAGgAZQBhAGQAIAAvACAAeQBlAGEAcgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA1AC4AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADIALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIABUAHkAcABlAFwAIgAsACAAXAAiAE4ARQBqAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAHUAZgBmAGEAbABvAFwAIgAsACAAMwA5AC4ANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAG8AYQB0AHMAXAAiACwAIAA3AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGUAZQByAFwAIgAsACAAMQAzAC4AMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAbQBlAGwAcwBcACIALAAgADMAOQAuADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBsAHAAYQBjAGEAcwBcACIALAAgADcALgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHMAZQBzAFwAIgAsACAAMwA5AC4ANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAHUAbABlAHMALwBhAHMAcwBlAHMAXAAiACwAIAAxADMALgAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAbQB1AHMALwBvAHMAdAByAGkAYwBoAGUAcwBcACIALAAgADcALgAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABcAG4AVABhAGIAbABlACAAQQAuADEALgA1AC4ANAA6ACAATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAAQQB2AGUAcgBhAGcAZQAgAEwAaQB2AGUAdwBlAGkAZwBoAHQAcwAgACgAVwBjAG8AKQAgACgAawBnACkAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawAgAC0AIABBAHYAZQByAGEAZwBlACAATABpAHYAZQB3AGUAaQBnAGgAdABzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBXAGMAbwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADUALgA0AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMwAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawAgAFQAeQBwAGUAIABqAFwAIgAsACAAXAAiAEEAdgBlAHIAYQBnAGUAIABMAGkAdgBlAHcAZQBpAGcAaAB0AFwAIgAsACAAXAAiAEEAdgBlAHIAYQBnAGUAIABMAGkAdgBlAHcAZQBpAGcAaAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAHUAZgBmAGEAbABvAFwAIgAsACAAMwAzADYALAAgAFwAIgAtAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAG8AYQB0AHMAXAAiACwAIAAzADMALAAgAFwAIgAyADgAawBnACAALQAgAGwAbwB3ACAAcAByAG8AZAB1AGMAdABpAHYAaQB0AHkAIABzAHkAcwB0AGUAbQBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAG8AYQB0AHMAXAAiACwAIAAzADMALAAgAFwAIgA1ADAAawBnACAALQAgAGgAaQBnAGgAIABwAHIAbwBkAHUAYwB0AGkAdgBpAHQAeQAgAHMAeQBzAHQAZQBtAHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBlAHIAXAAiACwAIAAxADIAMAAsACAAMQAyADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBhAG0AZQBsAHMAXAAiACwAIAAyADEANwAsACAANQA3ADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBsAHAAYQBjAGEAcwBcACIALAAgAFwAIgAtAFwAIgAsACAANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHMAZQBzAFwAIgAsACAAMwA3ADcALAAgADUANQAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AdQBsAGUAcwAvAGEAcwBzAGUAcwBcACIALAAgADEAMwAwACwAIAAyADQANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AdQBzAC8AbwBzAHQAcgBpAGMAaABlAHMAXAAiACwAIAAxADIAMAAsACAAMQAyADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBlAGYAZQByAGUAbgBjAGUAXAAiACwAIABcACIASQBQAEMAQwAgADIAMAAxADkAIABUAGEAYgBsAGUAIAAxADAAQQAuADUAIABbADIAXQBcACIALAAgAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFQAYQBiAGwAZQAgADEAMAAuADEAMAAgAFsAMgBdAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAHQAaQBvAG4AVwBhAHMAdABlAEkAbgBNAE0AUwBcAG4AVABhAGIAbABlACAAQQAuADEALgA1AC4ANQA6ACAATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAARgByAGEAYwB0AGkAbwBuACAAbwBmACAAdwBhAHMAdABlACAAaQBuACAAZQBhAGMAaAAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdAAgAHMAeQBzAHQAZQBtACAAKABmAHIAYQBjAHQAaQBvAG4AKQAgACgATQBNAFMAbQApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAHQAaQBvAG4AVwBhAHMAdABlAEkAbgBNAE0AUwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAARgByAGEAYwB0AGkAbwBuACAAbwBmACAAdwBhAHMAdABlACAAaQBuACAAZQBhAGMAaAAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdAAgAHMAeQBzAHQAZQBtAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwB0AGkAbwBuAFcAYQBzAHQAZQBJAG4ATQBNAFMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATQBTAG0AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAHQAaQBvAG4AVwBhAHMAdABlAEkAbgBNAE0AUwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMAdABpAG8AbgBXAGEAcwB0AGUASQBuAE0ATQBTAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuADUAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAHQAaQBvAG4AVwBhAHMAdABlAEkAbgBNAE0AUwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMAdABpAG8AbgBXAGEAcwB0AGUASQBuAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXAAiACwAIABcACIAVQBuAGMAbwB2AGUAcgBlAGQAIABBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAEMAVABcACIALAAgACAAOQA5AC4ANgA2ACwAIAAgADAALgAzADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBTAFcAXAAiACwAIAAgADkAOQAuADYANgAsACAAIAAwAC4AMwA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AVABcACIALAAgACAAOQA5AC4ANgA2ACwAIAAgADAALgAzADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBMAEQAXAAiACwAIAAgADkAOQAuADYANgAsACAAIAAwAC4AMwA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAQQBcACIALAAgACAAOQA5AC4ANgA2ACwAIAAgADAALgAzADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABBAFMAXAAiACwAIAAgADkAOQAuADYANgAsACAAIAAwAC4AMwA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYASQBDAFwAIgAsACAAIAA5ADkALgA2ADYALAAgACAAMAAuADMANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAEEAXAAiACwAIAAgADkAOQAuADYANgAsACAAIAAwAC4AMwA0AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBcAG4AVABhAGIAbABlACAAQQAuADEALgA1AC4ANgA6ACAATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAcgBlAGcAaQBvAG4AIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawAgAC0AIABNAGUAdABoAGEAbgBlACAAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAcABlAHIAIAByAGUAZwBpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBDAEYAaQBtAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuADYAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMwAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAQwBUAFwAIgAsACAAIAAwAC4AMAAwADQANwAsACAAIAAwAC4ANwAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AUwBXAFwAIgAsACAAIAAwAC4AMAAwADQANwAsACAAIAAwAC4ANwA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AVABcACIALAAgACAAMAAuADAAMAA0ADcALAAgACAAMAAuADgAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAEwARABcACIALAAgACAAMAAuADAAMAA0ADcALAAgACAAMAAuADcAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEEAXAAiACwAIAAgADAALgAwADAANAA3ACwAIAAgADAALgA3ADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABBAFMAXAAiACwAIAAgADAALgAwADAANAA3ACwAIAAgADAALgA3ADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBJAEMAXAAiACwAIAAgADAALgAwADAANAA3ACwAIAAgADAALgA3ADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBBAFwAIgAsACAAIAAwAC4AMAAwADQANwAsACAAIAAwAC4ANwA2AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuAFgAOgAgAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAALQAgAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAKABtADMAIABDAEgANAAgAC8AIABrAGcAIABWAFMAKQAgACgAQgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAALQAgAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHAAbwB0AGUAbgB0AGkAYQBsAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQgBPAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAG0AMwAgAEMASAA0ACAALwAgAGsAZwAgAFYAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA1AC4AWABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6ACAAVABoAGUAcgBlACAAdwBlAHIAZQAgAG4AbwAgAHYAYQBsAHUAZQBzACAAaQBuACAAVgBFAEUAUgBHACAAcwBvACAAdABoAGkAcwAgAGQAYQB0AGEAIABoAGEAcwAgAGIAZQBlAG4AIABnAGUAbgBlAHIAYQB0AGUAZAAgAGIAeQAgAHUAcwBpAG4AZwAgAGQAbwBjAHUAbQBlAG4AdABlAGQAIABCAE8AIAB2AGEAbAB1AGUAcwAgAGYAcgBvAG0AIABvAHQAaABlAHIAIABsAGkAdgBlAHMAdABvAGMAawBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMwAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawAgAFQAeQBwAGUAXAAiACwAIABcACIAQgBPAFwAIgAsACAAXAAiAFQAYQBrAGUAbgAgAGYAcgBvAG0AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBmAGYAYQBsAG8AXAAiACwAIAAwAC4AMQA5ACwAIABcACIARgBlAGUAZABsAG8AdAAsACAAUABhAHMAdAB1AHIAZQAgAGIAZQBlAGYAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAbwBhAHQAcwBcACIALAAgADAALgAyADQALAAgAFwAIgBTAGgAZQBlAHAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBlAHIAXAAiACwAIAAwAC4AMgA0ACwAIABcACIAUwBoAGUAZQBwAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAbQBlAGwAcwBcACIALAAgADAALgAyADQALAAgAFwAIgBTAGgAZQBlAHAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbABwAGEAYwBhAHMAXAAiACwAIAAwAC4AMgA0ACwAIABcACIAUwBoAGUAZQBwAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgBzAGUAcwBcACIALAAgADAALgAxADkALAAgAFwAIgBGAGUAZQBkAGwAbwB0ACwAIABQAGEAcwB0AHUAcgBlACAAYgBlAGUAZgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQB1AGwAZQBzAC8AYQBzAHMAZQBzAFwAIgAsACAAMAAuADIANAAsACAAXAAiAFMAaABlAGUAcABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAHUAcwAvAG8AcwB0AHIAaQBjAGgAZQBzAFwAIgAsACAAMAAuADMANgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIAAtACAAbQBlAGEAdAAgAGMAaABpAGMAawBlAG4AcwBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGYAcgBvAG0AIAB1AHIAaQBuAGUAIABhAG4AZAAgAGYAYQBlAGMAZQBzACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAZgByAG8AbQAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZgBhAGUAYwBlAHMAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBHAEEAUwBNAHMAbwBpAGwAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgBIADMALQBOACAAKwAgAE4ATwB4AC0ATgApAC8AawBnACAATgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMARwBBAFMATQBTAG8AaQBsAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgA3AC4AMgAuADMAIABDAE8ATgBTAFQAQQBOAFQAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMARwBBAFMATQBTAG8AaQBsAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgAyADEAKQA7AFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMwAuADYAOgAgAEUAbgB0AGUAcgBpAGMAIABNAGUAdABoAGEAbgBlACAALQAgAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAzAC4ANgAuADEALgAxACAATQBlAHQAaABvAGQAIAAxACAALQAgAEUAbgB0AGUAcgBpAGMAIABPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADMAXwA2AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAFwAbgBUAG8AdABhAGwAIABhAG4AbgB1AGEAbAAgAG0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAGUAbgB0AGUAcgBpAGMAIABmAGUAcgBtAGUAbgB0AGEAdABpAG8AbgAgAGkAbgAgAG8AdABoAGUAcgAgAGwAaQB2AGUAcwB0AG8AYwBrAFwAbgBFAF8AZQBuAHQAZQByAGkAYwBcAG4AdAAgAEMASAA0AFwAbgBFAF8AewBlAG4AdABlAHIAaQBjAH0APQBcAFwAcwB1AG0AXwBqACgATgBfAGoAXABcAHQAaQBtAGUAcwAgAE0AXwBqACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXABuAE4AXwBqACAAPQAgAG4AdQBtAGIAZQByACAAbwBmACAAbABpAHYAZQBzAHQAbwBjAGsAIABvAGYAIABlAGEAYwBoACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlACAAagAgACgAaABlAGEAZAApAFwAbgBNAF8AagAgAD0AIABlAG4AdABlAHIAaQBjACAAZgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgACgAawBnACAAQwBIADQALwBoAGUAYQBkAC8AeQBlAGEAcgApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADMAXwA2AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE4AXwBqACwAIABNAF8AagAsAFwAbgAgACAAIAAgAFMAVQBNACgATgBfAGoAIAAqACAATQBfAGoAKQAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADYAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAbwB0AGEAbAAgAGEAbgBuAHUAYQBsACAAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAZQBuAHQAZQByAGkAYwAgAGYAZQByAG0AZQBuAHQAYQB0AGkAbwBuACAAaQBuACAAbwB0AGgAZQByACAAbABpAHYAZQBzAHQAbwBjAGsAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwA2AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AZQBuAHQAZQByAGkAYwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADYAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBIADQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwA2AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADMALgA2AC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8ANgBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADYAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewBlAG4AdABlAHIAaQBjAH0APQBcAFwAcwB1AG0AXwBqACgATgBfAGoAXABcAHQAaQBtAGUAcwAgAE0AXwBqACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwA2AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AXwBqAFwAIgAsACAAXAAiAG4AdQBtAGIAZQByACAAbwBmACAAbABpAHYAZQBzAHQAbwBjAGsAIABvAGYAIABlAGEAYwBoACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlACAAagBcACIALAAgAFwAIgBoAGUAYQBkAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBfAGoAXAAiACwAIABcACIAZQBuAHQAZQByAGkAYwAgAGYAZQByAG0AZQBuAHQAYQB0AGkAbwBuACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAXAAiACwAIABcACIAawBnACAAQwBIADQALwBoAGUAYQBkAC8AeQBlAGEAcgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGoAXAAiACwAIABcACIAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMwBfADQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEcAZQB0AE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBvAGQAdQBjAGUAZABfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAbwBkAHUAYwBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAG8AZAB1AGMAZQBkAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAbwBkAHUAYwBlAGQAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAbwBkAHUAYwBlAGQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAbwBkAHUAYwBlAGQAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwB0AGkAbwBuAFcAYQBzAHQAZQBJAG4ATQBNAFMAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAHQAaQBvAG4AVwBhAHMAdABlAEkAbgBNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMAdABpAG8AbgBXAGEAcwB0AGUASQBuAE0ATQBTAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMAdABpAG8AbgBXAGEAcwB0AGUASQBuAE0ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAHQAaQBvAG4AVwBhAHMAdABlAEkAbgBNAE0AUwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwB0AGkAbwBuAFcAYQBzAHQAZQBJAG4ATQBNAFMAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBEAGEAdABhACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADYAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8ANgBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFQAaQB0AGwAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwA2AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADYAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADYAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwA2AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8ANgBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8ANgBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAcgBnAHUAbQBlAG4AdABzACIAXQAsACIAbABvAGMAYQBsAGUAIgA6AHsAIgBsAGkAcwB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAcgBvAHcAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBjAG8AbAB1AG0AbgBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUABvAHMAaQB0AGkAbwBuAHMAIgA6AFsAMwBdACwAIgBkAGUAYwBpAG0AYQBsAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiAC4AIgAsACIAZABhAHQAZQBPAHIAZABlAHIAIgA6ACIARABNAFkAIgAsACIAYwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsACIAOgAiACQAIgAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbABMAGUAYQBkACIAOgB0AHIAdQBlACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAZQBwAEIAeQBTAHAAYQBjAGUAIgA6AGYAYQBsAHMAZQAsACIAcgBvAHcATABlAHQAdABlAHIAIgA6ACIAUgAiACwAIgBjAG8AbAB1AG0AbgBMAGUAdAB0AGUAcgAiADoAIgBDACIALAAiAHIAYwBMAGUAZgB0AEIAcgBhAGMAawBlAHQAIgA6ACIAWwAiACwAIgByAGMAUgBpAGcAaAB0AEIAcgBhAGMAawBlAHQAIgA6ACIAXQAiACwAIgBzAHQAYQB0AGUAbQBlAG4AdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGwAbwBjAGEAbABlAE4AYQBtAGUAIgA6ACIAZQBuAC0AdQBzACIAfQB9AA==</AFEJSONBlob>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -20402,34 +20414,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
-    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACkAKgAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADIAKQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAHQAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAC8AdABcAHUAMAAwADMAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAdQAwADAAMgA3AFwAIgAgAFwAdQAwADAAMgA2ACAAcwBoACAAXAB1ADAAMAAyADYAIABcACIAXAB1ADAAMAAyADcAIQBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFUATgBEACgAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIAAwACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAE0ATQBTACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAaQB0AGwAZQBDAGUAbABsACwAIABTAG8AdQByAGMAZQBDAGUAbABsACwAXABuACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAEwARQBGAFQAKABTAG8AdQByAGMAZQBDAGUAbABsACwAIABGAEkATgBEACgAXAAiACwAXAAiACwAIABTAG8AdQByAGMAZQBDAGUAbABsACkAIAAtADEAKQAsACAAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFwAIgAsACAAXAAiAFwAIgApACAAXAB1ADAAMAAyADYAIABcACIAIABcACIAIABcAHUAMAAwADIANgAgAFQAaQB0AGwAZQBDAGUAbABsAFwAbgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBcAG4AVABhAGIAbABlACAAQQAuADEALgA1AC4AMQA6ACAATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAARQBuAHQAZQByAGkAYwAgAGYAZQByAG0AZQBuAHQAYQB0AGkAbwBuACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGUAYQBjAGgAIABvAHQAaABlAHIAIABsAGkAdgBlAHMAdABvAGMAawAgAHQAeQBwAGUAIAAoAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAHkAZQBhAHIAKQAgACgATQBqACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawAgAC0AIABFAG4AdABlAHIAaQBjACAAZgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZQBhAGMAaAAgAG8AdABoAGUAcgAgAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGoAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAEMASAA0ACAALwAgAGgAZQBhAGQAIAAvACAAeQBlAGEAcgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuADEAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADIALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIABUAHkAcABlAFwAIgAsACAAXAAiAE0AagBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgB1AGYAZgBhAGwAbwBcACIALAAgADYAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAG8AYQB0AHMAXAAiACwAIAA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBlAHIAXAAiACwAIAAyADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBhAG0AZQBsAHMAXAAiACwAIAA0ADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBsAHAAYQBjAGEAcwBcACIALAAgADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABvAHIAcwBlAHMAXAAiACwAIAAxADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQB1AGwAZQBzAC8AYQBzAHMAZQBzAFwAIgAsACAAMQAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAbQB1AHMALwBvAHMAdAByAGkAYwBoAGUAcwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBvAGQAdQBjAGUAZABcAG4AVABhAGIAbABlACAAQQAuADEALgA1AC4AMgA6ACAATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAAVgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIABwAHIAbwBkAHUAYwBlAGQAIABiAHkAIABlAGEAYwBoACAAbwB0AGgAZQByACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlACAAKABrAGcAIABWAFMALwBoAGUAYQBkAC8AZABhAHkAKQAgACgAVgBTAGoAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBvAGQAdQBjAGUAZABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAAVgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIABwAHIAbwBkAHUAYwBlAGQAIABiAHkAIABlAGEAYwBoACAAbwB0AGgAZQByACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBvAGQAdQBjAGUAZABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBTAGoAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAG8AZAB1AGMAZQBkAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAAVgBTACAALwAgAGgAZQBhAGQAIAAvACAAZABhAHkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAG8AZAB1AGMAZQBkAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuADIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAG8AZAB1AGMAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBvAGQAdQBjAGUAZABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAyACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAAVAB5AHAAZQBcACIALAAgAFwAIgBWAFMAagBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgB1AGYAZgBhAGwAbwBcACIALAAgADIALgA3ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBvAGEAdABzAFwAIgAsACAAMAAuADMANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGUAZQByAFwAIgAsACAAMAAuADkAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAbQBlAGwAcwBcACIALAAgADIALgA3ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBsAHAAYQBjAGEAcwBcACIALAAgADAALgAzADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABvAHIAcwBlAHMAXAAiACwAIAAyAC4ANwAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AdQBsAGUAcwAvAGEAcwBzAGUAcwBcACIALAAgADAALgA5ADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAHUAcwAvAG8AcwB0AHIAaQBjAGgAZQBzAFwAIgAsACAAMAAuADMANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADUALgAzADoAIABPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawAgAC0AIABOAGkAdAByAG8AZwBlAG4AIABlAHgAYwByAGUAdABlAGQAIABwAGUAcgAgAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQAgACgAawBnACAATgAyAE8ALwBoAGUAYQBkAC8AeQBlAGEAcgApACAAKABOAEUAagApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawAgAC0AIABOAGkAdAByAG8AZwBlAG4AIABlAHgAYwByAGUAdABlAGQAIABwAGUAcgAgAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4ARQBqAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALwAgAGgAZQBhAGQAIAAvACAAeQBlAGEAcgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA1AC4AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADIALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIABUAHkAcABlAFwAIgAsACAAXAAiAE4ARQBqAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAHUAZgBmAGEAbABvAFwAIgAsACAAMwA5AC4ANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAG8AYQB0AHMAXAAiACwAIAA3AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGUAZQByAFwAIgAsACAAMQAzAC4AMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAbQBlAGwAcwBcACIALAAgADMAOQAuADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBsAHAAYQBjAGEAcwBcACIALAAgADcALgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHMAZQBzAFwAIgAsACAAMwA5AC4ANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAHUAbABlAHMALwBhAHMAcwBlAHMAXAAiACwAIAAxADMALgAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAbQB1AHMALwBvAHMAdAByAGkAYwBoAGUAcwBcACIALAAgADcALgAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABcAG4AVABhAGIAbABlACAAQQAuADEALgA1AC4ANAA6ACAATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAAQQB2AGUAcgBhAGcAZQAgAEwAaQB2AGUAdwBlAGkAZwBoAHQAcwAgACgAVwBjAG8AKQAgACgAawBnACkAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawAgAC0AIABBAHYAZQByAGEAZwBlACAATABpAHYAZQB3AGUAaQBnAGgAdABzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBXAGMAbwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADUALgA0AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMwAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawAgAFQAeQBwAGUAIABqAFwAIgAsACAAXAAiAEEAdgBlAHIAYQBnAGUAIABMAGkAdgBlAHcAZQBpAGcAaAB0AFwAIgAsACAAXAAiAEEAdgBlAHIAYQBnAGUAIABMAGkAdgBlAHcAZQBpAGcAaAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAHUAZgBmAGEAbABvAFwAIgAsACAAMwAzADYALAAgAFwAIgAtAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAG8AYQB0AHMAXAAiACwAIAAzADMALAAgAFwAIgAyADgAawBnACAALQAgAGwAbwB3ACAAcAByAG8AZAB1AGMAdABpAHYAaQB0AHkAIABzAHkAcwB0AGUAbQBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAG8AYQB0AHMAXAAiACwAIAAzADMALAAgAFwAIgA1ADAAawBnACAALQAgAGgAaQBnAGgAIABwAHIAbwBkAHUAYwB0AGkAdgBpAHQAeQAgAHMAeQBzAHQAZQBtAHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBlAHIAXAAiACwAIAAxADIAMAAsACAAMQAyADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBhAG0AZQBsAHMAXAAiACwAIAAyADEANwAsACAANQA3ADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBsAHAAYQBjAGEAcwBcACIALAAgAFwAIgAtAFwAIgAsACAANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHMAZQBzAFwAIgAsACAAMwA3ADcALAAgADUANQAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AdQBsAGUAcwAvAGEAcwBzAGUAcwBcACIALAAgADEAMwAwACwAIAAyADQANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AdQBzAC8AbwBzAHQAcgBpAGMAaABlAHMAXAAiACwAIAAxADIAMAAsACAAMQAyADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBlAGYAZQByAGUAbgBjAGUAXAAiACwAIABcACIASQBQAEMAQwAgADIAMAAxADkAIABUAGEAYgBsAGUAIAAxADAAQQAuADUAIABbADIAXQBcACIALAAgAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFQAYQBiAGwAZQAgADEAMAAuADEAMAAgAFsAMgBdAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAHQAaQBvAG4AVwBhAHMAdABlAEkAbgBNAE0AUwBcAG4AVABhAGIAbABlACAAQQAuADEALgA1AC4ANQA6ACAATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAARgByAGEAYwB0AGkAbwBuACAAbwBmACAAdwBhAHMAdABlACAAaQBuACAAZQBhAGMAaAAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdAAgAHMAeQBzAHQAZQBtACAAKABmAHIAYQBjAHQAaQBvAG4AKQAgACgATQBNAFMAbQApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAHQAaQBvAG4AVwBhAHMAdABlAEkAbgBNAE0AUwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAARgByAGEAYwB0AGkAbwBuACAAbwBmACAAdwBhAHMAdABlACAAaQBuACAAZQBhAGMAaAAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdAAgAHMAeQBzAHQAZQBtAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwB0AGkAbwBuAFcAYQBzAHQAZQBJAG4ATQBNAFMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATQBTAG0AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAHQAaQBvAG4AVwBhAHMAdABlAEkAbgBNAE0AUwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMAdABpAG8AbgBXAGEAcwB0AGUASQBuAE0ATQBTAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuADUAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAHQAaQBvAG4AVwBhAHMAdABlAEkAbgBNAE0AUwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMAdABpAG8AbgBXAGEAcwB0AGUASQBuAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXAAiACwAIABcACIAVQBuAGMAbwB2AGUAcgBlAGQAIABBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAEMAVABcACIALAAgACAAOQA5AC4ANgA2ACwAIAAgADAALgAzADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBTAFcAXAAiACwAIAAgADkAOQAuADYANgAsACAAIAAwAC4AMwA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AVABcACIALAAgACAAOQA5AC4ANgA2ACwAIAAgADAALgAzADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBMAEQAXAAiACwAIAAgADkAOQAuADYANgAsACAAIAAwAC4AMwA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAQQBcACIALAAgACAAOQA5AC4ANgA2ACwAIAAgADAALgAzADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABBAFMAXAAiACwAIAAgADkAOQAuADYANgAsACAAIAAwAC4AMwA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYASQBDAFwAIgAsACAAIAA5ADkALgA2ADYALAAgACAAMAAuADMANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAEEAXAAiACwAIAAgADkAOQAuADYANgAsACAAIAAwAC4AMwA0AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBcAG4AVABhAGIAbABlACAAQQAuADEALgA1AC4ANgA6ACAATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAcgBlAGcAaQBvAG4AIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawAgAC0AIABNAGUAdABoAGEAbgBlACAAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAcABlAHIAIAByAGUAZwBpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBDAEYAaQBtAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuADYAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMwAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAQwBUAFwAIgAsACAAIAAwAC4AMAAwADQANwAsACAAIAAwAC4ANwAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AUwBXAFwAIgAsACAAIAAwAC4AMAAwADQANwAsACAAIAAwAC4ANwA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AVABcACIALAAgACAAMAAuADAAMAA0ADcALAAgACAAMAAuADgAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAEwARABcACIALAAgACAAMAAuADAAMAA0ADcALAAgACAAMAAuADcAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEEAXAAiACwAIAAgADAALgAwADAANAA3ACwAIAAgADAALgA3ADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABBAFMAXAAiACwAIAAgADAALgAwADAANAA3ACwAIAAgADAALgA3ADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBJAEMAXAAiACwAIAAgADAALgAwADAANAA3ACwAIAAgADAALgA3ADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBBAFwAIgAsACAAIAAwAC4AMAAwADQANwAsACAAIAAwAC4ANwA2AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuAFgAOgAgAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAALQAgAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAKABtADMAIABDAEgANAAgAC8AIABrAGcAIABWAFMAKQAgACgAQgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAALQAgAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHAAbwB0AGUAbgB0AGkAYQBsAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQgBPAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAG0AMwAgAEMASAA0ACAALwAgAGsAZwAgAFYAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA1AC4AWABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6ACAAVABoAGUAcgBlACAAdwBlAHIAZQAgAG4AbwAgAHYAYQBsAHUAZQBzACAAaQBuACAAVgBFAEUAUgBHACAAcwBvACAAdABoAGkAcwAgAGQAYQB0AGEAIABoAGEAcwAgAGIAZQBlAG4AIABnAGUAbgBlAHIAYQB0AGUAZAAgAGIAeQAgAHUAcwBpAG4AZwAgAGQAbwBjAHUAbQBlAG4AdABlAGQAIABCAE8AIAB2AGEAbAB1AGUAcwAgAGYAcgBvAG0AIABvAHQAaABlAHIAIABsAGkAdgBlAHMAdABvAGMAawBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMwAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawAgAFQAeQBwAGUAXAAiACwAIABcACIAQgBPAFwAIgAsACAAXAAiAFQAYQBrAGUAbgAgAGYAcgBvAG0AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBmAGYAYQBsAG8AXAAiACwAIAAwAC4AMQA5ACwAIABcACIARgBlAGUAZABsAG8AdAAsACAAUABhAHMAdAB1AHIAZQAgAGIAZQBlAGYAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAbwBhAHQAcwBcACIALAAgADAALgAyADQALAAgAFwAIgBTAGgAZQBlAHAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBlAHIAXAAiACwAIAAwAC4AMgA0ACwAIABcACIAUwBoAGUAZQBwAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAbQBlAGwAcwBcACIALAAgADAALgAyADQALAAgAFwAIgBTAGgAZQBlAHAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbABwAGEAYwBhAHMAXAAiACwAIAAwAC4AMgA0ACwAIABcACIAUwBoAGUAZQBwAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgBzAGUAcwBcACIALAAgADAALgAxADkALAAgAFwAIgBGAGUAZQBkAGwAbwB0ACwAIABQAGEAcwB0AHUAcgBlACAAYgBlAGUAZgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQB1AGwAZQBzAC8AYQBzAHMAZQBzAFwAIgAsACAAMAAuADIANAAsACAAXAAiAFMAaABlAGUAcABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAHUAcwAvAG8AcwB0AHIAaQBjAGgAZQBzAFwAIgAsACAAMAAuADMANgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIAAtACAAbQBlAGEAdAAgAGMAaABpAGMAawBlAG4AcwBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGYAcgBvAG0AIAB1AHIAaQBuAGUAIABhAG4AZAAgAGYAYQBlAGMAZQBzACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAZgByAG8AbQAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZgBhAGUAYwBlAHMAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBHAEEAUwBNAHMAbwBpAGwAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgBIADMALQBOACAAKwAgAE4ATwB4AC0ATgApAC8AawBnACAATgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMARwBBAFMATQBTAG8AaQBsAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgA3AC4AMgAuADMAIABDAE8ATgBTAFQAQQBOAFQAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMARwBBAFMATQBTAG8AaQBsAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgAyADEAKQA7AFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMwAuADYAOgAgAEUAbgB0AGUAcgBpAGMAIABNAGUAdABoAGEAbgBlACAALQAgAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAzAC4ANgAuADEALgAxACAATQBlAHQAaABvAGQAIAAxACAALQAgAEUAbgB0AGUAcgBpAGMAIABPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADMAXwA2AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAFwAbgBUAG8AdABhAGwAIABhAG4AbgB1AGEAbAAgAG0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAGUAbgB0AGUAcgBpAGMAIABmAGUAcgBtAGUAbgB0AGEAdABpAG8AbgAgAGkAbgAgAG8AdABoAGUAcgAgAGwAaQB2AGUAcwB0AG8AYwBrAFwAbgBFAF8AZQBuAHQAZQByAGkAYwBcAG4AdAAgAEMASAA0AFwAbgBFAF8AewBlAG4AdABlAHIAaQBjAH0APQBcAFwAcwB1AG0AXwBqACgATgBfAGoAXABcAHQAaQBtAGUAcwAgAE0AXwBqACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXABuAE4AXwBqACAAPQAgAG4AdQBtAGIAZQByACAAbwBmACAAbABpAHYAZQBzAHQAbwBjAGsAIABvAGYAIABlAGEAYwBoACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlACAAagAgACgAaABlAGEAZAApAFwAbgBNAF8AagAgAD0AIABlAG4AdABlAHIAaQBjACAAZgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgACgAawBnACAAQwBIADQALwBoAGUAYQBkAC8AeQBlAGEAcgApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADMAXwA2AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE4AXwBqACwAIABNAF8AagAsAFwAbgAgACAAIAAgAFMAVQBNACgATgBfAGoAIAAqACAATQBfAGoAKQAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADYAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAbwB0AGEAbAAgAGEAbgBuAHUAYQBsACAAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAZQBuAHQAZQByAGkAYwAgAGYAZQByAG0AZQBuAHQAYQB0AGkAbwBuACAAaQBuACAAbwB0AGgAZQByACAAbABpAHYAZQBzAHQAbwBjAGsAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwA2AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AZQBuAHQAZQByAGkAYwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADYAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBIADQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwA2AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADMALgA2AC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8ANgBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADYAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewBlAG4AdABlAHIAaQBjAH0APQBcAFwAcwB1AG0AXwBqACgATgBfAGoAXABcAHQAaQBtAGUAcwAgAE0AXwBqACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwA2AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AXwBqAFwAIgAsACAAXAAiAG4AdQBtAGIAZQByACAAbwBmACAAbABpAHYAZQBzAHQAbwBjAGsAIABvAGYAIABlAGEAYwBoACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlACAAagBcACIALAAgAFwAIgBoAGUAYQBkAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBfAGoAXAAiACwAIABcACIAZQBuAHQAZQByAGkAYwAgAGYAZQByAG0AZQBuAHQAYQB0AGkAbwBuACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAXAAiACwAIABcACIAawBnACAAQwBIADQALwBoAGUAYQBkAC8AeQBlAGEAcgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGoAXAAiACwAIABcACIAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMwBfADQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEcAZQB0AE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBvAGQAdQBjAGUAZABfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAbwBkAHUAYwBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAG8AZAB1AGMAZQBkAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAbwBkAHUAYwBlAGQAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAbwBkAHUAYwBlAGQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAbwBkAHUAYwBlAGQAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwB0AGkAbwBuAFcAYQBzAHQAZQBJAG4ATQBNAFMAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAHQAaQBvAG4AVwBhAHMAdABlAEkAbgBNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMAdABpAG8AbgBXAGEAcwB0AGUASQBuAE0ATQBTAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEYAcgBhAGMAdABpAG8AbgBXAGEAcwB0AGUASQBuAE0ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBGAHIAYQBjAHQAaQBvAG4AVwBhAHMAdABlAEkAbgBNAE0AUwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARgByAGEAYwB0AGkAbwBuAFcAYQBzAHQAZQBJAG4ATQBNAFMAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE0AZQB0AGgAYQBuAGUAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATQBlAHQAaABhAG4AZQBDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBNAGUAdABoAGEAbgBlAEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBEAGEAdABhACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADYAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8ANgBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAFQAaQB0AGwAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwA2AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADYAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADYAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwA2AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8ANgBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8ANgBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAcgBnAHUAbQBlAG4AdABzACIAXQAsACIAbABvAGMAYQBsAGUAIgA6AHsAIgBsAGkAcwB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAcgBvAHcAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBjAG8AbAB1AG0AbgBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUABvAHMAaQB0AGkAbwBuAHMAIgA6AFsAMwBdACwAIgBkAGUAYwBpAG0AYQBsAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiAC4AIgAsACIAZABhAHQAZQBPAHIAZABlAHIAIgA6ACIARABNAFkAIgAsACIAYwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsACIAOgAiACQAIgAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbABMAGUAYQBkACIAOgB0AHIAdQBlACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAZQBwAEIAeQBTAHAAYQBjAGUAIgA6AGYAYQBsAHMAZQAsACIAcgBvAHcATABlAHQAdABlAHIAIgA6ACIAUgAiACwAIgBjAG8AbAB1AG0AbgBMAGUAdAB0AGUAcgAiADoAIgBDACIALAAiAHIAYwBMAGUAZgB0AEIAcgBhAGMAawBlAHQAIgA6ACIAWwAiACwAIgByAGMAUgBpAGcAaAB0AEIAcgBhAGMAawBlAHQAIgA6ACIAXQAiACwAIgBzAHQAYQB0AGUAbQBlAG4AdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGwAbwBjAGEAbABlAE4AYQBtAGUAIgA6ACIAZQBuAC0AdQBzACIAfQB9AA==</AFEJSONBlob>
 </file>
 
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809E3D44-A88D-4EBF-A307-6B8CE77A3361}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -20446,4 +20455,31 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
+    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Excel/3_6_Enteric_OtherLivestock_WIP_v01.xlsx
+++ b/Excel/3_6_Enteric_OtherLivestock_WIP_v01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D30CC707-0120-44CF-B523-069D32487072}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6DA0019-B11D-44E3-8658-ECF093A386D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" firstSheet="7" activeTab="7" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="28800" windowHeight="15345" firstSheet="7" activeTab="7" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -12726,7 +12726,7 @@
         <v>58</v>
       </c>
       <c r="E13" s="57">
-        <f>DATE(YEAR(E12)+1,MONTH(E12),DAY(E12))-1</f>
+        <f>DATE(YEAR(X_Cell_Site_StartDate)+1,MONTH(X_Cell_Site_StartDate),DAY(X_Cell_Site_StartDate))-1</f>
         <v>45657</v>
       </c>
       <c r="F13" s="2" t="s">
@@ -13792,7 +13792,7 @@
         <v>0</v>
       </c>
       <c r="D8" s="1" t="str">
-        <f>"Average number of head between " &amp; TEXT('Input - Site'!$E$12, "dd mmm yy") &amp; " and " &amp; TEXT('Input - Site'!$E$13, "dd mmm yy")</f>
+        <f>"Average number of head between " &amp; TEXT(X_Cell_Site_StartDate, "dd mmm yy") &amp; " and " &amp; TEXT(X_Cell_Site_EndDate, "dd mmm yy")</f>
         <v>Average number of head between 01 Jan 24 and 31 Dec 24</v>
       </c>
       <c r="E8" s="75">
@@ -13863,7 +13863,7 @@
         <v>3.6.1.1-2 Enteric Methane</v>
       </c>
       <c r="D14" s="1" t="str">
-        <f>"Average number of head between " &amp; TEXT('Input - Site'!$E$12, "dd mmm yy") &amp; " and " &amp; TEXT('Input - Site'!$E$13, "dd mmm yy")</f>
+        <f>"Average number of head between " &amp; TEXT(X_Cell_Site_StartDate, "dd mmm yy") &amp; " and " &amp; TEXT(X_Cell_Site_EndDate, "dd mmm yy")</f>
         <v>Average number of head between 01 Jan 24 and 31 Dec 24</v>
       </c>
       <c r="E14" s="75">
@@ -13937,7 +13937,7 @@
         <v>Acknowledgements</v>
       </c>
       <c r="D20" s="1" t="str">
-        <f>"Average number of head between " &amp; TEXT('Input - Site'!$E$12, "dd mmm yy") &amp; " and " &amp; TEXT('Input - Site'!$E$13, "dd mmm yy")</f>
+        <f>"Average number of head between " &amp; TEXT(X_Cell_Site_StartDate, "dd mmm yy") &amp; " and " &amp; TEXT(X_Cell_Site_EndDate, "dd mmm yy")</f>
         <v>Average number of head between 01 Jan 24 and 31 Dec 24</v>
       </c>
       <c r="E20" s="75">
@@ -13998,7 +13998,7 @@
     </row>
     <row r="26" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D26" s="1" t="str">
-        <f>"Average number of head between " &amp; TEXT('Input - Site'!$E$12, "dd mmm yy") &amp; " and " &amp; TEXT('Input - Site'!$E$13, "dd mmm yy")</f>
+        <f>"Average number of head between " &amp; TEXT(X_Cell_Site_StartDate, "dd mmm yy") &amp; " and " &amp; TEXT(X_Cell_Site_EndDate, "dd mmm yy")</f>
         <v>Average number of head between 01 Jan 24 and 31 Dec 24</v>
       </c>
       <c r="E26" s="75">
@@ -20656,7 +20656,12 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACkAKgAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADIAKQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAHQAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAC8AdABcAHUAMAAwADMAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAdQAwADAAMgA3AFwAIgAgAFwAdQAwADAAMgA2ACAAcwBoACAAXAB1ADAAMAAyADYAIABcACIAXAB1ADAAMAAyADcAIQBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFUATgBEACgAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIAAwACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAE0ATQBTACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAaQB0AGwAZQBDAGUAbABsACwAIABTAG8AdQByAGMAZQBDAGUAbABsACwAXABuACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAEwARQBGAFQAKABTAG8AdQByAGMAZQBDAGUAbABsACwAIABGAEkATgBEACgAXAAiACwAXAAiACwAIABTAG8AdQByAGMAZQBDAGUAbABsACkAIAAtADEAKQAsACAAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFwAIgAsACAAXAAiAFwAIgApACAAXAB1ADAAMAAyADYAIABcACIAIABcACIAIABcAHUAMAAwADIANgAgAFQAaQB0AGwAZQBDAGUAbABsAFwAbgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBcAG4AVABhAGIAbABlACAAQQAuADEALgA1AC4AMQA6ACAATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAARQBuAHQAZQByAGkAYwAgAGYAZQByAG0AZQBuAHQAYQB0AGkAbwBuACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGUAYQBjAGgAIABvAHQAaABlAHIAIABsAGkAdgBlAHMAdABvAGMAawAgAHQAeQBwAGUAIAAoAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAHkAZQBhAHIAKQAgACgATQBqACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawAgAC0AIABFAG4AdABlAHIAaQBjACAAZgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZQBhAGMAaAAgAG8AdABoAGUAcgAgAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGoAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAEMASAA0ACAALwAgAGgAZQBhAGQAIAAvACAAeQBlAGEAcgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuADEAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADIALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIABUAHkAcABlAFwAIgAsACAAXAAiAE0AagBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgB1AGYAZgBhAGwAbwBcACIALAAgADYAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAG8AYQB0AHMAXAAiACwAIAA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBlAHIAXAAiACwAIAAyADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBhAG0AZQBsAHMAXAAiACwAIAA0ADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBsAHAAYQBjAGEAcwBcACIALAAgADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABvAHIAcwBlAHMAXAAiACwAIAAxADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQB1AGwAZQBzAC8AYQBzAHMAZQBzAFwAIgAsACAAMQAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAbQB1AHMALwBvAHMAdAByAGkAYwBoAGUAcwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBvAGQAdQBjAGUAZABcAG4AVABhAGIAbABlACAAQQAuADEALgA1AC4AMgA6ACAATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAAVgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIABwAHIAbwBkAHUAYwBlAGQAIABiAHkAIABlAGEAYwBoACAAbwB0AGgAZQByACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlACAAKABrAGcAIABWAFMALwBoAGUAYQBkAC8AZABhAHkAKQAgACgAVgBTAGoAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBvAGQAdQBjAGUAZABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAAVgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIABwAHIAbwBkAHUAYwBlAGQAIABiAHkAIABlAGEAYwBoACAAbwB0AGgAZQByACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBvAGQAdQBjAGUAZABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBTAGoAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAG8AZAB1AGMAZQBkAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAAVgBTACAALwAgAGgAZQBhAGQAIAAvACAAZABhAHkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAG8AZAB1AGMAZQBkAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4ANQAuADIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAG8AZAB1AGMAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBvAGQAdQBjAGUAZABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAyACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAEwAaQB2AGUAcwB0AG8AYwBrACAAVAB5AHAAZQBcACIALAAgAFwAIgBWAFMAagBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgB1AGYAZgBhAGwAbwBcACIALAAgADIALgA3ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBvAGEAdABzAFwAIgAsACAAMAAuADMANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGUAZQByAFwAIgAsACAAMAAuADkAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAbQBlAGwAcwBcACIALAAgADIALgA3ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBsAHAAYQBjAGEAcwBcACIALAAgADAALgAzADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABvAHIAcwBlAHMAXAAiACwAIAAyAC4ANwAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AdQBsAGUAcwAvAGEAcwBzAGUAcwBcACIALAAgADAALgA5ADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAHUAcwAvAG8AcwB0AHIAaQBjAGgAZQBzAFwAIgAsACAAMAAuADMANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADUALgAzADoAIABPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawAgAC0AIABOAGkAdAByAG8AZwBlAG4AIABlAHgAYwByAGUAdABlAGQAIABwAGUAcgAgAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQAgACgAawBnACAATgAyAE8ALwBoAGUAYQBkAC8AeQBlAGEAcgApACAAKABOAEUAagApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawAgAC0AIABOAGkAdAByAG8AZwBlAG4AIABlAHgAYwByAGUAdABlAGQAIABwAGUAcgAgAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4ARQBqAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGUAZABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALwAgAGgAZQBhAGQAIAAvACAAeQBlAGEAcgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA1AC4AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABlAGQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBPAHQAaABlAHIATABpAHYAZQBzAHQAbwBjAGsAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAZQBkAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADIALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIABUAHkAcABlAFwAIgAsACAAXAAiAE4ARQBqAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAHUAZgBmAGEAbABvAFwAIgAsACAAMwA5AC4ANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAG8AYQB0AHMAXAAiACwAIAA3AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGUAZQByAFwAIgAsACAAMQAzAC4AMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAbQBlAGwAcwBcACIALAAgADMAOQAuADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBsAHAAYQBjAGEAcwBcACIALAAgADcALgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHMAZQBzAFwAIgAsACAAMwA5AC4ANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAHUAbABlAHMALwBhAHMAcwBlAHMAXAAiACwAIAAxADMALgAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAbQB1AHMALwBvAHMAdAByAGkAYwBoAGUAcwBcACIALAAgADcALgAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAE8AdABoAGUAcgBMAGkAdgBlAHMAdABvAGMAawBfAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABcAG4AVABhAGIAbABlACAAQQAuADEALgA1AC4ANAA6ACAATwB0AGgAZQByACAATABpAHYAZQBzAHQAbwBjAGsAIAAtACAAQQB2AGUAcgBhAGcAZQAgAEwAaQB2AGUAdwBlAGkAZwBoAHQAcwAgACgAVwBjAG8AKQAgACgAawBnACkAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATwB0AGgAZQByAEwAaQB2AGUAcwB0AG8AYwBrAF8AQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBPAHQAaABlAHIAIABMAGkAdgBlAHMAdABvAGMAawAgAC0AIABBAHYAZQByAGEAZwBlACAATABpAHYAZQB3AGUAaQBnAGgAd